--- a/database/event/4597/event_4597_evp_summary.xlsx
+++ b/database/event/4597/event_4597_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.9873</v>
       </c>
       <c r="D2" t="n">
-        <v>2.822</v>
+        <v>2.7547</v>
       </c>
       <c r="E2" t="n">
         <v>8.028600000000001</v>
@@ -548,7 +548,7 @@
         <v>1.8704</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6312</v>
+        <v>2.5665</v>
       </c>
       <c r="E3" t="n">
         <v>7.5563</v>
@@ -594,7 +594,7 @@
         <v>1.1425</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4434</v>
+        <v>1.3951</v>
       </c>
       <c r="E4" t="n">
         <v>4.6159</v>
@@ -640,7 +640,7 @@
         <v>1.06</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3087</v>
+        <v>1.2623</v>
       </c>
       <c r="E5" t="n">
         <v>4.2826</v>
@@ -686,7 +686,7 @@
         <v>1.0379</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2725</v>
+        <v>1.2266</v>
       </c>
       <c r="E6" t="n">
         <v>4.193</v>
@@ -732,7 +732,7 @@
         <v>1.0261</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2533</v>
+        <v>1.2077</v>
       </c>
       <c r="E7" t="n">
         <v>4.1455</v>
@@ -778,7 +778,7 @@
         <v>0.9988</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2087</v>
+        <v>1.1636</v>
       </c>
       <c r="E8" t="n">
         <v>4.035</v>
@@ -824,7 +824,7 @@
         <v>0.9944</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2015</v>
+        <v>1.1565</v>
       </c>
       <c r="E9" t="n">
         <v>4.0172</v>
@@ -870,7 +870,7 @@
         <v>0.9624</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1493</v>
+        <v>1.1051</v>
       </c>
       <c r="E10" t="n">
         <v>3.888</v>
@@ -916,7 +916,7 @@
         <v>0.893</v>
       </c>
       <c r="D11" t="n">
-        <v>1.036</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="E11" t="n">
         <v>3.6076</v>
@@ -962,7 +962,7 @@
         <v>0.8734</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0041</v>
+        <v>0.9618</v>
       </c>
       <c r="E12" t="n">
         <v>3.5285</v>
@@ -1008,7 +1008,7 @@
         <v>0.7879</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8646</v>
+        <v>0.8243</v>
       </c>
       <c r="E13" t="n">
         <v>3.1832</v>
@@ -1054,7 +1054,7 @@
         <v>0.6256</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5997</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="E14" t="n">
         <v>2.5274</v>
@@ -1100,7 +1100,7 @@
         <v>0.4948</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3862</v>
+        <v>0.3525</v>
       </c>
       <c r="E15" t="n">
         <v>1.999</v>
@@ -1146,7 +1146,7 @@
         <v>0.4697</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3452</v>
+        <v>0.3121</v>
       </c>
       <c r="E16" t="n">
         <v>1.8976</v>
@@ -1192,7 +1192,7 @@
         <v>0.4639</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3357</v>
+        <v>0.3027</v>
       </c>
       <c r="E17" t="n">
         <v>1.8741</v>
@@ -1238,7 +1238,7 @@
         <v>0.4563</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3234</v>
+        <v>0.2905</v>
       </c>
       <c r="E18" t="n">
         <v>1.8435</v>
@@ -1284,7 +1284,7 @@
         <v>0.3654</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1751</v>
+        <v>0.1443</v>
       </c>
       <c r="E19" t="n">
         <v>1.4764</v>
@@ -1330,7 +1330,7 @@
         <v>0.3321</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1206</v>
+        <v>0.0906</v>
       </c>
       <c r="E20" t="n">
         <v>1.3416</v>
@@ -1376,7 +1376,7 @@
         <v>0.2954</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0607</v>
+        <v>0.0315</v>
       </c>
       <c r="E21" t="n">
         <v>1.1933</v>
@@ -1422,7 +1422,7 @@
         <v>0.2206</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0613</v>
+        <v>-0.0888</v>
       </c>
       <c r="E22" t="n">
         <v>0.8914</v>
@@ -1468,7 +1468,7 @@
         <v>0.1613</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1582</v>
+        <v>-0.1844</v>
       </c>
       <c r="E23" t="n">
         <v>0.6515</v>
@@ -1514,7 +1514,7 @@
         <v>0.1071</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2466</v>
+        <v>-0.2715</v>
       </c>
       <c r="E24" t="n">
         <v>0.4327</v>
@@ -1560,7 +1560,7 @@
         <v>0.0998</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2586</v>
+        <v>-0.2834</v>
       </c>
       <c r="E25" t="n">
         <v>0.403</v>
@@ -1606,7 +1606,7 @@
         <v>0.0215</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3863</v>
+        <v>-0.4094</v>
       </c>
       <c r="E26" t="n">
         <v>0.0867</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0267</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4649</v>
+        <v>-0.4869</v>
       </c>
       <c r="E27" t="n">
         <v>-0.1078</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0804</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5527</v>
+        <v>-0.5734</v>
       </c>
       <c r="E28" t="n">
         <v>-0.325</v>
@@ -1744,7 +1744,7 @@
         <v>-0.1238</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6234</v>
+        <v>-0.6432</v>
       </c>
       <c r="E29" t="n">
         <v>-0.5001</v>
@@ -1790,7 +1790,7 @@
         <v>-0.1357</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6429</v>
+        <v>-0.6624</v>
       </c>
       <c r="E30" t="n">
         <v>-0.5484</v>
@@ -1836,7 +1836,7 @@
         <v>-0.178</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7119</v>
+        <v>-0.7304</v>
       </c>
       <c r="E31" t="n">
         <v>-0.7192</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1864</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7256</v>
+        <v>-0.7439</v>
       </c>
       <c r="E32" t="n">
         <v>-0.753</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2437</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.819</v>
+        <v>-0.8361</v>
       </c>
       <c r="E33" t="n">
         <v>-0.9844000000000001</v>
@@ -1974,7 +1974,7 @@
         <v>-0.2484</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8268</v>
+        <v>-0.8438</v>
       </c>
       <c r="E34" t="n">
         <v>-1.0037</v>
@@ -2020,7 +2020,7 @@
         <v>-0.2486</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8272</v>
+        <v>-0.8441</v>
       </c>
       <c r="E35" t="n">
         <v>-1.0045</v>
@@ -2066,7 +2066,7 @@
         <v>-0.2495</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8285</v>
+        <v>-0.8454</v>
       </c>
       <c r="E36" t="n">
         <v>-1.0078</v>
@@ -2112,7 +2112,7 @@
         <v>-0.25</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8294</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="E37" t="n">
         <v>-1.0101</v>
@@ -2158,7 +2158,7 @@
         <v>-0.2654</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8545</v>
+        <v>-0.8711</v>
       </c>
       <c r="E38" t="n">
         <v>-1.0722</v>
@@ -2204,7 +2204,7 @@
         <v>-0.309</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9256</v>
+        <v>-0.9412</v>
       </c>
       <c r="E39" t="n">
         <v>-1.2483</v>
@@ -2250,7 +2250,7 @@
         <v>-0.651</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4838</v>
+        <v>-1.4917</v>
       </c>
       <c r="E40" t="n">
         <v>-2.63</v>
@@ -2296,7 +2296,7 @@
         <v>-0.703</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5688</v>
+        <v>-1.5755</v>
       </c>
       <c r="E41" t="n">
         <v>-2.8403</v>

--- a/database/event/4597/event_4597_evp_summary.xlsx
+++ b/database/event/4597/event_4597_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.028600000000001</v>
+        <v>7.0953</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9873</v>
+        <v>1.7563</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7547</v>
+        <v>2.5652</v>
       </c>
       <c r="E2" t="n">
-        <v>8.028600000000001</v>
+        <v>7.0953</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1985</v>
+        <v>3.4714</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8301</v>
+        <v>3.6239</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3309</v>
+        <v>6.7448</v>
       </c>
       <c r="I2" t="n">
-        <v>3.5103</v>
+        <v>3.507</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8301</v>
+        <v>3.6239</v>
       </c>
       <c r="K2" t="n">
         <v>108</v>
@@ -529,7 +529,7 @@
         <v>160</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3404</v>
+        <v>7.1309</v>
       </c>
       <c r="N2" t="n">
         <v>268</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.5563</v>
+        <v>6.7258</v>
       </c>
       <c r="C3" t="n">
-        <v>1.8704</v>
+        <v>1.6648</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5665</v>
+        <v>2.3983</v>
       </c>
       <c r="E3" t="n">
-        <v>7.5563</v>
+        <v>6.7258</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7461</v>
+        <v>3.2691</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8102</v>
+        <v>3.4567</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7461</v>
+        <v>6.0319</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0363</v>
+        <v>3.1363</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8102</v>
+        <v>3.4567</v>
       </c>
       <c r="K3" t="n">
         <v>108</v>
@@ -575,7 +575,7 @@
         <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>6.846500000000001</v>
+        <v>6.593</v>
       </c>
       <c r="N3" t="n">
         <v>268</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6159</v>
+        <v>4.3483</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1425</v>
+        <v>1.0763</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3951</v>
+        <v>1.325</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6159</v>
+        <v>4.3483</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3271</v>
+        <v>3.9251</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2888</v>
+        <v>0.4232</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8484</v>
+        <v>8.3432</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9297</v>
+        <v>4.3381</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2888</v>
+        <v>0.4232</v>
       </c>
       <c r="K4" t="n">
         <v>126</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2185</v>
+        <v>4.7613</v>
       </c>
       <c r="N4" t="n">
         <v>205</v>
@@ -630,127 +630,127 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2826</v>
+        <v>4.2986</v>
       </c>
       <c r="C5" t="n">
-        <v>1.06</v>
+        <v>1.064</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2623</v>
+        <v>1.3026</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2826</v>
+        <v>4.2986</v>
       </c>
       <c r="F5" t="n">
-        <v>4.0592</v>
+        <v>2.5036</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2234</v>
+        <v>1.795</v>
       </c>
       <c r="H5" t="n">
-        <v>4.0592</v>
+        <v>3.3347</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2901</v>
+        <v>1.7339</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2234</v>
+        <v>1.795</v>
       </c>
       <c r="K5" t="n">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="L5" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5135</v>
+        <v>3.5289</v>
       </c>
       <c r="N5" t="n">
-        <v>342</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.193</v>
+        <v>3.9247</v>
       </c>
       <c r="C6" t="n">
-        <v>1.0379</v>
+        <v>0.9715</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2266</v>
+        <v>1.1338</v>
       </c>
       <c r="E6" t="n">
-        <v>4.193</v>
+        <v>3.9247</v>
       </c>
       <c r="F6" t="n">
-        <v>4.1938</v>
+        <v>3.83</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0008</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>4.312</v>
+        <v>8.0082</v>
       </c>
       <c r="I6" t="n">
-        <v>3.495</v>
+        <v>4.1639</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0008</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="L6" t="n">
-        <v>192</v>
+        <v>79</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4942</v>
+        <v>4.258599999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>342</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1455</v>
+        <v>3.8062</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0261</v>
+        <v>0.9421</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2077</v>
+        <v>1.0803</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1455</v>
+        <v>3.8062</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2956</v>
+        <v>3.2537</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1501</v>
+        <v>0.5525</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7216</v>
+        <v>5.9776</v>
       </c>
       <c r="I7" t="n">
-        <v>3.827</v>
+        <v>3.1081</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1501</v>
+        <v>0.5525</v>
       </c>
       <c r="K7" t="n">
         <v>126</v>
@@ -759,7 +759,7 @@
         <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6769</v>
+        <v>3.6606</v>
       </c>
       <c r="N7" t="n">
         <v>205</v>
@@ -768,265 +768,265 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.035</v>
+        <v>3.7169</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9988</v>
+        <v>0.92</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1636</v>
+        <v>1.04</v>
       </c>
       <c r="E8" t="n">
-        <v>4.035</v>
+        <v>3.7169</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3273</v>
+        <v>3.73</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7077</v>
+        <v>-0.0131</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3273</v>
+        <v>7.6559</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6969</v>
+        <v>3.9807</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7077</v>
+        <v>-0.0131</v>
       </c>
       <c r="K8" t="n">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="L8" t="n">
-        <v>79</v>
+        <v>192</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4046</v>
+        <v>3.9676</v>
       </c>
       <c r="N8" t="n">
-        <v>205</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.0172</v>
+        <v>3.5377</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9944</v>
+        <v>0.8757</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1565</v>
+        <v>0.9591</v>
       </c>
       <c r="E9" t="n">
-        <v>4.0172</v>
+        <v>3.5377</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0571</v>
+        <v>3.5514</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9601</v>
+        <v>-0.0137</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0571</v>
+        <v>7.0268</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6673</v>
+        <v>3.6536</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9601</v>
+        <v>-0.0137</v>
       </c>
       <c r="K9" t="n">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="L9" t="n">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6274</v>
+        <v>3.6399</v>
       </c>
       <c r="N9" t="n">
-        <v>268</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.888</v>
+        <v>3.4986</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9624</v>
+        <v>0.866</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1051</v>
+        <v>0.9414</v>
       </c>
       <c r="E10" t="n">
-        <v>3.888</v>
+        <v>3.4986</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4247</v>
+        <v>2.5891</v>
       </c>
       <c r="G10" t="n">
-        <v>3.4633</v>
+        <v>0.9095</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4247</v>
+        <v>3.6359</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3442</v>
+        <v>1.8905</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4633</v>
+        <v>0.9095</v>
       </c>
       <c r="K10" t="n">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="L10" t="n">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8075</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>268</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6076</v>
+        <v>3.4695</v>
       </c>
       <c r="C11" t="n">
-        <v>0.893</v>
+        <v>0.8588</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.9283</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6076</v>
+        <v>3.4695</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6752</v>
+        <v>0.3371</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.06759999999999999</v>
+        <v>3.1324</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6752</v>
+        <v>0.3371</v>
       </c>
       <c r="I11" t="n">
-        <v>2.9789</v>
+        <v>0.1753</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.06759999999999999</v>
+        <v>3.1324</v>
       </c>
       <c r="K11" t="n">
-        <v>235</v>
+        <v>108</v>
       </c>
       <c r="L11" t="n">
-        <v>47</v>
+        <v>160</v>
       </c>
       <c r="M11" t="n">
-        <v>2.9113</v>
+        <v>3.3077</v>
       </c>
       <c r="N11" t="n">
-        <v>282</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5285</v>
+        <v>3.4228</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8734</v>
+        <v>0.8472</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9618</v>
+        <v>0.9072</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5285</v>
+        <v>3.4228</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8202</v>
+        <v>3.3465</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7083</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8202</v>
+        <v>6.3048</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2858</v>
+        <v>3.2782</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7083</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>150</v>
+        <v>235</v>
       </c>
       <c r="L12" t="n">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9941</v>
+        <v>3.3545</v>
       </c>
       <c r="N12" t="n">
-        <v>342</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.1832</v>
+        <v>3.3157</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7879</v>
+        <v>0.8207</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8243</v>
+        <v>0.8589</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1832</v>
+        <v>3.3157</v>
       </c>
       <c r="F13" t="n">
-        <v>4.2923</v>
+        <v>3.1244</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.1091</v>
+        <v>0.1913</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7085</v>
+        <v>5.522</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8164</v>
+        <v>2.8712</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1091</v>
+        <v>0.1913</v>
       </c>
       <c r="K13" t="n">
         <v>150</v>
@@ -1035,7 +1035,7 @@
         <v>192</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7073</v>
+        <v>3.0625</v>
       </c>
       <c r="N13" t="n">
         <v>342</v>
@@ -1044,35 +1044,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>device</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5274</v>
+        <v>2.9648</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6256</v>
+        <v>0.7339</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.7004</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5274</v>
+        <v>2.9648</v>
       </c>
       <c r="F14" t="n">
-        <v>1.957</v>
+        <v>3.7239</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5704</v>
+        <v>-0.7591</v>
       </c>
       <c r="H14" t="n">
-        <v>1.957</v>
+        <v>7.6345</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5862</v>
+        <v>3.9696</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5704</v>
+        <v>-0.7591</v>
       </c>
       <c r="K14" t="n">
         <v>150</v>
@@ -1081,7 +1081,7 @@
         <v>192</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1566</v>
+        <v>3.2105</v>
       </c>
       <c r="N14" t="n">
         <v>342</v>
@@ -1090,139 +1090,139 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.999</v>
+        <v>2.4727</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4948</v>
+        <v>0.6121</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3525</v>
+        <v>0.4783</v>
       </c>
       <c r="E15" t="n">
-        <v>1.999</v>
+        <v>2.4727</v>
       </c>
       <c r="F15" t="n">
-        <v>1.999</v>
+        <v>2.2864</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.1863</v>
       </c>
       <c r="H15" t="n">
-        <v>1.999</v>
+        <v>2.5695</v>
       </c>
       <c r="I15" t="n">
-        <v>1.999</v>
+        <v>1.336</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.1863</v>
       </c>
       <c r="K15" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M15" t="n">
-        <v>1.999</v>
+        <v>1.5223</v>
       </c>
       <c r="N15" t="n">
-        <v>210</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8976</v>
+        <v>2.2572</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4697</v>
+        <v>0.5587</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3121</v>
+        <v>0.381</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8976</v>
+        <v>2.2572</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8976</v>
+        <v>2.2572</v>
       </c>
       <c r="G16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8976</v>
+        <v>2.2572</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3486</v>
+        <v>2.2572</v>
       </c>
       <c r="J16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>126</v>
+        <v>210</v>
       </c>
       <c r="L16" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3486</v>
+        <v>2.2572</v>
       </c>
       <c r="N16" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8741</v>
+        <v>2.2175</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4639</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3027</v>
+        <v>0.3631</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8741</v>
+        <v>2.2175</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8741</v>
+        <v>3.071</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.8535</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8741</v>
+        <v>5.3339</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8741</v>
+        <v>2.7734</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.8535</v>
       </c>
       <c r="K17" t="n">
-        <v>210</v>
+        <v>126</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8741</v>
+        <v>1.9199</v>
       </c>
       <c r="N17" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18">
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.8435</v>
+        <v>2.1451</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4563</v>
+        <v>0.531</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2905</v>
+        <v>0.3304</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8435</v>
+        <v>2.1451</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8435</v>
+        <v>2.1451</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8435</v>
+        <v>2.1451</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8435</v>
+        <v>2.1451</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8435</v>
+        <v>2.1451</v>
       </c>
       <c r="N18" t="n">
         <v>143</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4764</v>
+        <v>2.0812</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3654</v>
+        <v>0.5151</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1443</v>
+        <v>0.3015</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4764</v>
+        <v>2.0812</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6858</v>
+        <v>2.0812</v>
       </c>
       <c r="G19" t="n">
-        <v>3.1622</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6858</v>
+        <v>2.0812</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3664</v>
+        <v>2.0812</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1622</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>108</v>
+        <v>210</v>
       </c>
       <c r="L19" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7958</v>
+        <v>2.0812</v>
       </c>
       <c r="N19" t="n">
-        <v>268</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3416</v>
+        <v>1.7168</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3321</v>
+        <v>0.4249</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0906</v>
+        <v>0.137</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3416</v>
+        <v>1.7168</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2919</v>
+        <v>0.9595</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0497</v>
+        <v>0.7573</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2919</v>
+        <v>0.9595</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0471</v>
+        <v>0.4989</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0497</v>
+        <v>0.7573</v>
       </c>
       <c r="K20" t="n">
-        <v>235</v>
+        <v>126</v>
       </c>
       <c r="L20" t="n">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0968</v>
+        <v>1.2562</v>
       </c>
       <c r="N20" t="n">
-        <v>282</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1933</v>
+        <v>1.4342</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2954</v>
+        <v>0.355</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0315</v>
+        <v>0.0095</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1933</v>
+        <v>1.4342</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1933</v>
+        <v>1.4342</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1933</v>
+        <v>1.4342</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1933</v>
+        <v>1.4342</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1933</v>
+        <v>1.4342</v>
       </c>
       <c r="N21" t="n">
         <v>210</v>
@@ -1412,139 +1412,139 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8914</v>
+        <v>1.2172</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2206</v>
+        <v>0.3013</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0888</v>
+        <v>-0.0885</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8914</v>
+        <v>1.2172</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0823</v>
+        <v>-2.1073</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8091</v>
+        <v>3.3245</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0823</v>
+        <v>-2.1073</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0667</v>
+        <v>-1.0957</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8091</v>
+        <v>3.3245</v>
       </c>
       <c r="K22" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="L22" t="n">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8758</v>
+        <v>2.2288</v>
       </c>
       <c r="N22" t="n">
-        <v>205</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6515</v>
+        <v>1.1809</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1613</v>
+        <v>0.2923</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1844</v>
+        <v>-0.1049</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6515</v>
+        <v>1.1809</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6515</v>
+        <v>1.1809</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6515</v>
+        <v>1.1809</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6515</v>
+        <v>1.1809</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6515</v>
+        <v>1.1809</v>
       </c>
       <c r="N23" t="n">
-        <v>101</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4327</v>
+        <v>1.0308</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1071</v>
+        <v>0.2551</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2715</v>
+        <v>-0.1727</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4327</v>
+        <v>1.0308</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4327</v>
+        <v>1.0308</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4327</v>
+        <v>1.0308</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4327</v>
+        <v>1.0308</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4327</v>
+        <v>1.0308</v>
       </c>
       <c r="N24" t="n">
-        <v>143</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.403</v>
+        <v>0.7201</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0998</v>
+        <v>0.1782</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2834</v>
+        <v>-0.3129</v>
       </c>
       <c r="E25" t="n">
-        <v>0.403</v>
+        <v>0.7201</v>
       </c>
       <c r="F25" t="n">
-        <v>0.403</v>
+        <v>0.7201</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.403</v>
+        <v>0.7201</v>
       </c>
       <c r="I25" t="n">
-        <v>0.403</v>
+        <v>0.7201</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.403</v>
+        <v>0.7201</v>
       </c>
       <c r="N25" t="n">
         <v>101</v>
@@ -1596,400 +1596,400 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0867</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0215</v>
+        <v>0.1399</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4094</v>
+        <v>-0.3829</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0867</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0867</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0867</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0867</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0867</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>210</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.1078</v>
+        <v>0.4347</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0267</v>
+        <v>0.1076</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4869</v>
+        <v>-0.4418</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.1078</v>
+        <v>0.4347</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1078</v>
+        <v>0.4347</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1078</v>
+        <v>0.4347</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1078</v>
+        <v>0.4347</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1078</v>
+        <v>0.4347</v>
       </c>
       <c r="N27" t="n">
-        <v>143</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.325</v>
+        <v>0.1133</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0804</v>
+        <v>0.028</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5734</v>
+        <v>-0.5869</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.325</v>
+        <v>0.1133</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.325</v>
+        <v>0.7329</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.6196</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.325</v>
+        <v>0.7329</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.325</v>
+        <v>0.3811</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.6196</v>
       </c>
       <c r="K28" t="n">
-        <v>101</v>
+        <v>235</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.325</v>
+        <v>-0.2385</v>
       </c>
       <c r="N28" t="n">
-        <v>101</v>
+        <v>282</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5001</v>
+        <v>0.0243</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1238</v>
+        <v>0.006</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6432</v>
+        <v>-0.627</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5001</v>
+        <v>0.0243</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.5001</v>
+        <v>0.0243</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5001</v>
+        <v>0.0243</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5001</v>
+        <v>0.0243</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5001</v>
+        <v>0.0243</v>
       </c>
       <c r="N29" t="n">
-        <v>143</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5484</v>
+        <v>-0.0683</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1357</v>
+        <v>-0.0169</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6624</v>
+        <v>-0.6688</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5484</v>
+        <v>-0.0683</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.5484</v>
+        <v>-0.0683</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.5484</v>
+        <v>-0.0683</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5484</v>
+        <v>-0.0683</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5484</v>
+        <v>-0.0683</v>
       </c>
       <c r="N30" t="n">
-        <v>101</v>
+        <v>143</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7192</v>
+        <v>-0.1003</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.178</v>
+        <v>-0.0248</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7304</v>
+        <v>-0.6833</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7192</v>
+        <v>-0.1003</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.7192</v>
+        <v>-0.1003</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7192</v>
+        <v>-0.1003</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7192</v>
+        <v>-0.1003</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>101</v>
+        <v>210</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7192</v>
+        <v>-0.1003</v>
       </c>
       <c r="N31" t="n">
-        <v>101</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.753</v>
+        <v>-0.217</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1864</v>
+        <v>-0.0537</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7439</v>
+        <v>-0.736</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.753</v>
+        <v>-0.217</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.753</v>
+        <v>0.2877</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-0.5047</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.753</v>
+        <v>0.2877</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.753</v>
+        <v>0.1496</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>-0.5047</v>
       </c>
       <c r="K32" t="n">
-        <v>101</v>
+        <v>235</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.753</v>
+        <v>-0.3551</v>
       </c>
       <c r="N32" t="n">
-        <v>101</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.4436</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2437</v>
+        <v>-0.1098</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8361</v>
+        <v>-0.8383</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.4436</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.4436</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.4436</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.4436</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>210</v>
+        <v>101</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.4436</v>
       </c>
       <c r="N33" t="n">
-        <v>210</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>vanity</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0037</v>
+        <v>-0.4569</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2484</v>
+        <v>-0.1131</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8438</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0037</v>
+        <v>-0.4569</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.0037</v>
+        <v>-0.4569</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.0037</v>
+        <v>-0.4569</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0037</v>
+        <v>-0.4569</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0037</v>
+        <v>-0.4569</v>
       </c>
       <c r="N34" t="n">
         <v>101</v>
@@ -2010,32 +2010,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0045</v>
+        <v>-0.5107</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2486</v>
+        <v>-0.1264</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8441</v>
+        <v>-0.8686</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0045</v>
+        <v>-0.5107</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.0045</v>
+        <v>-0.5107</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.0045</v>
+        <v>-0.5107</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.0045</v>
+        <v>-0.5107</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.0045</v>
+        <v>-0.5107</v>
       </c>
       <c r="N35" t="n">
         <v>101</v>
@@ -2056,124 +2056,124 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>food</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0078</v>
+        <v>-0.6079</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2495</v>
+        <v>-0.1505</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8454</v>
+        <v>-0.9125</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0078</v>
+        <v>-0.6079</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.076</v>
+        <v>-0.6079</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.9318</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.076</v>
+        <v>-0.6079</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0616</v>
+        <v>-0.6079</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.9318</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>235</v>
+        <v>101</v>
       </c>
       <c r="L36" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9933999999999999</v>
+        <v>-0.6079</v>
       </c>
       <c r="N36" t="n">
-        <v>282</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>MarKE</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0101</v>
+        <v>-0.7174</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.25</v>
+        <v>-0.1776</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8463000000000001</v>
+        <v>-0.9619</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0101</v>
+        <v>-0.7174</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.2903</v>
+        <v>-0.7174</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.7198</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.2903</v>
+        <v>-0.7174</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2353</v>
+        <v>-0.7174</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7198</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>235</v>
+        <v>101</v>
       </c>
       <c r="L37" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9551000000000001</v>
+        <v>-0.7174</v>
       </c>
       <c r="N37" t="n">
-        <v>282</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MarKE</t>
+          <t>vanity</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0722</v>
+        <v>-0.7551</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2654</v>
+        <v>-0.1869</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8711</v>
+        <v>-0.9789</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0722</v>
+        <v>-0.7551</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0722</v>
+        <v>-0.7551</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0722</v>
+        <v>-0.7551</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0722</v>
+        <v>-0.7551</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0722</v>
+        <v>-0.7551</v>
       </c>
       <c r="N38" t="n">
         <v>101</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2483</v>
+        <v>-1.0545</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.309</v>
+        <v>-0.261</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9412</v>
+        <v>-1.1141</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2483</v>
+        <v>-1.0545</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2483</v>
+        <v>-1.0545</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2483</v>
+        <v>-1.0545</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2483</v>
+        <v>-1.0545</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2483</v>
+        <v>-1.0545</v>
       </c>
       <c r="N39" t="n">
         <v>101</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.63</v>
+        <v>-2.0538</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.651</v>
+        <v>-0.5084</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4917</v>
+        <v>-1.5652</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.63</v>
+        <v>-2.0538</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.63</v>
+        <v>-1.2853</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>-0.7685</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.63</v>
+        <v>-1.2853</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3212</v>
+        <v>-0.6683</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>-0.7685</v>
       </c>
       <c r="K40" t="n">
         <v>235</v>
@@ -2277,7 +2277,7 @@
         <v>47</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.3212</v>
+        <v>-1.4368</v>
       </c>
       <c r="N40" t="n">
         <v>282</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.8403</v>
+        <v>-2.4019</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.703</v>
+        <v>-0.5945</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5755</v>
+        <v>-1.7224</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.8403</v>
+        <v>-2.4019</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.8403</v>
+        <v>-2.4019</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.8403</v>
+        <v>-2.4019</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.8403</v>
+        <v>-2.4019</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.8403</v>
+        <v>-2.4019</v>
       </c>
       <c r="N41" t="n">
         <v>143</v>
@@ -2429,10 +2429,10 @@
         <v>0.9</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0878</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.4136</v>
+        <v>-1.6682</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.79</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2554</v>
+        <v>-0.2105</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.8526</v>
+        <v>-3.9995</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.72</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3711</v>
+        <v>-0.2795</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.0509</v>
+        <v>-5.3105</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.61</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5618</v>
+        <v>-0.3799</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.6742</v>
+        <v>-7.2181</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7378</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.0182</v>
+        <v>-9.528499999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.66</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4361</v>
+        <v>1.2941</v>
       </c>
       <c r="J7" t="n">
-        <v>27.2859</v>
+        <v>24.5879</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.51</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1419</v>
+        <v>1.1153</v>
       </c>
       <c r="J8" t="n">
-        <v>21.6961</v>
+        <v>21.1907</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.37</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8089</v>
+        <v>0.9079</v>
       </c>
       <c r="J9" t="n">
-        <v>15.3691</v>
+        <v>17.2501</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.34</v>
       </c>
       <c r="I10" t="n">
-        <v>0.739</v>
+        <v>0.8436</v>
       </c>
       <c r="J10" t="n">
-        <v>14.041</v>
+        <v>16.0284</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.15</v>
       </c>
       <c r="I11" t="n">
-        <v>0.292</v>
+        <v>0.3915</v>
       </c>
       <c r="J11" t="n">
-        <v>5.548</v>
+        <v>7.4385</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.35</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5944</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>16.6432</v>
+        <v>20.0536</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0153</v>
+        <v>-0.0186</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4284</v>
+        <v>-0.5208</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.88</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2519</v>
+        <v>-0.1527</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.0532</v>
+        <v>-4.2756</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3467</v>
+        <v>-0.2153</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.707599999999999</v>
+        <v>-6.0284</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3616</v>
+        <v>-0.2254</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.1248</v>
+        <v>-6.3112</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.5981</v>
       </c>
       <c r="J17" t="n">
-        <v>17.7408</v>
+        <v>16.7468</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.13</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4459</v>
+        <v>0.4145</v>
       </c>
       <c r="J18" t="n">
-        <v>12.4852</v>
+        <v>11.606</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3566</v>
+        <v>0.3318</v>
       </c>
       <c r="J19" t="n">
-        <v>9.9848</v>
+        <v>9.2904</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.93</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3342</v>
+        <v>-0.2755</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.3576</v>
+        <v>-7.714</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.365</v>
+        <v>-0.3059</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.22</v>
+        <v>-8.565200000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.16</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3273</v>
+        <v>0.2609</v>
       </c>
       <c r="J22" t="n">
-        <v>13.7466</v>
+        <v>10.9578</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.05</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1389</v>
+        <v>0.1004</v>
       </c>
       <c r="J23" t="n">
-        <v>5.8338</v>
+        <v>4.2168</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.05</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1389</v>
+        <v>0.1004</v>
       </c>
       <c r="J24" t="n">
-        <v>5.8338</v>
+        <v>4.2168</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.01</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0455</v>
+        <v>0.0277</v>
       </c>
       <c r="J25" t="n">
-        <v>1.911</v>
+        <v>1.1634</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5318000000000001</v>
+        <v>-0.3448</v>
       </c>
       <c r="J26" t="n">
-        <v>-22.3356</v>
+        <v>-14.4816</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.23</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4023</v>
+        <v>0.3612</v>
       </c>
       <c r="J27" t="n">
-        <v>16.8966</v>
+        <v>15.1704</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.14</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2671</v>
+        <v>0.2363</v>
       </c>
       <c r="J28" t="n">
-        <v>11.2182</v>
+        <v>9.9246</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.11</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2164</v>
+        <v>0.1924</v>
       </c>
       <c r="J29" t="n">
-        <v>9.088800000000001</v>
+        <v>8.0808</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.03</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0474</v>
+        <v>0.063</v>
       </c>
       <c r="J30" t="n">
-        <v>1.9908</v>
+        <v>2.646</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.84</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3407</v>
+        <v>-0.2062</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.3094</v>
+        <v>-8.660399999999999</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>0.96</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0111</v>
+        <v>-0.026</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2664</v>
+        <v>-0.624</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.93</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.047</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.128</v>
+        <v>-1.5768</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2527</v>
+        <v>-0.2004</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.0648</v>
+        <v>-4.8096</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.65</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5259</v>
+        <v>-0.3513</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.6216</v>
+        <v>-8.4312</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.43</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8116</v>
+        <v>-0.556</v>
       </c>
       <c r="J36" t="n">
-        <v>-19.4784</v>
+        <v>-13.344</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.55</v>
       </c>
       <c r="I37" t="n">
-        <v>1.2489</v>
+        <v>1.1721</v>
       </c>
       <c r="J37" t="n">
-        <v>29.9736</v>
+        <v>28.1304</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.54</v>
       </c>
       <c r="I38" t="n">
-        <v>1.229</v>
+        <v>1.1599</v>
       </c>
       <c r="J38" t="n">
-        <v>29.496</v>
+        <v>27.8376</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.33</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7477</v>
+        <v>0.831</v>
       </c>
       <c r="J39" t="n">
-        <v>17.9448</v>
+        <v>19.944</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.31</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6983</v>
+        <v>0.7873</v>
       </c>
       <c r="J40" t="n">
-        <v>16.7592</v>
+        <v>18.8952</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.03</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0348</v>
+        <v>0.0485</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8352000000000001</v>
+        <v>1.164</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.71</v>
       </c>
       <c r="I42" t="n">
-        <v>1.6083</v>
+        <v>1.1225</v>
       </c>
       <c r="J42" t="n">
-        <v>38.5992</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.25</v>
       </c>
       <c r="I43" t="n">
-        <v>0.649</v>
+        <v>0.533</v>
       </c>
       <c r="J43" t="n">
-        <v>15.576</v>
+        <v>12.792</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.14</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3346</v>
+        <v>0.3759</v>
       </c>
       <c r="J44" t="n">
-        <v>8.0304</v>
+        <v>9.021599999999999</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.07</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1349</v>
+        <v>0.2081</v>
       </c>
       <c r="J45" t="n">
-        <v>3.2376</v>
+        <v>4.9944</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.97</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2703</v>
+        <v>-0.189</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.4872</v>
+        <v>-4.536</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.11</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3223</v>
+        <v>0.3382</v>
       </c>
       <c r="J47" t="n">
-        <v>7.7352</v>
+        <v>8.1168</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.75</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.3938</v>
+        <v>-0.2629</v>
       </c>
       <c r="J48" t="n">
-        <v>-9.4512</v>
+        <v>-6.3096</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.75</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3938</v>
+        <v>-0.2629</v>
       </c>
       <c r="J49" t="n">
-        <v>-9.4512</v>
+        <v>-6.3096</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.71</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.455</v>
+        <v>-0.301</v>
       </c>
       <c r="J50" t="n">
-        <v>-10.92</v>
+        <v>-7.224</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4985</v>
+        <v>-0.3295</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.964</v>
+        <v>-7.908</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.55</v>
       </c>
       <c r="I52" t="n">
-        <v>1.2423</v>
+        <v>0.896</v>
       </c>
       <c r="J52" t="n">
-        <v>28.5729</v>
+        <v>20.608</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.44</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0142</v>
+        <v>0.7615</v>
       </c>
       <c r="J53" t="n">
-        <v>23.3266</v>
+        <v>17.5145</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.41</v>
       </c>
       <c r="I54" t="n">
-        <v>0.9469</v>
+        <v>0.7245</v>
       </c>
       <c r="J54" t="n">
-        <v>21.7787</v>
+        <v>16.6635</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.22</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4769</v>
+        <v>0.4767</v>
       </c>
       <c r="J55" t="n">
-        <v>10.9687</v>
+        <v>10.9641</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.21</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4528</v>
+        <v>0.4624</v>
       </c>
       <c r="J56" t="n">
-        <v>10.4144</v>
+        <v>10.6352</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5047</v>
+        <v>0.4873</v>
       </c>
       <c r="J57" t="n">
-        <v>11.6081</v>
+        <v>11.2079</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.84</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2213</v>
+        <v>-0.1752</v>
       </c>
       <c r="J58" t="n">
-        <v>-5.0899</v>
+        <v>-4.0296</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.75</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3899</v>
+        <v>-0.2619</v>
       </c>
       <c r="J59" t="n">
-        <v>-8.967700000000001</v>
+        <v>-6.0237</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.65</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.538</v>
+        <v>-0.3567</v>
       </c>
       <c r="J60" t="n">
-        <v>-12.374</v>
+        <v>-8.2041</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.49</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.7453</v>
+        <v>-0.5056</v>
       </c>
       <c r="J61" t="n">
-        <v>-17.1419</v>
+        <v>-11.6288</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.3</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5693</v>
+        <v>0.5389</v>
       </c>
       <c r="J62" t="n">
-        <v>14.2325</v>
+        <v>13.4725</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.95</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0567</v>
+        <v>-0.0618</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.4175</v>
+        <v>-1.545</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.87</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.2111</v>
+        <v>-0.1528</v>
       </c>
       <c r="J64" t="n">
-        <v>-5.2775</v>
+        <v>-3.82</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.72</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4619</v>
+        <v>-0.3003</v>
       </c>
       <c r="J65" t="n">
-        <v>-11.5475</v>
+        <v>-7.5075</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.48</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7695</v>
+        <v>-0.5235</v>
       </c>
       <c r="J66" t="n">
-        <v>-19.2375</v>
+        <v>-13.0875</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.78</v>
       </c>
       <c r="I67" t="n">
-        <v>1.7052</v>
+        <v>1.1949</v>
       </c>
       <c r="J67" t="n">
-        <v>42.63</v>
+        <v>29.8725</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.49</v>
       </c>
       <c r="I68" t="n">
-        <v>1.1678</v>
+        <v>0.8395</v>
       </c>
       <c r="J68" t="n">
-        <v>29.195</v>
+        <v>20.9875</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.22</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5228</v>
+        <v>0.4884</v>
       </c>
       <c r="J69" t="n">
-        <v>13.07</v>
+        <v>12.21</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.97</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2831</v>
+        <v>-0.1991</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.0775</v>
+        <v>-4.9775</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.89</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5223</v>
+        <v>-0.449</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.0575</v>
+        <v>-11.225</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.44</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6421</v>
+        <v>0.4697</v>
       </c>
       <c r="J72" t="n">
-        <v>16.0525</v>
+        <v>11.7425</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.42</v>
       </c>
       <c r="I73" t="n">
-        <v>0.6181</v>
+        <v>0.4565</v>
       </c>
       <c r="J73" t="n">
-        <v>15.4525</v>
+        <v>11.4125</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.17</v>
       </c>
       <c r="I74" t="n">
-        <v>0.272</v>
+        <v>0.2478</v>
       </c>
       <c r="J74" t="n">
-        <v>6.8</v>
+        <v>6.195</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1115</v>
+        <v>0.1272</v>
       </c>
       <c r="J75" t="n">
-        <v>2.7875</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5199</v>
+        <v>-0.334</v>
       </c>
       <c r="J76" t="n">
-        <v>-12.9975</v>
+        <v>-8.35</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.15</v>
       </c>
       <c r="I77" t="n">
-        <v>0.325</v>
+        <v>0.2745</v>
       </c>
       <c r="J77" t="n">
-        <v>8.125</v>
+        <v>6.8625</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.13</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2938</v>
+        <v>0.2443</v>
       </c>
       <c r="J78" t="n">
-        <v>7.345</v>
+        <v>6.1075</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.88</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.247</v>
+        <v>-0.1511</v>
       </c>
       <c r="J79" t="n">
-        <v>-6.175</v>
+        <v>-3.7775</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.247</v>
+        <v>-0.1511</v>
       </c>
       <c r="J80" t="n">
-        <v>-6.175</v>
+        <v>-3.7775</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4578</v>
+        <v>-0.2928</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.445</v>
+        <v>-7.32</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.4</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6392</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>18.5368</v>
+        <v>17.2927</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.18</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3474</v>
+        <v>0.3704</v>
       </c>
       <c r="J83" t="n">
-        <v>10.0746</v>
+        <v>10.7416</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.06</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1463</v>
+        <v>0.1578</v>
       </c>
       <c r="J84" t="n">
-        <v>4.2427</v>
+        <v>4.5762</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4023</v>
+        <v>-0.2513</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.6667</v>
+        <v>-7.2877</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.67</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5622</v>
+        <v>-0.3667</v>
       </c>
       <c r="J86" t="n">
-        <v>-16.3038</v>
+        <v>-10.6343</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.38</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0362</v>
+        <v>0.7406</v>
       </c>
       <c r="J87" t="n">
-        <v>30.0498</v>
+        <v>21.4774</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.26</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7664</v>
+        <v>0.5723</v>
       </c>
       <c r="J88" t="n">
-        <v>22.2256</v>
+        <v>16.5967</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.09</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3026</v>
+        <v>0.2985</v>
       </c>
       <c r="J89" t="n">
-        <v>8.775399999999999</v>
+        <v>8.656499999999999</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0688</v>
+        <v>-0.0178</v>
       </c>
       <c r="J90" t="n">
-        <v>-1.9952</v>
+        <v>-0.5162</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.9938</v>
+        <v>-0.9688</v>
       </c>
       <c r="J91" t="n">
-        <v>-28.8202</v>
+        <v>-28.0952</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.12</v>
       </c>
       <c r="I92" t="n">
-        <v>0.353</v>
+        <v>0.3855</v>
       </c>
       <c r="J92" t="n">
-        <v>7.766</v>
+        <v>8.481</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3035</v>
+        <v>0.319</v>
       </c>
       <c r="J93" t="n">
-        <v>6.677</v>
+        <v>7.018</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.4713</v>
+        <v>-0.3151</v>
       </c>
       <c r="J94" t="n">
-        <v>-10.3686</v>
+        <v>-6.9322</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.61</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.5849</v>
+        <v>-0.3903</v>
       </c>
       <c r="J95" t="n">
-        <v>-12.8678</v>
+        <v>-8.586600000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.32</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.9418</v>
+        <v>-0.658</v>
       </c>
       <c r="J96" t="n">
-        <v>-20.7196</v>
+        <v>-14.476</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.42</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9769</v>
+        <v>1.0055</v>
       </c>
       <c r="J97" t="n">
-        <v>21.4918</v>
+        <v>22.121</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.4</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9315</v>
+        <v>0.9719</v>
       </c>
       <c r="J98" t="n">
-        <v>20.493</v>
+        <v>21.3818</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.4</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9315</v>
+        <v>0.9719</v>
       </c>
       <c r="J99" t="n">
-        <v>20.493</v>
+        <v>21.3818</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.31</v>
       </c>
       <c r="I100" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.787</v>
       </c>
       <c r="J100" t="n">
-        <v>15.3362</v>
+        <v>17.314</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.24</v>
       </c>
       <c r="I101" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.6266</v>
       </c>
       <c r="J101" t="n">
-        <v>11.6534</v>
+        <v>13.7852</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.1</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3517</v>
+        <v>0.3882</v>
       </c>
       <c r="J102" t="n">
-        <v>8.0891</v>
+        <v>8.928599999999999</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.2223</v>
+        <v>-0.1891</v>
       </c>
       <c r="J103" t="n">
-        <v>-5.1129</v>
+        <v>-4.3493</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.62</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.5463</v>
+        <v>-0.3702</v>
       </c>
       <c r="J104" t="n">
-        <v>-12.5649</v>
+        <v>-8.5146</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.59</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5897</v>
+        <v>-0.3982</v>
       </c>
       <c r="J105" t="n">
-        <v>-13.5631</v>
+        <v>-9.1586</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.37</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8736</v>
+        <v>-0.6038</v>
       </c>
       <c r="J106" t="n">
-        <v>-20.0928</v>
+        <v>-13.8874</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.66</v>
       </c>
       <c r="I107" t="n">
-        <v>1.4274</v>
+        <v>1.2906</v>
       </c>
       <c r="J107" t="n">
-        <v>32.8302</v>
+        <v>29.6838</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.52</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1524</v>
+        <v>1.1248</v>
       </c>
       <c r="J108" t="n">
-        <v>26.5052</v>
+        <v>25.8704</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.47</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0452</v>
+        <v>1.0648</v>
       </c>
       <c r="J109" t="n">
-        <v>24.0396</v>
+        <v>24.4904</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.43</v>
       </c>
       <c r="I110" t="n">
-        <v>0.9492</v>
+        <v>1.012</v>
       </c>
       <c r="J110" t="n">
-        <v>21.8316</v>
+        <v>23.276</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.05</v>
       </c>
       <c r="I111" t="n">
-        <v>0.0122</v>
+        <v>0.1004</v>
       </c>
       <c r="J111" t="n">
-        <v>0.2806</v>
+        <v>2.3092</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.31</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5187</v>
+        <v>0.6185</v>
       </c>
       <c r="J112" t="n">
-        <v>18.6732</v>
+        <v>22.266</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.09</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1923</v>
+        <v>0.2165</v>
       </c>
       <c r="J113" t="n">
-        <v>6.9228</v>
+        <v>7.794</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.01</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0092</v>
+        <v>0.0321</v>
       </c>
       <c r="J114" t="n">
-        <v>0.3312</v>
+        <v>1.1556</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.97</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.1099</v>
+        <v>-0.0543</v>
       </c>
       <c r="J115" t="n">
-        <v>-3.9564</v>
+        <v>-1.9548</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.335</v>
+        <v>-0.2034</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.06</v>
+        <v>-7.3224</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.23</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7</v>
+        <v>0.6684</v>
       </c>
       <c r="J117" t="n">
-        <v>25.2</v>
+        <v>24.0624</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.2</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6251</v>
+        <v>0.593</v>
       </c>
       <c r="J118" t="n">
-        <v>22.5036</v>
+        <v>21.348</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.6251</v>
+        <v>0.593</v>
       </c>
       <c r="J119" t="n">
-        <v>22.5036</v>
+        <v>21.348</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.88</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4864</v>
+        <v>-0.426</v>
       </c>
       <c r="J120" t="n">
-        <v>-17.5104</v>
+        <v>-15.336</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.84</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5928</v>
+        <v>-0.5359</v>
       </c>
       <c r="J121" t="n">
-        <v>-21.3408</v>
+        <v>-19.2924</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.58</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7881</v>
+        <v>0.7067</v>
       </c>
       <c r="J122" t="n">
-        <v>21.2787</v>
+        <v>19.0809</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5159</v>
+        <v>0.454</v>
       </c>
       <c r="J123" t="n">
-        <v>13.9293</v>
+        <v>12.258</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.27</v>
       </c>
       <c r="I124" t="n">
-        <v>0.4077</v>
+        <v>0.3623</v>
       </c>
       <c r="J124" t="n">
-        <v>11.0079</v>
+        <v>9.7821</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0742</v>
+        <v>-0.0202</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.0034</v>
+        <v>-0.5454</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.88</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3073</v>
+        <v>-0.1787</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.2971</v>
+        <v>-4.8249</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.56</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8618</v>
+        <v>0.8426</v>
       </c>
       <c r="J127" t="n">
-        <v>23.2686</v>
+        <v>22.7502</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.21</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4278</v>
+        <v>0.374</v>
       </c>
       <c r="J128" t="n">
-        <v>11.5506</v>
+        <v>10.098</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.79</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.376</v>
+        <v>-0.2388</v>
       </c>
       <c r="J129" t="n">
-        <v>-10.152</v>
+        <v>-6.4476</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.55</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.6937</v>
+        <v>-0.4658</v>
       </c>
       <c r="J130" t="n">
-        <v>-18.7299</v>
+        <v>-12.5766</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.47</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7883</v>
+        <v>-0.5381</v>
       </c>
       <c r="J131" t="n">
-        <v>-21.2841</v>
+        <v>-14.5287</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.05</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1988</v>
+        <v>0.1867</v>
       </c>
       <c r="J132" t="n">
-        <v>5.3676</v>
+        <v>5.0409</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.01</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1109</v>
+        <v>0.0788</v>
       </c>
       <c r="J133" t="n">
-        <v>2.9943</v>
+        <v>2.1276</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.93</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0866</v>
+        <v>-0.0835</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.3382</v>
+        <v>-2.2545</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.73</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.4413</v>
+        <v>-0.288</v>
       </c>
       <c r="J135" t="n">
-        <v>-11.9151</v>
+        <v>-7.776</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.5</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.503</v>
       </c>
       <c r="J136" t="n">
-        <v>-20.0448</v>
+        <v>-13.581</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.46</v>
       </c>
       <c r="I137" t="n">
-        <v>1.0954</v>
+        <v>1.0714</v>
       </c>
       <c r="J137" t="n">
-        <v>29.5758</v>
+        <v>28.9278</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.36</v>
       </c>
       <c r="I138" t="n">
-        <v>0.8774</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="J138" t="n">
-        <v>23.6898</v>
+        <v>24.4269</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.25</v>
       </c>
       <c r="I139" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.6624</v>
       </c>
       <c r="J139" t="n">
-        <v>15.8274</v>
+        <v>17.8848</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.5608</v>
+        <v>0.6391</v>
       </c>
       <c r="J140" t="n">
-        <v>15.1416</v>
+        <v>17.2557</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.15</v>
       </c>
       <c r="I141" t="n">
-        <v>0.332</v>
+        <v>0.4168</v>
       </c>
       <c r="J141" t="n">
-        <v>8.964</v>
+        <v>11.2536</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.15</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3286</v>
+        <v>0.3621</v>
       </c>
       <c r="J142" t="n">
-        <v>9.858000000000001</v>
+        <v>10.863</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.04</v>
       </c>
       <c r="I143" t="n">
-        <v>0.138</v>
+        <v>0.1283</v>
       </c>
       <c r="J143" t="n">
-        <v>4.14</v>
+        <v>3.849</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.98</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0291</v>
+        <v>-0.0318</v>
       </c>
       <c r="J144" t="n">
-        <v>-0.873</v>
+        <v>-0.954</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.96</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0767</v>
+        <v>-0.0591</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.301</v>
+        <v>-1.773</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.6</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6375</v>
+        <v>-0.4234</v>
       </c>
       <c r="J146" t="n">
-        <v>-19.125</v>
+        <v>-12.702</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.46</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1936</v>
+        <v>1.1171</v>
       </c>
       <c r="J147" t="n">
-        <v>35.808</v>
+        <v>33.513</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.2</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6078</v>
+        <v>0.5837</v>
       </c>
       <c r="J148" t="n">
-        <v>18.234</v>
+        <v>17.511</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.09</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2742</v>
+        <v>0.2961</v>
       </c>
       <c r="J149" t="n">
-        <v>8.226000000000001</v>
+        <v>8.882999999999999</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.88</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4972</v>
+        <v>-0.4338</v>
       </c>
       <c r="J150" t="n">
-        <v>-14.916</v>
+        <v>-13.014</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.86</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5507</v>
+        <v>-0.4894</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.521</v>
+        <v>-14.682</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.29</v>
       </c>
       <c r="I152" t="n">
-        <v>0.4985</v>
+        <v>0.5903</v>
       </c>
       <c r="J152" t="n">
-        <v>13.958</v>
+        <v>16.5284</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.163</v>
+        <v>0.1783</v>
       </c>
       <c r="J153" t="n">
-        <v>4.564</v>
+        <v>4.9924</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.06</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1435</v>
+        <v>0.1567</v>
       </c>
       <c r="J154" t="n">
-        <v>4.018</v>
+        <v>4.3876</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0183</v>
+        <v>-0.0018</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.5124</v>
+        <v>-0.0504</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.71</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5118</v>
+        <v>-0.3296</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.3304</v>
+        <v>-9.2288</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.2</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>16.8084</v>
+        <v>16.2428</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.19</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5742</v>
+        <v>0.555</v>
       </c>
       <c r="J158" t="n">
-        <v>16.0776</v>
+        <v>15.54</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.16</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4928</v>
+        <v>0.4788</v>
       </c>
       <c r="J159" t="n">
-        <v>13.7984</v>
+        <v>13.4064</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.14</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4351</v>
+        <v>0.4271</v>
       </c>
       <c r="J160" t="n">
-        <v>12.1828</v>
+        <v>11.9588</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.4927</v>
       </c>
       <c r="J161" t="n">
-        <v>-15.5372</v>
+        <v>-13.7956</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.28</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7953</v>
+        <v>0.7748</v>
       </c>
       <c r="J162" t="n">
-        <v>21.4731</v>
+        <v>20.9196</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.13</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4028</v>
+        <v>0.4006</v>
       </c>
       <c r="J163" t="n">
-        <v>10.8756</v>
+        <v>10.8162</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.11</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3297</v>
+        <v>0.3483</v>
       </c>
       <c r="J164" t="n">
-        <v>8.901899999999999</v>
+        <v>9.4041</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.08</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2277</v>
+        <v>0.2651</v>
       </c>
       <c r="J165" t="n">
-        <v>6.1479</v>
+        <v>7.1577</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.96</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.262</v>
+        <v>-0.1941</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.074</v>
+        <v>-5.2407</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.32</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.6651</v>
       </c>
       <c r="J167" t="n">
-        <v>15.039</v>
+        <v>17.9577</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.04</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1288</v>
+        <v>0.1228</v>
       </c>
       <c r="J168" t="n">
-        <v>3.4776</v>
+        <v>3.3156</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J169" t="n">
-        <v>2.268</v>
+        <v>1.944</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.331</v>
+        <v>-0.2049</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.936999999999999</v>
+        <v>-5.5323</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.63</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6039</v>
+        <v>-0.3982</v>
       </c>
       <c r="J171" t="n">
-        <v>-16.3053</v>
+        <v>-10.7514</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.66</v>
       </c>
       <c r="I172" t="n">
-        <v>1.5061</v>
+        <v>1.3289</v>
       </c>
       <c r="J172" t="n">
-        <v>36.1464</v>
+        <v>31.8936</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.53</v>
       </c>
       <c r="I173" t="n">
-        <v>1.2575</v>
+        <v>1.1678</v>
       </c>
       <c r="J173" t="n">
-        <v>30.18</v>
+        <v>28.0272</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.37</v>
       </c>
       <c r="I174" t="n">
-        <v>0.9238</v>
+        <v>0.9358</v>
       </c>
       <c r="J174" t="n">
-        <v>22.1712</v>
+        <v>22.4592</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.19</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4564</v>
+        <v>0.5275</v>
       </c>
       <c r="J175" t="n">
-        <v>10.9536</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.5</v>
       </c>
       <c r="I176" t="n">
-        <v>-1.367</v>
+        <v>-1.398</v>
       </c>
       <c r="J176" t="n">
-        <v>-32.808</v>
+        <v>-33.552</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.35</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.7395</v>
       </c>
       <c r="J177" t="n">
-        <v>14.6736</v>
+        <v>17.748</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.17</v>
       </c>
       <c r="I178" t="n">
-        <v>0.3676</v>
+        <v>0.4099</v>
       </c>
       <c r="J178" t="n">
-        <v>8.8224</v>
+        <v>9.8376</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.92</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.154</v>
+        <v>-0.1042</v>
       </c>
       <c r="J179" t="n">
-        <v>-3.696</v>
+        <v>-2.5008</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.67</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5442</v>
+        <v>-0.3554</v>
       </c>
       <c r="J180" t="n">
-        <v>-13.0608</v>
+        <v>-8.5296</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.5</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.7541</v>
+        <v>-0.5118</v>
       </c>
       <c r="J181" t="n">
-        <v>-18.0984</v>
+        <v>-12.2832</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.97</v>
       </c>
       <c r="I182" t="n">
-        <v>1.9356</v>
+        <v>1.636</v>
       </c>
       <c r="J182" t="n">
-        <v>36.7764</v>
+        <v>31.084</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.6</v>
       </c>
       <c r="I183" t="n">
-        <v>1.2915</v>
+        <v>1.2133</v>
       </c>
       <c r="J183" t="n">
-        <v>24.5385</v>
+        <v>23.0527</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.6</v>
       </c>
       <c r="I184" t="n">
-        <v>1.2915</v>
+        <v>1.2133</v>
       </c>
       <c r="J184" t="n">
-        <v>24.5385</v>
+        <v>23.0527</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.2</v>
       </c>
       <c r="I185" t="n">
-        <v>0.394</v>
+        <v>0.5049</v>
       </c>
       <c r="J185" t="n">
-        <v>7.486</v>
+        <v>9.5931</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.99</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2545</v>
+        <v>-0.1643</v>
       </c>
       <c r="J186" t="n">
-        <v>-4.8355</v>
+        <v>-3.1217</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.8</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1747</v>
+        <v>-0.1636</v>
       </c>
       <c r="J187" t="n">
-        <v>-3.3193</v>
+        <v>-3.1084</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.75</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2524</v>
+        <v>-0.2197</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.7956</v>
+        <v>-4.1743</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.62</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.4556</v>
+        <v>-0.3526</v>
       </c>
       <c r="J189" t="n">
-        <v>-8.6564</v>
+        <v>-6.6994</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.48</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.6986</v>
+        <v>-0.4799</v>
       </c>
       <c r="J190" t="n">
-        <v>-13.2734</v>
+        <v>-9.1181</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.25</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.9982</v>
+        <v>-0.7016</v>
       </c>
       <c r="J191" t="n">
-        <v>-18.9658</v>
+        <v>-13.3304</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.23</v>
       </c>
       <c r="I192" t="n">
-        <v>0.4179</v>
+        <v>0.3715</v>
       </c>
       <c r="J192" t="n">
-        <v>15.0444</v>
+        <v>13.374</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.14</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2846</v>
+        <v>0.2443</v>
       </c>
       <c r="J193" t="n">
-        <v>10.2456</v>
+        <v>8.7948</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1638</v>
+        <v>-0.0906</v>
       </c>
       <c r="J194" t="n">
-        <v>-5.8968</v>
+        <v>-3.2616</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.91</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2181</v>
+        <v>-0.1257</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.8516</v>
+        <v>-4.5252</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.9</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.2351</v>
+        <v>-0.1369</v>
       </c>
       <c r="J196" t="n">
-        <v>-8.4636</v>
+        <v>-4.9284</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.37</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5714</v>
+        <v>0.4947</v>
       </c>
       <c r="J197" t="n">
-        <v>20.5704</v>
+        <v>17.8092</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.36</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5589</v>
+        <v>0.4831</v>
       </c>
       <c r="J198" t="n">
-        <v>20.1204</v>
+        <v>17.3916</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.13</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2281</v>
+        <v>0.2009</v>
       </c>
       <c r="J199" t="n">
-        <v>8.211600000000001</v>
+        <v>7.2324</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.05</v>
       </c>
       <c r="I200" t="n">
-        <v>0.0713</v>
+        <v>0.0867</v>
       </c>
       <c r="J200" t="n">
-        <v>2.5668</v>
+        <v>3.1212</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.68</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5639</v>
+        <v>-0.3671</v>
       </c>
       <c r="J201" t="n">
-        <v>-20.3004</v>
+        <v>-13.2156</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.71</v>
       </c>
       <c r="I202" t="n">
-        <v>1.5715</v>
+        <v>1.3746</v>
       </c>
       <c r="J202" t="n">
-        <v>37.716</v>
+        <v>32.9904</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.3</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7056</v>
+        <v>0.7722</v>
       </c>
       <c r="J203" t="n">
-        <v>16.9344</v>
+        <v>18.5328</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.28</v>
       </c>
       <c r="I204" t="n">
-        <v>0.6522</v>
+        <v>0.7279</v>
       </c>
       <c r="J204" t="n">
-        <v>15.6528</v>
+        <v>17.4696</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.25</v>
       </c>
       <c r="I205" t="n">
-        <v>0.5767</v>
+        <v>0.6594</v>
       </c>
       <c r="J205" t="n">
-        <v>13.8408</v>
+        <v>15.8256</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.1581</v>
+        <v>-0.0747</v>
       </c>
       <c r="J206" t="n">
-        <v>-3.7944</v>
+        <v>-1.7928</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.1</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2523</v>
+        <v>0.2647</v>
       </c>
       <c r="J207" t="n">
-        <v>6.0552</v>
+        <v>6.3528</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0373</v>
+        <v>0.0114</v>
       </c>
       <c r="J208" t="n">
-        <v>0.8952</v>
+        <v>0.2736</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.96</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0707</v>
+        <v>-0.0582</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.6968</v>
+        <v>-1.3968</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.82</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3368</v>
+        <v>-0.2112</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.0832</v>
+        <v>-5.0688</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.367</v>
+        <v>-0.2313</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.808</v>
+        <v>-5.5512</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.32</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.6479</v>
       </c>
       <c r="J212" t="n">
-        <v>15.1984</v>
+        <v>18.1412</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.14</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2898</v>
+        <v>0.323</v>
       </c>
       <c r="J213" t="n">
-        <v>8.1144</v>
+        <v>9.044</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.96</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1187</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.3236</v>
+        <v>-1.7976</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.85</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3117</v>
+        <v>-0.1891</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.727600000000001</v>
+        <v>-5.2948</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.78</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4143</v>
+        <v>-0.2601</v>
       </c>
       <c r="J216" t="n">
-        <v>-11.6004</v>
+        <v>-7.2828</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.38</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0286</v>
+        <v>1.0034</v>
       </c>
       <c r="J217" t="n">
-        <v>28.8008</v>
+        <v>28.0952</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.27</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7821</v>
+        <v>0.7574</v>
       </c>
       <c r="J218" t="n">
-        <v>21.8988</v>
+        <v>21.2072</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0766</v>
+        <v>-0.0214</v>
       </c>
       <c r="J219" t="n">
-        <v>-2.1448</v>
+        <v>-0.5992</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.97</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2181</v>
+        <v>-0.1543</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.1068</v>
+        <v>-4.3204</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.85</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5755</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.114</v>
+        <v>-14.4368</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.14</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3117</v>
+        <v>0.3411</v>
       </c>
       <c r="J222" t="n">
-        <v>8.104200000000001</v>
+        <v>8.868600000000001</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.03</v>
       </c>
       <c r="I223" t="n">
-        <v>0.115</v>
+        <v>0.1024</v>
       </c>
       <c r="J223" t="n">
-        <v>2.99</v>
+        <v>2.6624</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.89</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2275</v>
+        <v>-0.1397</v>
       </c>
       <c r="J224" t="n">
-        <v>-5.915</v>
+        <v>-3.6322</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.85</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2943</v>
+        <v>-0.1821</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.6518</v>
+        <v>-4.7346</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.84</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3101</v>
+        <v>-0.1925</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.0626</v>
+        <v>-5.005</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.57</v>
       </c>
       <c r="I227" t="n">
-        <v>1.3726</v>
+        <v>1.2377</v>
       </c>
       <c r="J227" t="n">
-        <v>35.6876</v>
+        <v>32.1802</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.17</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4581</v>
+        <v>0.492</v>
       </c>
       <c r="J228" t="n">
-        <v>11.9106</v>
+        <v>12.792</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.13</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3376</v>
+        <v>0.3903</v>
       </c>
       <c r="J229" t="n">
-        <v>8.7776</v>
+        <v>10.1478</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.0122</v>
+        <v>0.0539</v>
       </c>
       <c r="J230" t="n">
-        <v>-0.3172</v>
+        <v>1.4014</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.98</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2141</v>
+        <v>-0.1381</v>
       </c>
       <c r="J231" t="n">
-        <v>-5.5666</v>
+        <v>-3.5906</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.2</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3906</v>
+        <v>0.4453</v>
       </c>
       <c r="J232" t="n">
-        <v>10.9368</v>
+        <v>12.4684</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.06</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1637</v>
+        <v>0.1663</v>
       </c>
       <c r="J233" t="n">
-        <v>4.5836</v>
+        <v>4.6564</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.93</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1666</v>
+        <v>-0.098</v>
       </c>
       <c r="J234" t="n">
-        <v>-4.6648</v>
+        <v>-2.744</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.2036</v>
+        <v>-0.1209</v>
       </c>
       <c r="J235" t="n">
-        <v>-5.7008</v>
+        <v>-3.3852</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.8</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3788</v>
+        <v>-0.2367</v>
       </c>
       <c r="J236" t="n">
-        <v>-10.6064</v>
+        <v>-6.6276</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.35</v>
       </c>
       <c r="I237" t="n">
-        <v>0.98</v>
+        <v>0.9576</v>
       </c>
       <c r="J237" t="n">
-        <v>27.44</v>
+        <v>26.8128</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.29</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8456</v>
+        <v>0.8181</v>
       </c>
       <c r="J238" t="n">
-        <v>23.6768</v>
+        <v>22.9068</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.18</v>
       </c>
       <c r="I239" t="n">
-        <v>0.5772</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="J239" t="n">
-        <v>16.1616</v>
+        <v>15.2292</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.95</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2735</v>
+        <v>-0.2144</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.658</v>
+        <v>-6.0032</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.55</v>
       </c>
       <c r="I241" t="n">
-        <v>-1.2409</v>
+        <v>-1.2487</v>
       </c>
       <c r="J241" t="n">
-        <v>-34.7452</v>
+        <v>-34.9636</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1</v>
       </c>
       <c r="I242" t="n">
-        <v>0.1596</v>
+        <v>0.1393</v>
       </c>
       <c r="J242" t="n">
-        <v>3.5112</v>
+        <v>3.0646</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.74</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.3133</v>
+        <v>-0.2529</v>
       </c>
       <c r="J243" t="n">
-        <v>-6.8926</v>
+        <v>-5.5638</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.68</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.412</v>
+        <v>-0.3108</v>
       </c>
       <c r="J244" t="n">
-        <v>-9.064</v>
+        <v>-6.8376</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.62</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5274</v>
+        <v>-0.3642</v>
       </c>
       <c r="J245" t="n">
-        <v>-11.6028</v>
+        <v>-8.0124</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.26</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.9978</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="J246" t="n">
-        <v>-21.9516</v>
+        <v>-15.4462</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.78</v>
       </c>
       <c r="I247" t="n">
-        <v>1.6472</v>
+        <v>1.4307</v>
       </c>
       <c r="J247" t="n">
-        <v>36.2384</v>
+        <v>31.4754</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.66</v>
       </c>
       <c r="I248" t="n">
-        <v>1.4283</v>
+        <v>1.291</v>
       </c>
       <c r="J248" t="n">
-        <v>31.4226</v>
+        <v>28.402</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.63</v>
       </c>
       <c r="I249" t="n">
-        <v>1.3715</v>
+        <v>1.2557</v>
       </c>
       <c r="J249" t="n">
-        <v>30.173</v>
+        <v>27.6254</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.05</v>
       </c>
       <c r="I250" t="n">
-        <v>0.0127</v>
+        <v>0.1008</v>
       </c>
       <c r="J250" t="n">
-        <v>0.2794</v>
+        <v>2.2176</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>1</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.1872</v>
+        <v>-0.0999</v>
       </c>
       <c r="J251" t="n">
-        <v>-4.1184</v>
+        <v>-2.1978</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.43</v>
       </c>
       <c r="I252" t="n">
-        <v>1.1192</v>
+        <v>1.0702</v>
       </c>
       <c r="J252" t="n">
-        <v>33.576</v>
+        <v>32.106</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.17</v>
       </c>
       <c r="I253" t="n">
-        <v>0.512</v>
+        <v>0.5014</v>
       </c>
       <c r="J253" t="n">
-        <v>15.36</v>
+        <v>15.042</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.08</v>
       </c>
       <c r="I254" t="n">
-        <v>0.2205</v>
+        <v>0.263</v>
       </c>
       <c r="J254" t="n">
-        <v>6.615</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2308</v>
+        <v>-0.1618</v>
       </c>
       <c r="J255" t="n">
-        <v>-6.924</v>
+        <v>-4.854</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.96</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.2663</v>
+        <v>-0.1967</v>
       </c>
       <c r="J256" t="n">
-        <v>-7.989</v>
+        <v>-5.901</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.25</v>
       </c>
       <c r="I257" t="n">
-        <v>0.4536</v>
+        <v>0.5291</v>
       </c>
       <c r="J257" t="n">
-        <v>13.608</v>
+        <v>15.873</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.14</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2934</v>
+        <v>0.3257</v>
       </c>
       <c r="J258" t="n">
-        <v>8.802</v>
+        <v>9.771000000000001</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.07</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1743</v>
+        <v>0.1836</v>
       </c>
       <c r="J259" t="n">
-        <v>5.229</v>
+        <v>5.508</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.83</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3395</v>
+        <v>-0.2086</v>
       </c>
       <c r="J260" t="n">
-        <v>-10.185</v>
+        <v>-6.258</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.71</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.5072</v>
+        <v>-0.3267</v>
       </c>
       <c r="J261" t="n">
-        <v>-15.216</v>
+        <v>-9.801</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>2</v>
       </c>
       <c r="I262" t="n">
-        <v>1.9477</v>
+        <v>1.6512</v>
       </c>
       <c r="J262" t="n">
-        <v>33.1109</v>
+        <v>28.0704</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.79</v>
       </c>
       <c r="I263" t="n">
-        <v>1.6111</v>
+        <v>1.4184</v>
       </c>
       <c r="J263" t="n">
-        <v>27.3887</v>
+        <v>24.1128</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.49</v>
       </c>
       <c r="I264" t="n">
-        <v>0.9949</v>
+        <v>1.078</v>
       </c>
       <c r="J264" t="n">
-        <v>16.9133</v>
+        <v>18.326</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.28</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5514</v>
+        <v>0.6792</v>
       </c>
       <c r="J265" t="n">
-        <v>9.373799999999999</v>
+        <v>11.5464</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.22</v>
       </c>
       <c r="I266" t="n">
-        <v>0.4179</v>
+        <v>0.5372</v>
       </c>
       <c r="J266" t="n">
-        <v>7.1043</v>
+        <v>9.132400000000001</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.18</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5392</v>
+        <v>0.6867</v>
       </c>
       <c r="J267" t="n">
-        <v>9.166399999999999</v>
+        <v>11.6739</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.64</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.4271</v>
+        <v>-0.3348</v>
       </c>
       <c r="J268" t="n">
-        <v>-7.2607</v>
+        <v>-5.6916</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.42</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.7839</v>
+        <v>-0.5382</v>
       </c>
       <c r="J269" t="n">
-        <v>-13.3263</v>
+        <v>-9.1494</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.35</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.8753</v>
+        <v>-0.6055</v>
       </c>
       <c r="J270" t="n">
-        <v>-14.8801</v>
+        <v>-10.2935</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.34</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.888</v>
+        <v>-0.6152</v>
       </c>
       <c r="J271" t="n">
-        <v>-15.096</v>
+        <v>-10.4584</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.4</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0562</v>
+        <v>1.0273</v>
       </c>
       <c r="J272" t="n">
-        <v>38.0232</v>
+        <v>36.9828</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.36</v>
       </c>
       <c r="I273" t="n">
-        <v>0.9702</v>
+        <v>0.9553</v>
       </c>
       <c r="J273" t="n">
-        <v>34.9272</v>
+        <v>34.3908</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.08</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2205</v>
+        <v>0.263</v>
       </c>
       <c r="J274" t="n">
-        <v>7.938</v>
+        <v>9.468</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.03</v>
       </c>
       <c r="I275" t="n">
-        <v>0.0506</v>
+        <v>0.104</v>
       </c>
       <c r="J275" t="n">
-        <v>1.8216</v>
+        <v>3.744</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.74</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.8493000000000001</v>
+        <v>-0.8079</v>
       </c>
       <c r="J276" t="n">
-        <v>-30.5748</v>
+        <v>-29.0844</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.21</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4134</v>
+        <v>0.4725</v>
       </c>
       <c r="J277" t="n">
-        <v>14.8824</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.16</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3402</v>
+        <v>0.3781</v>
       </c>
       <c r="J278" t="n">
-        <v>12.2472</v>
+        <v>13.6116</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.96</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0599</v>
       </c>
       <c r="J279" t="n">
-        <v>-3.0276</v>
+        <v>-2.1564</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.84</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.312</v>
+        <v>-0.1932</v>
       </c>
       <c r="J280" t="n">
-        <v>-11.232</v>
+        <v>-6.9552</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.61</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.6268</v>
+        <v>-0.4153</v>
       </c>
       <c r="J281" t="n">
-        <v>-22.5648</v>
+        <v>-14.9508</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.17</v>
       </c>
       <c r="I282" t="n">
-        <v>0.6069</v>
+        <v>0.5538</v>
       </c>
       <c r="J282" t="n">
-        <v>18.207</v>
+        <v>16.614</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.14</v>
       </c>
       <c r="I283" t="n">
-        <v>0.5271</v>
+        <v>0.472</v>
       </c>
       <c r="J283" t="n">
-        <v>15.813</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.9</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3812</v>
+        <v>-0.3414</v>
       </c>
       <c r="J284" t="n">
-        <v>-11.436</v>
+        <v>-10.242</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.86</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4974</v>
+        <v>-0.4534</v>
       </c>
       <c r="J285" t="n">
-        <v>-14.922</v>
+        <v>-13.602</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.8</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6565</v>
+        <v>-0.6132</v>
       </c>
       <c r="J286" t="n">
-        <v>-19.695</v>
+        <v>-18.396</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.63</v>
       </c>
       <c r="I287" t="n">
-        <v>0.8596</v>
+        <v>1.052</v>
       </c>
       <c r="J287" t="n">
-        <v>25.788</v>
+        <v>31.56</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.21</v>
       </c>
       <c r="I288" t="n">
-        <v>0.3426</v>
+        <v>0.4184</v>
       </c>
       <c r="J288" t="n">
-        <v>10.278</v>
+        <v>12.552</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.18</v>
       </c>
       <c r="I289" t="n">
-        <v>0.2953</v>
+        <v>0.3665</v>
       </c>
       <c r="J289" t="n">
-        <v>8.859</v>
+        <v>10.995</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.93</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.2158</v>
+        <v>-0.1165</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.474</v>
+        <v>-3.495</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.83</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.3711</v>
+        <v>-0.2254</v>
       </c>
       <c r="J291" t="n">
-        <v>-11.133</v>
+        <v>-6.762</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.48</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1879</v>
+        <v>1.1187</v>
       </c>
       <c r="J292" t="n">
-        <v>33.2612</v>
+        <v>31.3236</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.23</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6263</v>
+        <v>0.633</v>
       </c>
       <c r="J293" t="n">
-        <v>17.5364</v>
+        <v>17.724</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.14</v>
       </c>
       <c r="I294" t="n">
-        <v>0.3573</v>
+        <v>0.4136</v>
       </c>
       <c r="J294" t="n">
-        <v>10.0044</v>
+        <v>11.5808</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.13</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3288</v>
+        <v>0.3873</v>
       </c>
       <c r="J295" t="n">
-        <v>9.2064</v>
+        <v>10.8444</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.96</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2915</v>
+        <v>-0.214</v>
       </c>
       <c r="J296" t="n">
-        <v>-8.162000000000001</v>
+        <v>-5.992</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.05</v>
       </c>
       <c r="I297" t="n">
-        <v>0.1757</v>
+        <v>0.1653</v>
       </c>
       <c r="J297" t="n">
-        <v>4.9196</v>
+        <v>4.6284</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.02</v>
       </c>
       <c r="I298" t="n">
-        <v>0.1122</v>
+        <v>0.089</v>
       </c>
       <c r="J298" t="n">
-        <v>3.1416</v>
+        <v>2.492</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.9</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.182</v>
+        <v>-0.1244</v>
       </c>
       <c r="J299" t="n">
-        <v>-5.096</v>
+        <v>-3.4832</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.82</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3253</v>
+        <v>-0.2071</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.1084</v>
+        <v>-5.7988</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.72</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4724</v>
+        <v>-0.3053</v>
       </c>
       <c r="J301" t="n">
-        <v>-13.2272</v>
+        <v>-8.548400000000001</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>2.27</v>
       </c>
       <c r="I302" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J302" t="n">
-        <v>39.1267</v>
+        <v>34.8422</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.68</v>
       </c>
       <c r="I303" t="n">
-        <v>1.4345</v>
+        <v>1.3026</v>
       </c>
       <c r="J303" t="n">
-        <v>27.2555</v>
+        <v>24.7494</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.29</v>
       </c>
       <c r="I304" t="n">
-        <v>0.5913</v>
+        <v>0.7141</v>
       </c>
       <c r="J304" t="n">
-        <v>11.2347</v>
+        <v>13.5679</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.18</v>
       </c>
       <c r="I305" t="n">
-        <v>0.3401</v>
+        <v>0.45</v>
       </c>
       <c r="J305" t="n">
-        <v>6.4619</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.06</v>
       </c>
       <c r="I306" t="n">
-        <v>0.0267</v>
+        <v>0.1181</v>
       </c>
       <c r="J306" t="n">
-        <v>0.5073</v>
+        <v>2.2439</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.89</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.0318</v>
+        <v>-0.0575</v>
       </c>
       <c r="J307" t="n">
-        <v>-0.6042</v>
+        <v>-1.0925</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.62</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.46</v>
+        <v>-0.3538</v>
       </c>
       <c r="J308" t="n">
-        <v>-8.74</v>
+        <v>-6.7222</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.53</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.6272</v>
+        <v>-0.4342</v>
       </c>
       <c r="J309" t="n">
-        <v>-11.9168</v>
+        <v>-8.2498</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.52</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.6425</v>
+        <v>-0.4435</v>
       </c>
       <c r="J310" t="n">
-        <v>-12.2075</v>
+        <v>-8.426500000000001</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.37</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.8497</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="J311" t="n">
-        <v>-16.1443</v>
+        <v>-11.1378</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4597/event_4597_evp_summary.xlsx
+++ b/database/event/4597/event_4597_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.0953</v>
+        <v>7.1001</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7563</v>
+        <v>1.7574</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5652</v>
+        <v>2.6079</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0953</v>
+        <v>7.1001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4714</v>
+        <v>3.3948</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6239</v>
+        <v>3.7053</v>
       </c>
       <c r="H2" t="n">
-        <v>6.7448</v>
+        <v>6.3066</v>
       </c>
       <c r="I2" t="n">
-        <v>3.507</v>
+        <v>3.4055</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6239</v>
+        <v>3.7053</v>
       </c>
       <c r="K2" t="n">
         <v>108</v>
@@ -529,7 +529,7 @@
         <v>160</v>
       </c>
       <c r="M2" t="n">
-        <v>7.1309</v>
+        <v>7.110799999999999</v>
       </c>
       <c r="N2" t="n">
         <v>268</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.7258</v>
+        <v>6.783</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6648</v>
+        <v>1.679</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3983</v>
+        <v>2.4636</v>
       </c>
       <c r="E3" t="n">
-        <v>6.7258</v>
+        <v>6.783</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2691</v>
+        <v>3.1842</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4567</v>
+        <v>3.5988</v>
       </c>
       <c r="H3" t="n">
-        <v>6.0319</v>
+        <v>5.6116</v>
       </c>
       <c r="I3" t="n">
-        <v>3.1363</v>
+        <v>3.0302</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4567</v>
+        <v>3.5988</v>
       </c>
       <c r="K3" t="n">
         <v>108</v>
@@ -575,7 +575,7 @@
         <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>6.593</v>
+        <v>6.629</v>
       </c>
       <c r="N3" t="n">
         <v>268</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3483</v>
+        <v>4.4503</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0763</v>
+        <v>1.1016</v>
       </c>
       <c r="D4" t="n">
-        <v>1.325</v>
+        <v>1.4017</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3483</v>
+        <v>4.4503</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9251</v>
+        <v>3.9572</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4232</v>
+        <v>0.4931</v>
       </c>
       <c r="H4" t="n">
-        <v>8.3432</v>
+        <v>8.1622</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3381</v>
+        <v>4.4075</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4232</v>
+        <v>0.4931</v>
       </c>
       <c r="K4" t="n">
         <v>126</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7613</v>
+        <v>4.9006</v>
       </c>
       <c r="N4" t="n">
         <v>205</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2986</v>
+        <v>4.4418</v>
       </c>
       <c r="C5" t="n">
-        <v>1.064</v>
+        <v>1.0995</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3026</v>
+        <v>1.3978</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2986</v>
+        <v>4.4418</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5036</v>
+        <v>2.4257</v>
       </c>
       <c r="G5" t="n">
-        <v>1.795</v>
+        <v>2.0161</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3347</v>
+        <v>3.1091</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7339</v>
+        <v>1.6789</v>
       </c>
       <c r="J5" t="n">
-        <v>1.795</v>
+        <v>2.0161</v>
       </c>
       <c r="K5" t="n">
         <v>108</v>
@@ -667,7 +667,7 @@
         <v>160</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5289</v>
+        <v>3.695</v>
       </c>
       <c r="N5" t="n">
         <v>268</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9247</v>
+        <v>3.9055</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9715</v>
+        <v>0.9667</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1338</v>
+        <v>1.1537</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9247</v>
+        <v>3.9055</v>
       </c>
       <c r="F6" t="n">
-        <v>3.83</v>
+        <v>3.7746</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1309</v>
       </c>
       <c r="H6" t="n">
-        <v>8.0082</v>
+        <v>7.5596</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1639</v>
+        <v>4.0821</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.1309</v>
       </c>
       <c r="K6" t="n">
         <v>126</v>
@@ -713,7 +713,7 @@
         <v>79</v>
       </c>
       <c r="M6" t="n">
-        <v>4.258599999999999</v>
+        <v>4.212999999999999</v>
       </c>
       <c r="N6" t="n">
         <v>205</v>
@@ -722,127 +722,127 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8062</v>
+        <v>3.8192</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9421</v>
+        <v>0.9453</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0803</v>
+        <v>1.1144</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8062</v>
+        <v>3.8192</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2537</v>
+        <v>0.5545</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5525</v>
+        <v>3.2647</v>
       </c>
       <c r="H7" t="n">
-        <v>5.9776</v>
+        <v>0.5545</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1081</v>
+        <v>0.2994</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5525</v>
+        <v>3.2647</v>
       </c>
       <c r="K7" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="L7" t="n">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6606</v>
+        <v>3.5641</v>
       </c>
       <c r="N7" t="n">
-        <v>205</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7169</v>
+        <v>3.8165</v>
       </c>
       <c r="C8" t="n">
-        <v>0.92</v>
+        <v>0.9447</v>
       </c>
       <c r="D8" t="n">
-        <v>1.04</v>
+        <v>1.1131</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7169</v>
+        <v>3.8165</v>
       </c>
       <c r="F8" t="n">
-        <v>3.73</v>
+        <v>3.2054</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0131</v>
+        <v>0.6111</v>
       </c>
       <c r="H8" t="n">
-        <v>7.6559</v>
+        <v>5.6818</v>
       </c>
       <c r="I8" t="n">
-        <v>3.9807</v>
+        <v>3.0681</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0131</v>
+        <v>0.6111</v>
       </c>
       <c r="K8" t="n">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="L8" t="n">
-        <v>192</v>
+        <v>79</v>
       </c>
       <c r="M8" t="n">
-        <v>3.9676</v>
+        <v>3.6792</v>
       </c>
       <c r="N8" t="n">
-        <v>342</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5377</v>
+        <v>3.7071</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8757</v>
+        <v>0.9176</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9591</v>
+        <v>1.0633</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5377</v>
+        <v>3.7071</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5514</v>
+        <v>3.6423</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0137</v>
+        <v>0.0648</v>
       </c>
       <c r="H9" t="n">
-        <v>7.0268</v>
+        <v>7.1231</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6536</v>
+        <v>3.8464</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0137</v>
+        <v>0.0648</v>
       </c>
       <c r="K9" t="n">
         <v>150</v>
@@ -851,7 +851,7 @@
         <v>192</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6399</v>
+        <v>3.9112</v>
       </c>
       <c r="N9" t="n">
         <v>342</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4986</v>
+        <v>3.545</v>
       </c>
       <c r="C10" t="n">
-        <v>0.866</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9414</v>
+        <v>0.9896</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4986</v>
+        <v>3.545</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5891</v>
+        <v>3.4817</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9095</v>
+        <v>0.0633</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6359</v>
+        <v>6.5932</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8905</v>
+        <v>3.5603</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9095</v>
+        <v>0.0633</v>
       </c>
       <c r="K10" t="n">
         <v>150</v>
@@ -897,7 +897,7 @@
         <v>192</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>3.6236</v>
       </c>
       <c r="N10" t="n">
         <v>342</v>
@@ -906,139 +906,139 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4695</v>
+        <v>3.5114</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8588</v>
+        <v>0.8692</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9283</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4695</v>
+        <v>3.5114</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3371</v>
+        <v>2.5492</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1324</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3371</v>
+        <v>3.5165</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1753</v>
+        <v>1.8989</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1324</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="L11" t="n">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3077</v>
+        <v>2.8611</v>
       </c>
       <c r="N11" t="n">
-        <v>268</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4228</v>
+        <v>3.3897</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8472</v>
+        <v>0.839</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9072</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4228</v>
+        <v>3.3897</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3465</v>
+        <v>3.0426</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.3471</v>
       </c>
       <c r="H12" t="n">
-        <v>6.3048</v>
+        <v>5.1445</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2782</v>
+        <v>2.778</v>
       </c>
       <c r="J12" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.3471</v>
       </c>
       <c r="K12" t="n">
-        <v>235</v>
+        <v>150</v>
       </c>
       <c r="L12" t="n">
-        <v>47</v>
+        <v>192</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3545</v>
+        <v>3.1251</v>
       </c>
       <c r="N12" t="n">
-        <v>282</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.3157</v>
+        <v>3.2756</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8207</v>
+        <v>0.8108</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8589</v>
+        <v>0.8669</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3157</v>
+        <v>3.2756</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1244</v>
+        <v>3.2274</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1913</v>
+        <v>0.0482</v>
       </c>
       <c r="H13" t="n">
-        <v>5.522</v>
+        <v>5.7542</v>
       </c>
       <c r="I13" t="n">
-        <v>2.8712</v>
+        <v>3.1072</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1913</v>
+        <v>0.0482</v>
       </c>
       <c r="K13" t="n">
-        <v>150</v>
+        <v>235</v>
       </c>
       <c r="L13" t="n">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="M13" t="n">
-        <v>3.0625</v>
+        <v>3.1554</v>
       </c>
       <c r="N13" t="n">
-        <v>342</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.9648</v>
+        <v>2.8515</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7339</v>
+        <v>0.7058</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7004</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9648</v>
+        <v>2.8515</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7239</v>
+        <v>3.6489</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7591</v>
+        <v>-0.7974</v>
       </c>
       <c r="H14" t="n">
-        <v>7.6345</v>
+        <v>7.1447</v>
       </c>
       <c r="I14" t="n">
-        <v>3.9696</v>
+        <v>3.8581</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7591</v>
+        <v>-0.7974</v>
       </c>
       <c r="K14" t="n">
         <v>150</v>
@@ -1081,7 +1081,7 @@
         <v>192</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2105</v>
+        <v>3.0607</v>
       </c>
       <c r="N14" t="n">
         <v>342</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.4727</v>
+        <v>2.3762</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6121</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4783</v>
+        <v>0.4575</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4727</v>
+        <v>2.3762</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2864</v>
+        <v>2.1671</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1863</v>
+        <v>0.2091</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5695</v>
+        <v>2.2558</v>
       </c>
       <c r="I15" t="n">
-        <v>1.336</v>
+        <v>1.2181</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1863</v>
+        <v>0.2091</v>
       </c>
       <c r="K15" t="n">
         <v>235</v>
@@ -1127,7 +1127,7 @@
         <v>47</v>
       </c>
       <c r="M15" t="n">
-        <v>1.5223</v>
+        <v>1.4272</v>
       </c>
       <c r="N15" t="n">
         <v>282</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2572</v>
+        <v>2.1651</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5587</v>
+        <v>0.5359</v>
       </c>
       <c r="D16" t="n">
-        <v>0.381</v>
+        <v>0.3614</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2572</v>
+        <v>2.1651</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2572</v>
+        <v>2.1651</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2572</v>
+        <v>2.1651</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2572</v>
+        <v>2.1651</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.2572</v>
+        <v>2.1651</v>
       </c>
       <c r="N16" t="n">
         <v>210</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.2175</v>
+        <v>2.126</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5262</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3631</v>
+        <v>0.3436</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2175</v>
+        <v>2.126</v>
       </c>
       <c r="F17" t="n">
-        <v>3.071</v>
+        <v>3.0145</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8535</v>
+        <v>-0.8885</v>
       </c>
       <c r="H17" t="n">
-        <v>5.3339</v>
+        <v>5.0519</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7734</v>
+        <v>2.728</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8535</v>
+        <v>-0.8885</v>
       </c>
       <c r="K17" t="n">
         <v>126</v>
@@ -1219,7 +1219,7 @@
         <v>79</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9199</v>
+        <v>1.8395</v>
       </c>
       <c r="N17" t="n">
         <v>205</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.1451</v>
+        <v>2.0214</v>
       </c>
       <c r="C18" t="n">
-        <v>0.531</v>
+        <v>0.5003</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3304</v>
+        <v>0.296</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1451</v>
+        <v>2.0214</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1451</v>
+        <v>2.0214</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1451</v>
+        <v>2.0214</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1451</v>
+        <v>2.0214</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.1451</v>
+        <v>2.0214</v>
       </c>
       <c r="N18" t="n">
-        <v>143</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.0812</v>
+        <v>2.008</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5151</v>
+        <v>0.497</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3015</v>
+        <v>0.2899</v>
       </c>
       <c r="E19" t="n">
-        <v>2.0812</v>
+        <v>2.008</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0812</v>
+        <v>2.008</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0812</v>
+        <v>2.008</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0812</v>
+        <v>2.008</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.0812</v>
+        <v>2.008</v>
       </c>
       <c r="N19" t="n">
-        <v>210</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.7168</v>
+        <v>1.8709</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4249</v>
+        <v>0.4631</v>
       </c>
       <c r="D20" t="n">
-        <v>0.137</v>
+        <v>0.2275</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7168</v>
+        <v>1.8709</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9595</v>
+        <v>1.0091</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7573</v>
+        <v>0.8618</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9595</v>
+        <v>1.0091</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4989</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7573</v>
+        <v>0.8618</v>
       </c>
       <c r="K20" t="n">
         <v>126</v>
@@ -1357,7 +1357,7 @@
         <v>79</v>
       </c>
       <c r="M20" t="n">
-        <v>1.2562</v>
+        <v>1.4067</v>
       </c>
       <c r="N20" t="n">
         <v>205</v>
@@ -1366,93 +1366,93 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4342</v>
+        <v>1.4772</v>
       </c>
       <c r="C21" t="n">
-        <v>0.355</v>
+        <v>0.3656</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0095</v>
+        <v>0.0482</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4342</v>
+        <v>1.4772</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4342</v>
+        <v>-1.8684</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>3.3456</v>
       </c>
       <c r="H21" t="n">
-        <v>1.4342</v>
+        <v>-1.8684</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4342</v>
+        <v>-1.0089</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>3.3456</v>
       </c>
       <c r="K21" t="n">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M21" t="n">
-        <v>1.4342</v>
+        <v>2.3367</v>
       </c>
       <c r="N21" t="n">
-        <v>210</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.2172</v>
+        <v>1.473</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3013</v>
+        <v>0.3646</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0885</v>
+        <v>0.0463</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2172</v>
+        <v>1.473</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1073</v>
+        <v>1.473</v>
       </c>
       <c r="G22" t="n">
-        <v>3.3245</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1073</v>
+        <v>1.473</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0957</v>
+        <v>1.473</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3245</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>108</v>
+        <v>210</v>
       </c>
       <c r="L22" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.2288</v>
+        <v>1.473</v>
       </c>
       <c r="N22" t="n">
-        <v>268</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.1809</v>
+        <v>1.0436</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2923</v>
+        <v>0.2583</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1049</v>
+        <v>-0.1491</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1809</v>
+        <v>1.0436</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1809</v>
+        <v>1.0436</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1809</v>
+        <v>1.0436</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1809</v>
+        <v>1.0436</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1809</v>
+        <v>1.0436</v>
       </c>
       <c r="N23" t="n">
         <v>143</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.0308</v>
+        <v>0.9314</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2551</v>
+        <v>0.2305</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.1727</v>
+        <v>-0.2002</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0308</v>
+        <v>0.9314</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0308</v>
+        <v>0.9314</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.0308</v>
+        <v>0.9314</v>
       </c>
       <c r="I24" t="n">
-        <v>1.0308</v>
+        <v>0.9314</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0308</v>
+        <v>0.9314</v>
       </c>
       <c r="N24" t="n">
         <v>101</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7201</v>
+        <v>0.6802</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1782</v>
+        <v>0.1684</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3129</v>
+        <v>-0.3146</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7201</v>
+        <v>0.6802</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7201</v>
+        <v>0.6802</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7201</v>
+        <v>0.6802</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7201</v>
+        <v>0.6802</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7201</v>
+        <v>0.6802</v>
       </c>
       <c r="N25" t="n">
         <v>101</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.4551</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1399</v>
+        <v>0.1126</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3829</v>
+        <v>-0.417</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.4551</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.4551</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.4551</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.4551</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.4551</v>
       </c>
       <c r="N26" t="n">
         <v>143</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4347</v>
+        <v>0.3639</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1076</v>
+        <v>0.0901</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4418</v>
+        <v>-0.4585</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4347</v>
+        <v>0.3639</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4347</v>
+        <v>0.3639</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4347</v>
+        <v>0.3639</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4347</v>
+        <v>0.3639</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4347</v>
+        <v>0.3639</v>
       </c>
       <c r="N27" t="n">
         <v>210</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1133</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>0.028</v>
+        <v>0.0209</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5869</v>
+        <v>-0.5857</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1133</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7329</v>
+        <v>0.738</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.6196</v>
+        <v>-0.6534</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7329</v>
+        <v>0.738</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3811</v>
+        <v>0.3985</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6196</v>
+        <v>-0.6534</v>
       </c>
       <c r="K28" t="n">
         <v>235</v>
@@ -1725,7 +1725,7 @@
         <v>47</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2385</v>
+        <v>-0.2549</v>
       </c>
       <c r="N28" t="n">
         <v>282</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0243</v>
+        <v>-0.0464</v>
       </c>
       <c r="C29" t="n">
-        <v>0.006</v>
+        <v>-0.0115</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.627</v>
+        <v>-0.6453</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0243</v>
+        <v>-0.0464</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0243</v>
+        <v>-0.0464</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0243</v>
+        <v>-0.0464</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0243</v>
+        <v>-0.0464</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0243</v>
+        <v>-0.0464</v>
       </c>
       <c r="N29" t="n">
         <v>101</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0683</v>
+        <v>-0.1346</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0169</v>
+        <v>-0.0333</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6688</v>
+        <v>-0.6855</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0683</v>
+        <v>-0.1346</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0683</v>
+        <v>-0.1346</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0683</v>
+        <v>-0.1346</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0683</v>
+        <v>-0.1346</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0683</v>
+        <v>-0.1346</v>
       </c>
       <c r="N30" t="n">
         <v>143</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1003</v>
+        <v>-0.1382</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0248</v>
+        <v>-0.0342</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6833</v>
+        <v>-0.6871</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1003</v>
+        <v>-0.1382</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1003</v>
+        <v>-0.1382</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1003</v>
+        <v>-0.1382</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1003</v>
+        <v>-0.1382</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1003</v>
+        <v>-0.1382</v>
       </c>
       <c r="N31" t="n">
         <v>210</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.217</v>
+        <v>-0.4425</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0537</v>
+        <v>-0.1095</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.736</v>
+        <v>-0.8256</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.217</v>
+        <v>-0.4425</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2877</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5047</v>
+        <v>-0.5401</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2877</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1496</v>
+        <v>0.0527</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5047</v>
+        <v>-0.5401</v>
       </c>
       <c r="K32" t="n">
         <v>235</v>
@@ -1909,7 +1909,7 @@
         <v>47</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3551</v>
+        <v>-0.4874000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>282</v>
@@ -1918,32 +1918,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4436</v>
+        <v>-0.4691</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1098</v>
+        <v>-0.1161</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8383</v>
+        <v>-0.8377</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4436</v>
+        <v>-0.4691</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4436</v>
+        <v>-0.4691</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4436</v>
+        <v>-0.4691</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4436</v>
+        <v>-0.4691</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4436</v>
+        <v>-0.4691</v>
       </c>
       <c r="N33" t="n">
         <v>101</v>
@@ -1964,32 +1964,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4569</v>
+        <v>-0.4814</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1131</v>
+        <v>-0.1192</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8443000000000001</v>
+        <v>-0.8433</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4569</v>
+        <v>-0.4814</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4569</v>
+        <v>-0.4814</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4569</v>
+        <v>-0.4814</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4569</v>
+        <v>-0.4814</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4569</v>
+        <v>-0.4814</v>
       </c>
       <c r="N34" t="n">
         <v>101</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5107</v>
+        <v>-0.5854</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1264</v>
+        <v>-0.1449</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8686</v>
+        <v>-0.8907</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5107</v>
+        <v>-0.5854</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5107</v>
+        <v>-0.5854</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5107</v>
+        <v>-0.5854</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5107</v>
+        <v>-0.5854</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5107</v>
+        <v>-0.5854</v>
       </c>
       <c r="N35" t="n">
         <v>101</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6079</v>
+        <v>-0.6511</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1505</v>
+        <v>-0.1612</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9125</v>
+        <v>-0.9206</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6079</v>
+        <v>-0.6511</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6079</v>
+        <v>-0.6511</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6079</v>
+        <v>-0.6511</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6079</v>
+        <v>-0.6511</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6079</v>
+        <v>-0.6511</v>
       </c>
       <c r="N36" t="n">
         <v>101</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7174</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1776</v>
+        <v>-0.1895</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9619</v>
+        <v>-0.9727</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7174</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7174</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7174</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7174</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7174</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="N37" t="n">
         <v>101</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.7551</v>
+        <v>-0.7817</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1869</v>
+        <v>-0.1935</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9789</v>
+        <v>-0.98</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.7551</v>
+        <v>-0.7817</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.7551</v>
+        <v>-0.7817</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7551</v>
+        <v>-0.7817</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7551</v>
+        <v>-0.7817</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7551</v>
+        <v>-0.7817</v>
       </c>
       <c r="N38" t="n">
         <v>101</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0545</v>
+        <v>-1.0832</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.261</v>
+        <v>-0.2681</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1141</v>
+        <v>-1.1173</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0545</v>
+        <v>-1.0832</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0545</v>
+        <v>-1.0832</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0545</v>
+        <v>-1.0832</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0545</v>
+        <v>-1.0832</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0545</v>
+        <v>-1.0832</v>
       </c>
       <c r="N39" t="n">
         <v>101</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0538</v>
+        <v>-2.0463</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5084</v>
+        <v>-0.5065</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5652</v>
+        <v>-1.5557</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0538</v>
+        <v>-2.0463</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2853</v>
+        <v>-1.2517</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7685</v>
+        <v>-0.7946</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2853</v>
+        <v>-1.2517</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6683</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7685</v>
+        <v>-0.7946</v>
       </c>
       <c r="K40" t="n">
         <v>235</v>
@@ -2277,7 +2277,7 @@
         <v>47</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4368</v>
+        <v>-1.4705</v>
       </c>
       <c r="N40" t="n">
         <v>282</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4019</v>
+        <v>-2.2669</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5945</v>
+        <v>-0.5611</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.7224</v>
+        <v>-1.6561</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4019</v>
+        <v>-2.2669</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.4019</v>
+        <v>-2.2669</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.4019</v>
+        <v>-2.2669</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.4019</v>
+        <v>-2.2669</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.4019</v>
+        <v>-2.2669</v>
       </c>
       <c r="N41" t="n">
         <v>143</v>
@@ -2429,10 +2429,10 @@
         <v>0.9</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0878</v>
+        <v>-0.111</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.6682</v>
+        <v>-2.109</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.79</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2105</v>
+        <v>-0.2326</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.9995</v>
+        <v>-4.4194</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.72</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2795</v>
+        <v>-0.2999</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.3105</v>
+        <v>-5.6981</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.61</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3799</v>
+        <v>-0.3969</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.2181</v>
+        <v>-7.5411</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.5115</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.528499999999999</v>
+        <v>-9.718500000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.66</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2941</v>
+        <v>1.3714</v>
       </c>
       <c r="J7" t="n">
-        <v>24.5879</v>
+        <v>26.0566</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.51</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1153</v>
+        <v>1.112</v>
       </c>
       <c r="J8" t="n">
-        <v>21.1907</v>
+        <v>21.128</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.37</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9079</v>
+        <v>0.8615</v>
       </c>
       <c r="J9" t="n">
-        <v>17.2501</v>
+        <v>16.3685</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.34</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8436</v>
+        <v>0.8047</v>
       </c>
       <c r="J10" t="n">
-        <v>16.0284</v>
+        <v>15.2893</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.15</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3915</v>
+        <v>0.402</v>
       </c>
       <c r="J11" t="n">
-        <v>7.4385</v>
+        <v>7.638</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.35</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7161999999999999</v>
+        <v>0.6848</v>
       </c>
       <c r="J12" t="n">
-        <v>20.0536</v>
+        <v>19.1744</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0186</v>
+        <v>-0.0238</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5208</v>
+        <v>-0.6664</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.88</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1527</v>
+        <v>-0.1667</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.2756</v>
+        <v>-4.6676</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2153</v>
+        <v>-0.2296</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.0284</v>
+        <v>-6.4288</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2254</v>
+        <v>-0.2397</v>
       </c>
       <c r="J16" t="n">
-        <v>-6.3112</v>
+        <v>-6.7116</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5981</v>
+        <v>0.5713</v>
       </c>
       <c r="J17" t="n">
-        <v>16.7468</v>
+        <v>15.9964</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.13</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4145</v>
+        <v>0.4061</v>
       </c>
       <c r="J18" t="n">
-        <v>11.606</v>
+        <v>11.3708</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3318</v>
+        <v>0.3302</v>
       </c>
       <c r="J19" t="n">
-        <v>9.2904</v>
+        <v>9.2456</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.93</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2755</v>
+        <v>-0.2703</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.714</v>
+        <v>-7.5684</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3059</v>
+        <v>-0.2986</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.565200000000001</v>
+        <v>-8.360799999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.16</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2609</v>
+        <v>0.2718</v>
       </c>
       <c r="J22" t="n">
-        <v>10.9578</v>
+        <v>11.4156</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.05</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1004</v>
+        <v>0.1108</v>
       </c>
       <c r="J23" t="n">
-        <v>4.2168</v>
+        <v>4.6536</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.05</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1004</v>
+        <v>0.1108</v>
       </c>
       <c r="J24" t="n">
-        <v>4.2168</v>
+        <v>4.6536</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.01</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0277</v>
+        <v>0.0328</v>
       </c>
       <c r="J25" t="n">
-        <v>1.1634</v>
+        <v>1.3776</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3448</v>
+        <v>-0.3561</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.4816</v>
+        <v>-14.9562</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.23</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3612</v>
+        <v>0.3671</v>
       </c>
       <c r="J27" t="n">
-        <v>15.1704</v>
+        <v>15.4182</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.14</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2363</v>
+        <v>0.2473</v>
       </c>
       <c r="J28" t="n">
-        <v>9.9246</v>
+        <v>10.3866</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.11</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1924</v>
+        <v>0.2044</v>
       </c>
       <c r="J29" t="n">
-        <v>8.0808</v>
+        <v>8.5848</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.03</v>
       </c>
       <c r="I30" t="n">
-        <v>0.063</v>
+        <v>0.0731</v>
       </c>
       <c r="J30" t="n">
-        <v>2.646</v>
+        <v>3.0702</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.84</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2062</v>
+        <v>-0.2181</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.660399999999999</v>
+        <v>-9.1602</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>0.96</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.026</v>
+        <v>-0.0437</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.624</v>
+        <v>-1.0488</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.93</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>-1.5768</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2004</v>
+        <v>-0.2205</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.8096</v>
+        <v>-5.292</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.65</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3513</v>
+        <v>-0.368</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.4312</v>
+        <v>-8.832000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.43</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.556</v>
+        <v>-0.5613</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.344</v>
+        <v>-13.4712</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.55</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1721</v>
+        <v>1.1924</v>
       </c>
       <c r="J37" t="n">
-        <v>28.1304</v>
+        <v>28.6176</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.54</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1599</v>
+        <v>1.1747</v>
       </c>
       <c r="J38" t="n">
-        <v>27.8376</v>
+        <v>28.1928</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.33</v>
       </c>
       <c r="I39" t="n">
-        <v>0.831</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>19.944</v>
+        <v>19.0032</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.31</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7873</v>
+        <v>0.7532</v>
       </c>
       <c r="J40" t="n">
-        <v>18.8952</v>
+        <v>18.0768</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.03</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0485</v>
+        <v>0.079</v>
       </c>
       <c r="J41" t="n">
-        <v>1.164</v>
+        <v>1.896</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.71</v>
       </c>
       <c r="I42" t="n">
-        <v>1.1225</v>
+        <v>1.2293</v>
       </c>
       <c r="J42" t="n">
-        <v>26.94</v>
+        <v>29.5032</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.25</v>
       </c>
       <c r="I43" t="n">
-        <v>0.533</v>
+        <v>0.5924</v>
       </c>
       <c r="J43" t="n">
-        <v>12.792</v>
+        <v>14.2176</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.14</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3759</v>
+        <v>0.4054</v>
       </c>
       <c r="J44" t="n">
-        <v>9.021599999999999</v>
+        <v>9.7296</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.07</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2081</v>
+        <v>0.224</v>
       </c>
       <c r="J45" t="n">
-        <v>4.9944</v>
+        <v>5.376</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.97</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.189</v>
+        <v>-0.1764</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.536</v>
+        <v>-4.2336</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.11</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3382</v>
+        <v>0.3286</v>
       </c>
       <c r="J47" t="n">
-        <v>8.1168</v>
+        <v>7.8864</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.75</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2629</v>
+        <v>-0.2812</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.3096</v>
+        <v>-6.7488</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.75</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2629</v>
+        <v>-0.2812</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.3096</v>
+        <v>-6.7488</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.71</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.301</v>
+        <v>-0.3183</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.224</v>
+        <v>-7.6392</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3295</v>
+        <v>-0.3459</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.908</v>
+        <v>-8.301600000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.55</v>
       </c>
       <c r="I52" t="n">
-        <v>0.896</v>
+        <v>0.994</v>
       </c>
       <c r="J52" t="n">
-        <v>20.608</v>
+        <v>22.862</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.44</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7615</v>
+        <v>0.8485</v>
       </c>
       <c r="J53" t="n">
-        <v>17.5145</v>
+        <v>19.5155</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.41</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7245</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>16.6635</v>
+        <v>18.584</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.22</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4767</v>
+        <v>0.5331</v>
       </c>
       <c r="J55" t="n">
-        <v>10.9641</v>
+        <v>12.2613</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.21</v>
       </c>
       <c r="I56" t="n">
-        <v>0.4624</v>
+        <v>0.517</v>
       </c>
       <c r="J56" t="n">
-        <v>10.6352</v>
+        <v>11.891</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4873</v>
+        <v>0.5274</v>
       </c>
       <c r="J57" t="n">
-        <v>11.2079</v>
+        <v>12.1302</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.84</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1752</v>
+        <v>-0.1942</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.0296</v>
+        <v>-4.4666</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.75</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2619</v>
+        <v>-0.2804</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.0237</v>
+        <v>-6.4492</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.65</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3567</v>
+        <v>-0.3722</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.2041</v>
+        <v>-8.560600000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.49</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5056</v>
+        <v>-0.5134</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.6288</v>
+        <v>-11.8082</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.3</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5389</v>
+        <v>0.5913</v>
       </c>
       <c r="J62" t="n">
-        <v>13.4725</v>
+        <v>14.7825</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.95</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.0618</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.545</v>
+        <v>-1.8825</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.87</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1528</v>
+        <v>-0.1694</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.82</v>
+        <v>-4.235</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.72</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3003</v>
+        <v>-0.3159</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.5075</v>
+        <v>-7.8975</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.48</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5235</v>
+        <v>-0.529</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.0875</v>
+        <v>-13.225</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.78</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1949</v>
+        <v>1.3076</v>
       </c>
       <c r="J67" t="n">
-        <v>29.8725</v>
+        <v>32.69</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.49</v>
       </c>
       <c r="I68" t="n">
-        <v>0.8395</v>
+        <v>0.9296</v>
       </c>
       <c r="J68" t="n">
-        <v>20.9875</v>
+        <v>23.24</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.22</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4884</v>
+        <v>0.5432</v>
       </c>
       <c r="J69" t="n">
-        <v>12.21</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.97</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1991</v>
+        <v>-0.1835</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.9775</v>
+        <v>-4.5875</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.89</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.449</v>
+        <v>-0.4183</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.225</v>
+        <v>-10.4575</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.44</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4697</v>
+        <v>0.5346</v>
       </c>
       <c r="J72" t="n">
-        <v>11.7425</v>
+        <v>13.365</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.42</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4565</v>
+        <v>0.5191</v>
       </c>
       <c r="J73" t="n">
-        <v>11.4125</v>
+        <v>12.9775</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.17</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2478</v>
+        <v>0.265</v>
       </c>
       <c r="J74" t="n">
-        <v>6.195</v>
+        <v>6.625</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1272</v>
+        <v>0.1439</v>
       </c>
       <c r="J75" t="n">
-        <v>3.18</v>
+        <v>3.5975</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.334</v>
+        <v>-0.3424</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.35</v>
+        <v>-8.56</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.15</v>
       </c>
       <c r="I77" t="n">
-        <v>0.2745</v>
+        <v>0.279</v>
       </c>
       <c r="J77" t="n">
-        <v>6.8625</v>
+        <v>6.975</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.13</v>
       </c>
       <c r="I78" t="n">
-        <v>0.2443</v>
+        <v>0.25</v>
       </c>
       <c r="J78" t="n">
-        <v>6.1075</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.88</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1511</v>
+        <v>-0.1654</v>
       </c>
       <c r="J79" t="n">
-        <v>-3.7775</v>
+        <v>-4.135</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1511</v>
+        <v>-0.1654</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.7775</v>
+        <v>-4.135</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2928</v>
+        <v>-0.3063</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.32</v>
+        <v>-7.6575</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.4</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.6651</v>
       </c>
       <c r="J82" t="n">
-        <v>17.2927</v>
+        <v>19.2879</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.18</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3704</v>
+        <v>0.3949</v>
       </c>
       <c r="J83" t="n">
-        <v>10.7416</v>
+        <v>11.4521</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.06</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1578</v>
+        <v>0.1673</v>
       </c>
       <c r="J84" t="n">
-        <v>4.5762</v>
+        <v>4.8517</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2513</v>
+        <v>-0.2641</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.2877</v>
+        <v>-7.6589</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.67</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3667</v>
+        <v>-0.3767</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.6343</v>
+        <v>-10.9243</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.38</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7406</v>
+        <v>0.8137</v>
       </c>
       <c r="J87" t="n">
-        <v>21.4774</v>
+        <v>23.5973</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.26</v>
       </c>
       <c r="I88" t="n">
-        <v>0.5723</v>
+        <v>0.6299</v>
       </c>
       <c r="J88" t="n">
-        <v>16.5967</v>
+        <v>18.2671</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.09</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2985</v>
+        <v>0.3006</v>
       </c>
       <c r="J89" t="n">
-        <v>8.656499999999999</v>
+        <v>8.7174</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0178</v>
+        <v>-0.0121</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.5162</v>
+        <v>-0.3509</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.9688</v>
+        <v>-0.888</v>
       </c>
       <c r="J91" t="n">
-        <v>-28.0952</v>
+        <v>-25.752</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.12</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3855</v>
+        <v>0.3637</v>
       </c>
       <c r="J92" t="n">
-        <v>8.481</v>
+        <v>8.0014</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.319</v>
+        <v>0.301</v>
       </c>
       <c r="J93" t="n">
-        <v>7.018</v>
+        <v>6.622</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3151</v>
+        <v>-0.3329</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.9322</v>
+        <v>-7.3238</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.61</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3903</v>
+        <v>-0.4051</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.586600000000001</v>
+        <v>-8.9122</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.32</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.658</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.476</v>
+        <v>-14.4254</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.42</v>
       </c>
       <c r="I97" t="n">
-        <v>1.0055</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="J97" t="n">
-        <v>22.121</v>
+        <v>21.0342</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.4</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9719</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="J98" t="n">
-        <v>21.3818</v>
+        <v>20.2598</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.4</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9719</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="J99" t="n">
-        <v>21.3818</v>
+        <v>20.2598</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.31</v>
       </c>
       <c r="I100" t="n">
-        <v>0.787</v>
+        <v>0.753</v>
       </c>
       <c r="J100" t="n">
-        <v>17.314</v>
+        <v>16.566</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.24</v>
       </c>
       <c r="I101" t="n">
-        <v>0.6266</v>
+        <v>0.6108</v>
       </c>
       <c r="J101" t="n">
-        <v>13.7852</v>
+        <v>13.4376</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.1</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3882</v>
+        <v>0.357</v>
       </c>
       <c r="J102" t="n">
-        <v>8.928599999999999</v>
+        <v>8.211</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1891</v>
+        <v>-0.2117</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.3493</v>
+        <v>-4.8691</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.62</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3702</v>
+        <v>-0.3878</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.5146</v>
+        <v>-8.9194</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.59</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3982</v>
+        <v>-0.4144</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.1586</v>
+        <v>-9.5312</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.37</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6038</v>
+        <v>-0.6067</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.8874</v>
+        <v>-13.9541</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.66</v>
       </c>
       <c r="I107" t="n">
-        <v>1.2906</v>
+        <v>1.2727</v>
       </c>
       <c r="J107" t="n">
-        <v>29.6838</v>
+        <v>29.2721</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.52</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1248</v>
+        <v>1.0946</v>
       </c>
       <c r="J108" t="n">
-        <v>25.8704</v>
+        <v>25.1758</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.47</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0648</v>
+        <v>1.0269</v>
       </c>
       <c r="J109" t="n">
-        <v>24.4904</v>
+        <v>23.6187</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.43</v>
       </c>
       <c r="I110" t="n">
-        <v>1.012</v>
+        <v>0.9654</v>
       </c>
       <c r="J110" t="n">
-        <v>23.276</v>
+        <v>22.2042</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.05</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1004</v>
+        <v>0.1332</v>
       </c>
       <c r="J111" t="n">
-        <v>2.3092</v>
+        <v>3.0636</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.31</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6185</v>
+        <v>0.6014</v>
       </c>
       <c r="J112" t="n">
-        <v>22.266</v>
+        <v>21.6504</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.09</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2165</v>
+        <v>0.2259</v>
       </c>
       <c r="J113" t="n">
-        <v>7.794</v>
+        <v>8.132400000000001</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.01</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0321</v>
+        <v>0.0394</v>
       </c>
       <c r="J114" t="n">
-        <v>1.1556</v>
+        <v>1.4184</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.97</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0543</v>
+        <v>-0.0614</v>
       </c>
       <c r="J115" t="n">
-        <v>-1.9548</v>
+        <v>-2.2104</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2034</v>
+        <v>-0.2158</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.3224</v>
+        <v>-7.7688</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.23</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6684</v>
+        <v>0.6347</v>
       </c>
       <c r="J117" t="n">
-        <v>24.0624</v>
+        <v>22.8492</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.2</v>
       </c>
       <c r="I118" t="n">
-        <v>0.593</v>
+        <v>0.5678</v>
       </c>
       <c r="J118" t="n">
-        <v>21.348</v>
+        <v>20.4408</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.593</v>
+        <v>0.5678</v>
       </c>
       <c r="J119" t="n">
-        <v>21.348</v>
+        <v>20.4408</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.88</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.426</v>
+        <v>-0.4081</v>
       </c>
       <c r="J120" t="n">
-        <v>-15.336</v>
+        <v>-14.6916</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.84</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5359</v>
+        <v>-0.5074</v>
       </c>
       <c r="J121" t="n">
-        <v>-19.2924</v>
+        <v>-18.2664</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.58</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7067</v>
+        <v>0.7029</v>
       </c>
       <c r="J122" t="n">
-        <v>19.0809</v>
+        <v>18.9783</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.454</v>
+        <v>0.466</v>
       </c>
       <c r="J123" t="n">
-        <v>12.258</v>
+        <v>12.582</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.27</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3623</v>
+        <v>0.3781</v>
       </c>
       <c r="J124" t="n">
-        <v>9.7821</v>
+        <v>10.2087</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0202</v>
+        <v>-0.0156</v>
       </c>
       <c r="J125" t="n">
-        <v>-0.5454</v>
+        <v>-0.4212</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.88</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.1787</v>
+        <v>-0.187</v>
       </c>
       <c r="J126" t="n">
-        <v>-4.8249</v>
+        <v>-5.049</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.56</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8426</v>
+        <v>0.8005</v>
       </c>
       <c r="J127" t="n">
-        <v>22.7502</v>
+        <v>21.6135</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.21</v>
       </c>
       <c r="I128" t="n">
-        <v>0.374</v>
+        <v>0.3713</v>
       </c>
       <c r="J128" t="n">
-        <v>10.098</v>
+        <v>10.0251</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.79</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2388</v>
+        <v>-0.2544</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.4476</v>
+        <v>-6.8688</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.55</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4658</v>
+        <v>-0.4735</v>
       </c>
       <c r="J130" t="n">
-        <v>-12.5766</v>
+        <v>-12.7845</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.47</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5381</v>
+        <v>-0.5417999999999999</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.5287</v>
+        <v>-14.6286</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.05</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1867</v>
+        <v>0.1824</v>
       </c>
       <c r="J132" t="n">
-        <v>5.0409</v>
+        <v>4.9248</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.01</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0788</v>
+        <v>0.0731</v>
       </c>
       <c r="J133" t="n">
-        <v>2.1276</v>
+        <v>1.9737</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.93</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0835</v>
+        <v>-0.0989</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.2545</v>
+        <v>-2.6703</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.73</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.288</v>
+        <v>-0.3045</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.776</v>
+        <v>-8.221500000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.5</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.503</v>
+        <v>-0.51</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.581</v>
+        <v>-13.77</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.46</v>
       </c>
       <c r="I137" t="n">
-        <v>1.0714</v>
+        <v>1.0301</v>
       </c>
       <c r="J137" t="n">
-        <v>28.9278</v>
+        <v>27.8127</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.36</v>
       </c>
       <c r="I138" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.855</v>
       </c>
       <c r="J138" t="n">
-        <v>24.4269</v>
+        <v>23.085</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.25</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6624</v>
+        <v>0.6402</v>
       </c>
       <c r="J139" t="n">
-        <v>17.8848</v>
+        <v>17.2854</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.6391</v>
+        <v>0.6194</v>
       </c>
       <c r="J140" t="n">
-        <v>17.2557</v>
+        <v>16.7238</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.15</v>
       </c>
       <c r="I141" t="n">
-        <v>0.4168</v>
+        <v>0.4196</v>
       </c>
       <c r="J141" t="n">
-        <v>11.2536</v>
+        <v>11.3292</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.15</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3621</v>
+        <v>0.3587</v>
       </c>
       <c r="J142" t="n">
-        <v>10.863</v>
+        <v>10.761</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.04</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1283</v>
+        <v>0.1334</v>
       </c>
       <c r="J143" t="n">
-        <v>3.849</v>
+        <v>4.002</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.98</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0318</v>
+        <v>-0.0396</v>
       </c>
       <c r="J144" t="n">
-        <v>-0.954</v>
+        <v>-1.188</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.96</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0591</v>
+        <v>-0.0694</v>
       </c>
       <c r="J145" t="n">
-        <v>-1.773</v>
+        <v>-2.082</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.6</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4234</v>
+        <v>-0.4326</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.702</v>
+        <v>-12.978</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.46</v>
       </c>
       <c r="I147" t="n">
-        <v>1.1171</v>
+        <v>1.0726</v>
       </c>
       <c r="J147" t="n">
-        <v>33.513</v>
+        <v>32.178</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.2</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5837</v>
+        <v>0.5613</v>
       </c>
       <c r="J148" t="n">
-        <v>17.511</v>
+        <v>16.839</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.09</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2961</v>
+        <v>0.299</v>
       </c>
       <c r="J149" t="n">
-        <v>8.882999999999999</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.88</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4338</v>
+        <v>-0.4136</v>
       </c>
       <c r="J150" t="n">
-        <v>-13.014</v>
+        <v>-12.408</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.86</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4894</v>
+        <v>-0.464</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.682</v>
+        <v>-13.92</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.29</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5903</v>
+        <v>0.5746</v>
       </c>
       <c r="J152" t="n">
-        <v>16.5284</v>
+        <v>16.0888</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1783</v>
+        <v>0.1878</v>
       </c>
       <c r="J153" t="n">
-        <v>4.9924</v>
+        <v>5.2584</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.06</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1567</v>
+        <v>0.1665</v>
       </c>
       <c r="J154" t="n">
-        <v>4.3876</v>
+        <v>4.662</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0018</v>
+        <v>-0.0014</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.0504</v>
+        <v>-0.0392</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.71</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3296</v>
+        <v>-0.3407</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.2288</v>
+        <v>-9.5396</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.2</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5800999999999999</v>
+        <v>0.5588</v>
       </c>
       <c r="J157" t="n">
-        <v>16.2428</v>
+        <v>15.6464</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.19</v>
       </c>
       <c r="I158" t="n">
-        <v>0.555</v>
+        <v>0.5364</v>
       </c>
       <c r="J158" t="n">
-        <v>15.54</v>
+        <v>15.0192</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.16</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4788</v>
+        <v>0.4677</v>
       </c>
       <c r="J159" t="n">
-        <v>13.4064</v>
+        <v>13.0956</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.14</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4271</v>
+        <v>0.4207</v>
       </c>
       <c r="J160" t="n">
-        <v>11.9588</v>
+        <v>11.7796</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4927</v>
+        <v>-0.4663</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.7956</v>
+        <v>-13.0564</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.28</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7748</v>
+        <v>0.7313</v>
       </c>
       <c r="J162" t="n">
-        <v>20.9196</v>
+        <v>19.7451</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.13</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4006</v>
+        <v>0.3966</v>
       </c>
       <c r="J163" t="n">
-        <v>10.8162</v>
+        <v>10.7082</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.11</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3483</v>
+        <v>0.3482</v>
       </c>
       <c r="J164" t="n">
-        <v>9.4041</v>
+        <v>9.401400000000001</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.08</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2651</v>
+        <v>0.2706</v>
       </c>
       <c r="J165" t="n">
-        <v>7.1577</v>
+        <v>7.3062</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.96</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1941</v>
+        <v>-0.1893</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.2407</v>
+        <v>-5.1111</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.32</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6651</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="J167" t="n">
-        <v>17.9577</v>
+        <v>17.2422</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.04</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1228</v>
+        <v>0.1295</v>
       </c>
       <c r="J168" t="n">
-        <v>3.3156</v>
+        <v>3.4965</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0776</v>
       </c>
       <c r="J169" t="n">
-        <v>1.944</v>
+        <v>2.0952</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2049</v>
+        <v>-0.2193</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.5323</v>
+        <v>-5.9211</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.63</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3982</v>
+        <v>-0.4081</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.7514</v>
+        <v>-11.0187</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.66</v>
       </c>
       <c r="I172" t="n">
-        <v>1.3289</v>
+        <v>1.3064</v>
       </c>
       <c r="J172" t="n">
-        <v>31.8936</v>
+        <v>31.3536</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.53</v>
       </c>
       <c r="I173" t="n">
-        <v>1.1678</v>
+        <v>1.1347</v>
       </c>
       <c r="J173" t="n">
-        <v>28.0272</v>
+        <v>27.2328</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.37</v>
       </c>
       <c r="I174" t="n">
-        <v>0.9358</v>
+        <v>0.8815</v>
       </c>
       <c r="J174" t="n">
-        <v>22.4592</v>
+        <v>21.156</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.19</v>
       </c>
       <c r="I175" t="n">
-        <v>0.5275</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="J175" t="n">
-        <v>12.66</v>
+        <v>12.4224</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.5</v>
       </c>
       <c r="I176" t="n">
-        <v>-1.398</v>
+        <v>-1.2512</v>
       </c>
       <c r="J176" t="n">
-        <v>-33.552</v>
+        <v>-30.0288</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.35</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7395</v>
+        <v>0.702</v>
       </c>
       <c r="J177" t="n">
-        <v>17.748</v>
+        <v>16.848</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.17</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4099</v>
+        <v>0.4016</v>
       </c>
       <c r="J178" t="n">
-        <v>9.8376</v>
+        <v>9.638400000000001</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.92</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1042</v>
+        <v>-0.1179</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.5008</v>
+        <v>-2.8296</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.67</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3554</v>
+        <v>-0.3679</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.5296</v>
+        <v>-8.829599999999999</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.5</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5118</v>
+        <v>-0.5169</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.2832</v>
+        <v>-12.4056</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.97</v>
       </c>
       <c r="I182" t="n">
-        <v>1.636</v>
+        <v>1.639</v>
       </c>
       <c r="J182" t="n">
-        <v>31.084</v>
+        <v>31.141</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.6</v>
       </c>
       <c r="I183" t="n">
-        <v>1.2133</v>
+        <v>1.1913</v>
       </c>
       <c r="J183" t="n">
-        <v>23.0527</v>
+        <v>22.6347</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.6</v>
       </c>
       <c r="I184" t="n">
-        <v>1.2133</v>
+        <v>1.1913</v>
       </c>
       <c r="J184" t="n">
-        <v>23.0527</v>
+        <v>22.6347</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.2</v>
       </c>
       <c r="I185" t="n">
-        <v>0.5049</v>
+        <v>0.507</v>
       </c>
       <c r="J185" t="n">
-        <v>9.5931</v>
+        <v>9.632999999999999</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.99</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1643</v>
+        <v>-0.1361</v>
       </c>
       <c r="J186" t="n">
-        <v>-3.1217</v>
+        <v>-2.5859</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.8</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1636</v>
+        <v>-0.1938</v>
       </c>
       <c r="J187" t="n">
-        <v>-3.1084</v>
+        <v>-3.6822</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.75</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2197</v>
+        <v>-0.2477</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.1743</v>
+        <v>-4.7063</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.62</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3526</v>
+        <v>-0.3743</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.6994</v>
+        <v>-7.1117</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.48</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4799</v>
+        <v>-0.4946</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.1181</v>
+        <v>-9.397399999999999</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.25</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.7016</v>
+        <v>-0.6984</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.3304</v>
+        <v>-13.2696</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.23</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3715</v>
+        <v>0.3747</v>
       </c>
       <c r="J192" t="n">
-        <v>13.374</v>
+        <v>13.4892</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.14</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2443</v>
+        <v>0.2533</v>
       </c>
       <c r="J193" t="n">
-        <v>8.7948</v>
+        <v>9.1188</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.0906</v>
+        <v>-0.1009</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.2616</v>
+        <v>-3.6324</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.91</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1257</v>
+        <v>-0.1375</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.5252</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.9</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1369</v>
+        <v>-0.149</v>
       </c>
       <c r="J196" t="n">
-        <v>-4.9284</v>
+        <v>-5.364</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.37</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4947</v>
+        <v>0.5013</v>
       </c>
       <c r="J197" t="n">
-        <v>17.8092</v>
+        <v>18.0468</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.36</v>
       </c>
       <c r="I198" t="n">
-        <v>0.4831</v>
+        <v>0.4903</v>
       </c>
       <c r="J198" t="n">
-        <v>17.3916</v>
+        <v>17.6508</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.13</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2009</v>
+        <v>0.2172</v>
       </c>
       <c r="J199" t="n">
-        <v>7.2324</v>
+        <v>7.8192</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.05</v>
       </c>
       <c r="I200" t="n">
-        <v>0.0867</v>
+        <v>0.1006</v>
       </c>
       <c r="J200" t="n">
-        <v>3.1212</v>
+        <v>3.6216</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.68</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3671</v>
+        <v>-0.3754</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.2156</v>
+        <v>-13.5144</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.71</v>
       </c>
       <c r="I202" t="n">
-        <v>1.3746</v>
+        <v>1.3574</v>
       </c>
       <c r="J202" t="n">
-        <v>32.9904</v>
+        <v>32.5776</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.3</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7722</v>
+        <v>0.7383999999999999</v>
       </c>
       <c r="J203" t="n">
-        <v>18.5328</v>
+        <v>17.7216</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.28</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7279</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="J204" t="n">
-        <v>17.4696</v>
+        <v>16.7784</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.25</v>
       </c>
       <c r="I205" t="n">
-        <v>0.6594</v>
+        <v>0.6381</v>
       </c>
       <c r="J205" t="n">
-        <v>15.8256</v>
+        <v>15.3144</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.0747</v>
+        <v>-0.0518</v>
       </c>
       <c r="J206" t="n">
-        <v>-1.7928</v>
+        <v>-1.2432</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.1</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2647</v>
+        <v>0.2658</v>
       </c>
       <c r="J207" t="n">
-        <v>6.3528</v>
+        <v>6.3792</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0114</v>
+        <v>0.0081</v>
       </c>
       <c r="J208" t="n">
-        <v>0.2736</v>
+        <v>0.1944</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.96</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0582</v>
+        <v>-0.0687</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.3968</v>
+        <v>-1.6488</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.82</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2112</v>
+        <v>-0.2264</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.0688</v>
+        <v>-5.4336</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2313</v>
+        <v>-0.2464</v>
       </c>
       <c r="J211" t="n">
-        <v>-5.5512</v>
+        <v>-5.9136</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.32</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6479</v>
+        <v>0.6259</v>
       </c>
       <c r="J212" t="n">
-        <v>18.1412</v>
+        <v>17.5252</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.14</v>
       </c>
       <c r="I213" t="n">
-        <v>0.323</v>
+        <v>0.326</v>
       </c>
       <c r="J213" t="n">
-        <v>9.044</v>
+        <v>9.128</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.96</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0733</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.7976</v>
+        <v>-2.0524</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.85</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1891</v>
+        <v>-0.2024</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.2948</v>
+        <v>-5.6672</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.78</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2601</v>
+        <v>-0.273</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.2828</v>
+        <v>-7.644</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.38</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0034</v>
+        <v>0.9402</v>
       </c>
       <c r="J217" t="n">
-        <v>28.0952</v>
+        <v>26.3256</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.27</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7574</v>
+        <v>0.7149</v>
       </c>
       <c r="J218" t="n">
-        <v>21.2072</v>
+        <v>20.0172</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0214</v>
+        <v>-0.0146</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.5992</v>
+        <v>-0.4088</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.97</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1543</v>
+        <v>-0.1522</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.3204</v>
+        <v>-4.2616</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.85</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.4879</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.4368</v>
+        <v>-13.6612</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.14</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3411</v>
+        <v>0.3393</v>
       </c>
       <c r="J222" t="n">
-        <v>8.868600000000001</v>
+        <v>8.8218</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.03</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1024</v>
+        <v>0.1076</v>
       </c>
       <c r="J223" t="n">
-        <v>2.6624</v>
+        <v>2.7976</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.89</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1397</v>
+        <v>-0.1539</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.6322</v>
+        <v>-4.0014</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.85</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1821</v>
+        <v>-0.1969</v>
       </c>
       <c r="J225" t="n">
-        <v>-4.7346</v>
+        <v>-5.1194</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.84</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1925</v>
+        <v>-0.2073</v>
       </c>
       <c r="J226" t="n">
-        <v>-5.005</v>
+        <v>-5.3898</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.57</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2377</v>
+        <v>1.2058</v>
       </c>
       <c r="J227" t="n">
-        <v>32.1802</v>
+        <v>31.3508</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.17</v>
       </c>
       <c r="I228" t="n">
-        <v>0.492</v>
+        <v>0.4824</v>
       </c>
       <c r="J228" t="n">
-        <v>12.792</v>
+        <v>12.5424</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.13</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3903</v>
+        <v>0.3896</v>
       </c>
       <c r="J229" t="n">
-        <v>10.1478</v>
+        <v>10.1296</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>0.0539</v>
+        <v>0.0722</v>
       </c>
       <c r="J230" t="n">
-        <v>1.4014</v>
+        <v>1.8772</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.98</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1381</v>
+        <v>-0.1302</v>
       </c>
       <c r="J231" t="n">
-        <v>-3.5906</v>
+        <v>-3.3852</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.2</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4453</v>
+        <v>0.4386</v>
       </c>
       <c r="J232" t="n">
-        <v>12.4684</v>
+        <v>12.2808</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.06</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1663</v>
+        <v>0.1734</v>
       </c>
       <c r="J233" t="n">
-        <v>4.6564</v>
+        <v>4.8552</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.93</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.098</v>
+        <v>-0.1099</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.744</v>
+        <v>-3.0772</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1209</v>
+        <v>-0.1337</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.3852</v>
+        <v>-3.7436</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.8</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2367</v>
+        <v>-0.2506</v>
       </c>
       <c r="J236" t="n">
-        <v>-6.6276</v>
+        <v>-7.0168</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.35</v>
       </c>
       <c r="I237" t="n">
-        <v>0.9576</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="J237" t="n">
-        <v>26.8128</v>
+        <v>24.9368</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.29</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8181</v>
+        <v>0.7659</v>
       </c>
       <c r="J238" t="n">
-        <v>22.9068</v>
+        <v>21.4452</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.18</v>
       </c>
       <c r="I239" t="n">
-        <v>0.5439000000000001</v>
+        <v>0.5235</v>
       </c>
       <c r="J239" t="n">
-        <v>15.2292</v>
+        <v>14.658</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.95</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2144</v>
+        <v>-0.2121</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.0032</v>
+        <v>-5.9388</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.55</v>
       </c>
       <c r="I241" t="n">
-        <v>-1.2487</v>
+        <v>-1.129</v>
       </c>
       <c r="J241" t="n">
-        <v>-34.9636</v>
+        <v>-31.612</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1</v>
       </c>
       <c r="I242" t="n">
-        <v>0.1393</v>
+        <v>0.1022</v>
       </c>
       <c r="J242" t="n">
-        <v>3.0646</v>
+        <v>2.2484</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.74</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.2529</v>
+        <v>-0.2755</v>
       </c>
       <c r="J243" t="n">
-        <v>-5.5638</v>
+        <v>-6.061</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.68</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3108</v>
+        <v>-0.3316</v>
       </c>
       <c r="J244" t="n">
-        <v>-6.8376</v>
+        <v>-7.2952</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.62</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3642</v>
+        <v>-0.3831</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.0124</v>
+        <v>-8.4282</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.26</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.6977</v>
       </c>
       <c r="J246" t="n">
-        <v>-15.4462</v>
+        <v>-15.3494</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.78</v>
       </c>
       <c r="I247" t="n">
-        <v>1.4307</v>
+        <v>1.4213</v>
       </c>
       <c r="J247" t="n">
-        <v>31.4754</v>
+        <v>31.2686</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.66</v>
       </c>
       <c r="I248" t="n">
-        <v>1.291</v>
+        <v>1.273</v>
       </c>
       <c r="J248" t="n">
-        <v>28.402</v>
+        <v>28.006</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.63</v>
       </c>
       <c r="I249" t="n">
-        <v>1.2557</v>
+        <v>1.2353</v>
       </c>
       <c r="J249" t="n">
-        <v>27.6254</v>
+        <v>27.1766</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.05</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1008</v>
+        <v>0.1335</v>
       </c>
       <c r="J250" t="n">
-        <v>2.2176</v>
+        <v>2.937</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>1</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.0999</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="J251" t="n">
-        <v>-2.1978</v>
+        <v>-1.529</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.43</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0702</v>
+        <v>1.0203</v>
       </c>
       <c r="J252" t="n">
-        <v>32.106</v>
+        <v>30.609</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.17</v>
       </c>
       <c r="I253" t="n">
-        <v>0.5014</v>
+        <v>0.4888</v>
       </c>
       <c r="J253" t="n">
-        <v>15.042</v>
+        <v>14.664</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.08</v>
       </c>
       <c r="I254" t="n">
-        <v>0.263</v>
+        <v>0.2692</v>
       </c>
       <c r="J254" t="n">
-        <v>7.89</v>
+        <v>8.076000000000001</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1618</v>
+        <v>-0.1574</v>
       </c>
       <c r="J255" t="n">
-        <v>-4.854</v>
+        <v>-4.722</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.96</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1967</v>
+        <v>-0.1912</v>
       </c>
       <c r="J256" t="n">
-        <v>-5.901</v>
+        <v>-5.736</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.25</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5291</v>
+        <v>0.5171</v>
       </c>
       <c r="J257" t="n">
-        <v>15.873</v>
+        <v>15.513</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.14</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3257</v>
+        <v>0.328</v>
       </c>
       <c r="J258" t="n">
-        <v>9.771000000000001</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.07</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1836</v>
+        <v>0.1916</v>
       </c>
       <c r="J259" t="n">
-        <v>5.508</v>
+        <v>5.748</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.83</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2086</v>
+        <v>-0.2222</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.258</v>
+        <v>-6.666</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.71</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3267</v>
+        <v>-0.3385</v>
       </c>
       <c r="J261" t="n">
-        <v>-9.801</v>
+        <v>-10.155</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>2</v>
       </c>
       <c r="I262" t="n">
-        <v>1.6512</v>
+        <v>1.6578</v>
       </c>
       <c r="J262" t="n">
-        <v>28.0704</v>
+        <v>28.1826</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.79</v>
       </c>
       <c r="I263" t="n">
-        <v>1.4184</v>
+        <v>1.4126</v>
       </c>
       <c r="J263" t="n">
-        <v>24.1128</v>
+        <v>24.0142</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.49</v>
       </c>
       <c r="I264" t="n">
-        <v>1.078</v>
+        <v>1.0452</v>
       </c>
       <c r="J264" t="n">
-        <v>18.326</v>
+        <v>17.7684</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.28</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6792</v>
+        <v>0.6654</v>
       </c>
       <c r="J265" t="n">
-        <v>11.5464</v>
+        <v>11.3118</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.22</v>
       </c>
       <c r="I266" t="n">
-        <v>0.5372</v>
+        <v>0.5392</v>
       </c>
       <c r="J266" t="n">
-        <v>9.132400000000001</v>
+        <v>9.166399999999999</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.18</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6867</v>
+        <v>0.611</v>
       </c>
       <c r="J267" t="n">
-        <v>11.6739</v>
+        <v>10.387</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.64</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.3348</v>
+        <v>-0.3572</v>
       </c>
       <c r="J268" t="n">
-        <v>-5.6916</v>
+        <v>-6.0724</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.42</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.5382</v>
+        <v>-0.5485</v>
       </c>
       <c r="J269" t="n">
-        <v>-9.1494</v>
+        <v>-9.3245</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.35</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.6055</v>
+        <v>-0.6105</v>
       </c>
       <c r="J270" t="n">
-        <v>-10.2935</v>
+        <v>-10.3785</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.34</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6152</v>
+        <v>-0.6194</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.4584</v>
+        <v>-10.5298</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.4</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0273</v>
+        <v>0.969</v>
       </c>
       <c r="J272" t="n">
-        <v>36.9828</v>
+        <v>34.884</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.36</v>
       </c>
       <c r="I273" t="n">
-        <v>0.9553</v>
+        <v>0.8925</v>
       </c>
       <c r="J273" t="n">
-        <v>34.3908</v>
+        <v>32.13</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.08</v>
       </c>
       <c r="I274" t="n">
-        <v>0.263</v>
+        <v>0.2692</v>
       </c>
       <c r="J274" t="n">
-        <v>9.468</v>
+        <v>9.6912</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.03</v>
       </c>
       <c r="I275" t="n">
-        <v>0.104</v>
+        <v>0.1177</v>
       </c>
       <c r="J275" t="n">
-        <v>3.744</v>
+        <v>4.2372</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.74</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.8079</v>
+        <v>-0.746</v>
       </c>
       <c r="J276" t="n">
-        <v>-29.0844</v>
+        <v>-26.856</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.21</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4725</v>
+        <v>0.4621</v>
       </c>
       <c r="J277" t="n">
-        <v>17.01</v>
+        <v>16.6356</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.16</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3781</v>
+        <v>0.3744</v>
       </c>
       <c r="J278" t="n">
-        <v>13.6116</v>
+        <v>13.4784</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.96</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0599</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J279" t="n">
-        <v>-2.1564</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.84</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1932</v>
+        <v>-0.2079</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.9552</v>
+        <v>-7.4844</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.61</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4153</v>
+        <v>-0.4247</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.9508</v>
+        <v>-15.2892</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.17</v>
       </c>
       <c r="I282" t="n">
-        <v>0.5538</v>
+        <v>0.5252</v>
       </c>
       <c r="J282" t="n">
-        <v>16.614</v>
+        <v>15.756</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.14</v>
       </c>
       <c r="I283" t="n">
-        <v>0.472</v>
+        <v>0.4518</v>
       </c>
       <c r="J283" t="n">
-        <v>14.16</v>
+        <v>13.554</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.9</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3414</v>
+        <v>-0.3368</v>
       </c>
       <c r="J284" t="n">
-        <v>-10.242</v>
+        <v>-10.104</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.86</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4534</v>
+        <v>-0.4389</v>
       </c>
       <c r="J285" t="n">
-        <v>-13.602</v>
+        <v>-13.167</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.8</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6132</v>
+        <v>-0.5819</v>
       </c>
       <c r="J286" t="n">
-        <v>-18.396</v>
+        <v>-17.457</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.63</v>
       </c>
       <c r="I287" t="n">
-        <v>1.052</v>
+        <v>1.0183</v>
       </c>
       <c r="J287" t="n">
-        <v>31.56</v>
+        <v>30.549</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.21</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4184</v>
+        <v>0.4226</v>
       </c>
       <c r="J288" t="n">
-        <v>12.552</v>
+        <v>12.678</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.18</v>
       </c>
       <c r="I289" t="n">
-        <v>0.3665</v>
+        <v>0.3738</v>
       </c>
       <c r="J289" t="n">
-        <v>10.995</v>
+        <v>11.214</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.93</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1165</v>
+        <v>-0.1243</v>
       </c>
       <c r="J290" t="n">
-        <v>-3.495</v>
+        <v>-3.729</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.83</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2254</v>
+        <v>-0.2353</v>
       </c>
       <c r="J291" t="n">
-        <v>-6.762</v>
+        <v>-7.059</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.48</v>
       </c>
       <c r="I292" t="n">
-        <v>1.1187</v>
+        <v>1.0791</v>
       </c>
       <c r="J292" t="n">
-        <v>31.3236</v>
+        <v>30.2148</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.23</v>
       </c>
       <c r="I293" t="n">
-        <v>0.633</v>
+        <v>0.6103</v>
       </c>
       <c r="J293" t="n">
-        <v>17.724</v>
+        <v>17.0884</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.14</v>
       </c>
       <c r="I294" t="n">
-        <v>0.4136</v>
+        <v>0.4117</v>
       </c>
       <c r="J294" t="n">
-        <v>11.5808</v>
+        <v>11.5276</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.13</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3873</v>
+        <v>0.3876</v>
       </c>
       <c r="J295" t="n">
-        <v>10.8444</v>
+        <v>10.8528</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.96</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.214</v>
+        <v>-0.2032</v>
       </c>
       <c r="J296" t="n">
-        <v>-5.992</v>
+        <v>-5.6896</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.05</v>
       </c>
       <c r="I297" t="n">
-        <v>0.1653</v>
+        <v>0.1667</v>
       </c>
       <c r="J297" t="n">
-        <v>4.6284</v>
+        <v>4.6676</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.02</v>
       </c>
       <c r="I298" t="n">
-        <v>0.089</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J298" t="n">
-        <v>2.492</v>
+        <v>2.5172</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.9</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1244</v>
+        <v>-0.1394</v>
       </c>
       <c r="J299" t="n">
-        <v>-3.4832</v>
+        <v>-3.9032</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.82</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2071</v>
+        <v>-0.2232</v>
       </c>
       <c r="J300" t="n">
-        <v>-5.7988</v>
+        <v>-6.2496</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.72</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3053</v>
+        <v>-0.3198</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.548400000000001</v>
+        <v>-8.9544</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>2.27</v>
       </c>
       <c r="I302" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J302" t="n">
-        <v>34.8422</v>
+        <v>36.8068</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.68</v>
       </c>
       <c r="I303" t="n">
-        <v>1.3026</v>
+        <v>1.2876</v>
       </c>
       <c r="J303" t="n">
-        <v>24.7494</v>
+        <v>24.4644</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.29</v>
       </c>
       <c r="I304" t="n">
-        <v>0.7141</v>
+        <v>0.694</v>
       </c>
       <c r="J304" t="n">
-        <v>13.5679</v>
+        <v>13.186</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.18</v>
       </c>
       <c r="I305" t="n">
-        <v>0.45</v>
+        <v>0.4586</v>
       </c>
       <c r="J305" t="n">
-        <v>8.550000000000001</v>
+        <v>8.7134</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.06</v>
       </c>
       <c r="I306" t="n">
-        <v>0.1181</v>
+        <v>0.1534</v>
       </c>
       <c r="J306" t="n">
-        <v>2.2439</v>
+        <v>2.9146</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.89</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.0575</v>
+        <v>-0.0897</v>
       </c>
       <c r="J307" t="n">
-        <v>-1.0925</v>
+        <v>-1.7043</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.62</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.3538</v>
+        <v>-0.3752</v>
       </c>
       <c r="J308" t="n">
-        <v>-6.7222</v>
+        <v>-7.1288</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.53</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4342</v>
+        <v>-0.4517</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.2498</v>
+        <v>-8.5823</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.52</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4435</v>
+        <v>-0.4604</v>
       </c>
       <c r="J310" t="n">
-        <v>-8.426500000000001</v>
+        <v>-8.7476</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.37</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.5928</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.1378</v>
+        <v>-11.2632</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4597/event_4597_evp_summary.xlsx
+++ b/database/event/4597/event_4597_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.1001</v>
+        <v>6.9159</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7574</v>
+        <v>1.7118</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6079</v>
+        <v>2.5447</v>
       </c>
       <c r="E2" t="n">
-        <v>7.1001</v>
+        <v>6.9159</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3948</v>
+        <v>3.3075</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7053</v>
+        <v>3.6084</v>
       </c>
       <c r="H2" t="n">
-        <v>6.3066</v>
+        <v>5.975</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4055</v>
+        <v>3.3548</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7053</v>
+        <v>3.6084</v>
       </c>
       <c r="K2" t="n">
         <v>108</v>
@@ -529,7 +529,7 @@
         <v>160</v>
       </c>
       <c r="M2" t="n">
-        <v>7.110799999999999</v>
+        <v>6.963200000000001</v>
       </c>
       <c r="N2" t="n">
         <v>268</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.783</v>
+        <v>6.6074</v>
       </c>
       <c r="C3" t="n">
-        <v>1.679</v>
+        <v>1.6355</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4636</v>
+        <v>2.4042</v>
       </c>
       <c r="E3" t="n">
-        <v>6.783</v>
+        <v>6.6074</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1842</v>
+        <v>3.111</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5988</v>
+        <v>3.4964</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6116</v>
+        <v>5.2375</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0302</v>
+        <v>2.9407</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5988</v>
+        <v>3.4964</v>
       </c>
       <c r="K3" t="n">
         <v>108</v>
@@ -575,7 +575,7 @@
         <v>160</v>
       </c>
       <c r="M3" t="n">
-        <v>6.629</v>
+        <v>6.4371</v>
       </c>
       <c r="N3" t="n">
         <v>268</v>
@@ -584,185 +584,185 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4503</v>
+        <v>4.5436</v>
       </c>
       <c r="C4" t="n">
-        <v>1.1016</v>
+        <v>1.1246</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4017</v>
+        <v>1.464</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4503</v>
+        <v>4.5436</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9572</v>
+        <v>2.4691</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4931</v>
+        <v>2.0745</v>
       </c>
       <c r="H4" t="n">
-        <v>8.1622</v>
+        <v>2.8276</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4075</v>
+        <v>1.5876</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4931</v>
+        <v>2.0745</v>
       </c>
       <c r="K4" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="L4" t="n">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9006</v>
+        <v>3.6621</v>
       </c>
       <c r="N4" t="n">
-        <v>205</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4418</v>
+        <v>4.2466</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0995</v>
+        <v>1.0511</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3978</v>
+        <v>1.3287</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4418</v>
+        <v>4.2466</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4257</v>
+        <v>3.8005</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0161</v>
+        <v>0.4461</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1091</v>
+        <v>7.8261</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6789</v>
+        <v>4.3941</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0161</v>
+        <v>0.4461</v>
       </c>
       <c r="K5" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="L5" t="n">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="M5" t="n">
-        <v>3.695</v>
+        <v>4.8402</v>
       </c>
       <c r="N5" t="n">
-        <v>268</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9055</v>
+        <v>3.8256</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9667</v>
+        <v>0.9469</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1537</v>
+        <v>1.137</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9055</v>
+        <v>3.8256</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7746</v>
+        <v>0.5589</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1309</v>
+        <v>3.2667</v>
       </c>
       <c r="H6" t="n">
-        <v>7.5596</v>
+        <v>0.5589</v>
       </c>
       <c r="I6" t="n">
-        <v>4.0821</v>
+        <v>0.3138</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1309</v>
+        <v>3.2667</v>
       </c>
       <c r="K6" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="L6" t="n">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="M6" t="n">
-        <v>4.212999999999999</v>
+        <v>3.5805</v>
       </c>
       <c r="N6" t="n">
-        <v>205</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8192</v>
+        <v>3.6949</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9453</v>
+        <v>0.9146</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1144</v>
+        <v>1.0774</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8192</v>
+        <v>3.6949</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5545</v>
+        <v>3.6734</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2647</v>
+        <v>0.0215</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5545</v>
+        <v>7.3488</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2994</v>
+        <v>4.1261</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2647</v>
+        <v>0.0215</v>
       </c>
       <c r="K7" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="L7" t="n">
-        <v>160</v>
+        <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5641</v>
+        <v>4.1476</v>
       </c>
       <c r="N7" t="n">
-        <v>268</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8165</v>
+        <v>3.6807</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9447</v>
+        <v>0.9111</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1131</v>
+        <v>1.0709</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8165</v>
+        <v>3.6807</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2054</v>
+        <v>3.1358</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6111</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>5.6818</v>
+        <v>5.3307</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0681</v>
+        <v>2.993</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6111</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>126</v>
@@ -805,7 +805,7 @@
         <v>79</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6792</v>
+        <v>3.5379</v>
       </c>
       <c r="N8" t="n">
         <v>205</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7071</v>
+        <v>3.5668</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9176</v>
+        <v>0.8829</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0633</v>
+        <v>1.0191</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7071</v>
+        <v>3.5668</v>
       </c>
       <c r="F9" t="n">
-        <v>3.6423</v>
+        <v>3.5333</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0648</v>
+        <v>0.0335</v>
       </c>
       <c r="H9" t="n">
-        <v>7.1231</v>
+        <v>6.823</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8464</v>
+        <v>3.8309</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0648</v>
+        <v>0.0335</v>
       </c>
       <c r="K9" t="n">
         <v>150</v>
@@ -851,7 +851,7 @@
         <v>192</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9112</v>
+        <v>3.8644</v>
       </c>
       <c r="N9" t="n">
         <v>342</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.545</v>
+        <v>3.4824</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.862</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9896</v>
+        <v>0.9806</v>
       </c>
       <c r="E10" t="n">
-        <v>3.545</v>
+        <v>3.4824</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4817</v>
+        <v>3.4073</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0633</v>
+        <v>0.0751</v>
       </c>
       <c r="H10" t="n">
-        <v>6.5932</v>
+        <v>6.35</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5603</v>
+        <v>3.5653</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0633</v>
+        <v>0.0751</v>
       </c>
       <c r="K10" t="n">
         <v>150</v>
@@ -897,7 +897,7 @@
         <v>192</v>
       </c>
       <c r="M10" t="n">
-        <v>3.6236</v>
+        <v>3.6404</v>
       </c>
       <c r="N10" t="n">
         <v>342</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5114</v>
+        <v>3.4061</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8692</v>
+        <v>0.8431</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9459</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5114</v>
+        <v>3.4061</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5492</v>
+        <v>2.5468</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.8593</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5165</v>
+        <v>3.1193</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8989</v>
+        <v>1.7514</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.8593</v>
       </c>
       <c r="K11" t="n">
         <v>150</v>
@@ -943,7 +943,7 @@
         <v>192</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8611</v>
+        <v>2.6107</v>
       </c>
       <c r="N11" t="n">
         <v>342</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.3897</v>
+        <v>3.3826</v>
       </c>
       <c r="C12" t="n">
-        <v>0.839</v>
+        <v>0.8373</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.9351</v>
       </c>
       <c r="E12" t="n">
-        <v>3.3897</v>
+        <v>3.3826</v>
       </c>
       <c r="F12" t="n">
-        <v>3.0426</v>
+        <v>3.005</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3471</v>
+        <v>0.3776</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1445</v>
+        <v>4.8393</v>
       </c>
       <c r="I12" t="n">
-        <v>2.778</v>
+        <v>2.7171</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3471</v>
+        <v>0.3776</v>
       </c>
       <c r="K12" t="n">
         <v>150</v>
@@ -989,7 +989,7 @@
         <v>192</v>
       </c>
       <c r="M12" t="n">
-        <v>3.1251</v>
+        <v>3.0947</v>
       </c>
       <c r="N12" t="n">
         <v>342</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.2756</v>
+        <v>3.1829</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8108</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8669</v>
+        <v>0.8442</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2756</v>
+        <v>3.1829</v>
       </c>
       <c r="F13" t="n">
-        <v>3.2274</v>
+        <v>3.1632</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0482</v>
+        <v>0.0197</v>
       </c>
       <c r="H13" t="n">
-        <v>5.7542</v>
+        <v>5.4333</v>
       </c>
       <c r="I13" t="n">
-        <v>3.1072</v>
+        <v>3.0506</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0482</v>
+        <v>0.0197</v>
       </c>
       <c r="K13" t="n">
         <v>235</v>
@@ -1035,7 +1035,7 @@
         <v>47</v>
       </c>
       <c r="M13" t="n">
-        <v>3.1554</v>
+        <v>3.0703</v>
       </c>
       <c r="N13" t="n">
         <v>282</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8515</v>
+        <v>2.8324</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7058</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.6845</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8515</v>
+        <v>2.8324</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6489</v>
+        <v>3.557</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.7974</v>
+        <v>-0.7246</v>
       </c>
       <c r="H14" t="n">
-        <v>7.1447</v>
+        <v>6.9121</v>
       </c>
       <c r="I14" t="n">
-        <v>3.8581</v>
+        <v>3.8809</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.7974</v>
+        <v>-0.7246</v>
       </c>
       <c r="K14" t="n">
         <v>150</v>
@@ -1081,7 +1081,7 @@
         <v>192</v>
       </c>
       <c r="M14" t="n">
-        <v>3.0607</v>
+        <v>3.1563</v>
       </c>
       <c r="N14" t="n">
         <v>342</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3762</v>
+        <v>2.3164</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5734</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4575</v>
+        <v>0.4494</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3762</v>
+        <v>2.3164</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1671</v>
+        <v>2.1086</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2091</v>
+        <v>0.2078</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2558</v>
+        <v>2.1086</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2181</v>
+        <v>1.1839</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2091</v>
+        <v>0.2078</v>
       </c>
       <c r="K15" t="n">
         <v>235</v>
@@ -1127,7 +1127,7 @@
         <v>47</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4272</v>
+        <v>1.3917</v>
       </c>
       <c r="N15" t="n">
         <v>282</v>
@@ -1136,124 +1136,124 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sergej</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1651</v>
+        <v>2.1894</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5359</v>
+        <v>0.5419</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3614</v>
+        <v>0.3916</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1651</v>
+        <v>2.1894</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1651</v>
+        <v>3.0343</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.8449</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1651</v>
+        <v>4.9493</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1651</v>
+        <v>2.7789</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-0.8449</v>
       </c>
       <c r="K16" t="n">
-        <v>210</v>
+        <v>126</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1651</v>
+        <v>1.934</v>
       </c>
       <c r="N16" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.126</v>
+        <v>1.9924</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5262</v>
+        <v>0.4932</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3436</v>
+        <v>0.3018</v>
       </c>
       <c r="E17" t="n">
-        <v>2.126</v>
+        <v>1.9924</v>
       </c>
       <c r="F17" t="n">
-        <v>3.0145</v>
+        <v>1.9924</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8885</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>5.0519</v>
+        <v>1.9924</v>
       </c>
       <c r="I17" t="n">
-        <v>2.728</v>
+        <v>1.9924</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8885</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="L17" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8395</v>
+        <v>1.9924</v>
       </c>
       <c r="N17" t="n">
-        <v>205</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>sergej</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.0214</v>
+        <v>1.9768</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5003</v>
+        <v>0.4893</v>
       </c>
       <c r="D18" t="n">
-        <v>0.296</v>
+        <v>0.2947</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0214</v>
+        <v>1.9768</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0214</v>
+        <v>1.9768</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0214</v>
+        <v>1.9768</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0214</v>
+        <v>1.9768</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0214</v>
+        <v>1.9768</v>
       </c>
       <c r="N18" t="n">
         <v>210</v>
@@ -1274,47 +1274,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.008</v>
+        <v>1.8267</v>
       </c>
       <c r="C19" t="n">
-        <v>0.497</v>
+        <v>0.4522</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2899</v>
+        <v>0.2264</v>
       </c>
       <c r="E19" t="n">
-        <v>2.008</v>
+        <v>1.8267</v>
       </c>
       <c r="F19" t="n">
-        <v>2.008</v>
+        <v>1.8267</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>2.008</v>
+        <v>1.8267</v>
       </c>
       <c r="I19" t="n">
-        <v>2.008</v>
+        <v>1.8267</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.008</v>
+        <v>1.8267</v>
       </c>
       <c r="N19" t="n">
-        <v>143</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20">
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.8709</v>
+        <v>1.745</v>
       </c>
       <c r="C20" t="n">
-        <v>0.4631</v>
+        <v>0.4319</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2275</v>
+        <v>0.1891</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8709</v>
+        <v>1.745</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0091</v>
+        <v>0.9238</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8618</v>
+        <v>0.8212</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0091</v>
+        <v>0.9238</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5449000000000001</v>
+        <v>0.5187</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8618</v>
+        <v>0.8212</v>
       </c>
       <c r="K20" t="n">
         <v>126</v>
@@ -1357,7 +1357,7 @@
         <v>79</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4067</v>
+        <v>1.3399</v>
       </c>
       <c r="N20" t="n">
         <v>205</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.4772</v>
+        <v>1.664</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3656</v>
+        <v>0.4119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0482</v>
+        <v>0.1522</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4772</v>
+        <v>1.664</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8684</v>
+        <v>-1.6318</v>
       </c>
       <c r="G21" t="n">
-        <v>3.3456</v>
+        <v>3.2958</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8684</v>
+        <v>-1.6318</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0089</v>
+        <v>-0.9162</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3456</v>
+        <v>3.2958</v>
       </c>
       <c r="K21" t="n">
         <v>108</v>
@@ -1403,7 +1403,7 @@
         <v>160</v>
       </c>
       <c r="M21" t="n">
-        <v>2.3367</v>
+        <v>2.3796</v>
       </c>
       <c r="N21" t="n">
         <v>268</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.473</v>
+        <v>1.2357</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3646</v>
+        <v>0.3059</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0463</v>
+        <v>-0.0429</v>
       </c>
       <c r="E22" t="n">
-        <v>1.473</v>
+        <v>1.2357</v>
       </c>
       <c r="F22" t="n">
-        <v>1.473</v>
+        <v>1.2357</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.473</v>
+        <v>1.2357</v>
       </c>
       <c r="I22" t="n">
-        <v>1.473</v>
+        <v>1.2357</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.473</v>
+        <v>1.2357</v>
       </c>
       <c r="N22" t="n">
         <v>210</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.0436</v>
+        <v>0.9967</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2583</v>
+        <v>0.2467</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1491</v>
+        <v>-0.1517</v>
       </c>
       <c r="E23" t="n">
-        <v>1.0436</v>
+        <v>0.9967</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0436</v>
+        <v>0.9967</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0436</v>
+        <v>0.9967</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0436</v>
+        <v>0.9967</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0436</v>
+        <v>0.9967</v>
       </c>
       <c r="N23" t="n">
         <v>143</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9314</v>
+        <v>0.8459</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2305</v>
+        <v>0.2094</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2002</v>
+        <v>-0.2204</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9314</v>
+        <v>0.8459</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9314</v>
+        <v>0.8459</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9314</v>
+        <v>0.8459</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9314</v>
+        <v>0.8459</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9314</v>
+        <v>0.8459</v>
       </c>
       <c r="N24" t="n">
         <v>101</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6802</v>
+        <v>0.5306</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1684</v>
+        <v>0.1313</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3146</v>
+        <v>-0.3641</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6802</v>
+        <v>0.5306</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6802</v>
+        <v>0.5306</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6802</v>
+        <v>0.5306</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6802</v>
+        <v>0.5306</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6802</v>
+        <v>0.5306</v>
       </c>
       <c r="N25" t="n">
         <v>101</v>
@@ -1596,277 +1596,277 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MSL</t>
+          <t>xseveN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4551</v>
+        <v>0.4721</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1126</v>
+        <v>0.1169</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.417</v>
+        <v>-0.3907</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4551</v>
+        <v>0.4721</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4551</v>
+        <v>0.4721</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4551</v>
+        <v>0.4721</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4551</v>
+        <v>0.4721</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4551</v>
+        <v>0.4721</v>
       </c>
       <c r="N26" t="n">
-        <v>143</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>xseveN</t>
+          <t>MSL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3639</v>
+        <v>0.353</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0901</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4585</v>
+        <v>-0.445</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3639</v>
+        <v>0.353</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3639</v>
+        <v>0.353</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3639</v>
+        <v>0.353</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3639</v>
+        <v>0.353</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3639</v>
+        <v>0.353</v>
       </c>
       <c r="N27" t="n">
-        <v>210</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0682</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0209</v>
+        <v>-0.0169</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5857</v>
+        <v>-0.6369</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.0682</v>
       </c>
       <c r="F28" t="n">
-        <v>0.738</v>
+        <v>-0.0682</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.6534</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.738</v>
+        <v>-0.0682</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3985</v>
+        <v>-0.0682</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6534</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>235</v>
+        <v>101</v>
       </c>
       <c r="L28" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.2549</v>
+        <v>-0.0682</v>
       </c>
       <c r="N28" t="n">
-        <v>282</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Aerial</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0464</v>
+        <v>-0.1207</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0115</v>
+        <v>-0.0299</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6453</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0464</v>
+        <v>-0.1207</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0464</v>
+        <v>-0.1207</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0464</v>
+        <v>-0.1207</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0464</v>
+        <v>-0.1207</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>101</v>
+        <v>210</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0464</v>
+        <v>-0.1207</v>
       </c>
       <c r="N29" t="n">
-        <v>101</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1346</v>
+        <v>-0.1566</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0333</v>
+        <v>-0.0388</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6855</v>
+        <v>-0.6771</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1346</v>
+        <v>-0.1566</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1346</v>
+        <v>0.4657</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.6223</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1346</v>
+        <v>0.4657</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1346</v>
+        <v>0.2615</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.6223</v>
       </c>
       <c r="K30" t="n">
-        <v>143</v>
+        <v>235</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1346</v>
+        <v>-0.3608</v>
       </c>
       <c r="N30" t="n">
-        <v>143</v>
+        <v>282</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Aerial</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1382</v>
+        <v>-0.2234</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0342</v>
+        <v>-0.0553</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6871</v>
+        <v>-0.7076</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1382</v>
+        <v>-0.2234</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1382</v>
+        <v>-0.2234</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1382</v>
+        <v>-0.2234</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1382</v>
+        <v>-0.2234</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1382</v>
+        <v>-0.2234</v>
       </c>
       <c r="N31" t="n">
-        <v>210</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4425</v>
+        <v>-0.4282</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1095</v>
+        <v>-0.106</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8256</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4425</v>
+        <v>-0.4282</v>
       </c>
       <c r="F32" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0801</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5401</v>
+        <v>-0.5083</v>
       </c>
       <c r="H32" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0801</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0527</v>
+        <v>0.045</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5401</v>
+        <v>-0.5083</v>
       </c>
       <c r="K32" t="n">
         <v>235</v>
@@ -1909,7 +1909,7 @@
         <v>47</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4874000000000001</v>
+        <v>-0.4633</v>
       </c>
       <c r="N32" t="n">
         <v>282</v>
@@ -1918,32 +1918,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4691</v>
+        <v>-0.4685</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1161</v>
+        <v>-0.116</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8377</v>
+        <v>-0.8192</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4691</v>
+        <v>-0.4685</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4691</v>
+        <v>-0.4685</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4691</v>
+        <v>-0.4685</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4691</v>
+        <v>-0.4685</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4691</v>
+        <v>-0.4685</v>
       </c>
       <c r="N33" t="n">
         <v>101</v>
@@ -1964,32 +1964,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.4814</v>
+        <v>-0.5032</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1192</v>
+        <v>-0.1246</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8433</v>
+        <v>-0.835</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4814</v>
+        <v>-0.5032</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4814</v>
+        <v>-0.5032</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4814</v>
+        <v>-0.5032</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4814</v>
+        <v>-0.5032</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.4814</v>
+        <v>-0.5032</v>
       </c>
       <c r="N34" t="n">
         <v>101</v>
@@ -2010,32 +2010,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5854</v>
+        <v>-0.5605</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1449</v>
+        <v>-0.1387</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8907</v>
+        <v>-0.8611</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5854</v>
+        <v>-0.5605</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5854</v>
+        <v>-0.5605</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5854</v>
+        <v>-0.5605</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5854</v>
+        <v>-0.5605</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5854</v>
+        <v>-0.5605</v>
       </c>
       <c r="N35" t="n">
         <v>101</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6511</v>
+        <v>-0.662</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1612</v>
+        <v>-0.1639</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9206</v>
+        <v>-0.9074</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6511</v>
+        <v>-0.662</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6511</v>
+        <v>-0.662</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6511</v>
+        <v>-0.662</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6511</v>
+        <v>-0.662</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6511</v>
+        <v>-0.662</v>
       </c>
       <c r="N36" t="n">
         <v>101</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.7432</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1895</v>
+        <v>-0.184</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9727</v>
+        <v>-0.9444</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.7432</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.7432</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.7432</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.7432</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.7432</v>
       </c>
       <c r="N37" t="n">
         <v>101</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.7817</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1935</v>
+        <v>-0.1945</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.98</v>
+        <v>-0.9638</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.7817</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.7817</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7817</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7817</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7817</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>101</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0832</v>
+        <v>-1.1025</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2681</v>
+        <v>-0.2729</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1173</v>
+        <v>-1.108</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0832</v>
+        <v>-1.1025</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0832</v>
+        <v>-1.1025</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0832</v>
+        <v>-1.1025</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0832</v>
+        <v>-1.1025</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0832</v>
+        <v>-1.1025</v>
       </c>
       <c r="N39" t="n">
         <v>101</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0463</v>
+        <v>-1.9894</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5065</v>
+        <v>-0.4924</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5557</v>
+        <v>-1.5121</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0463</v>
+        <v>-1.9894</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2517</v>
+        <v>-1.2115</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.7946</v>
+        <v>-0.7779</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2517</v>
+        <v>-1.2115</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.6802</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7946</v>
+        <v>-0.7779</v>
       </c>
       <c r="K40" t="n">
         <v>235</v>
@@ -2277,7 +2277,7 @@
         <v>47</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4705</v>
+        <v>-1.4581</v>
       </c>
       <c r="N40" t="n">
         <v>282</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.2669</v>
+        <v>-2.4032</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5611</v>
+        <v>-0.5948</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6561</v>
+        <v>-1.7006</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.2669</v>
+        <v>-2.4032</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.2669</v>
+        <v>-2.4032</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.2669</v>
+        <v>-2.4032</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.2669</v>
+        <v>-2.4032</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2669</v>
+        <v>-2.4032</v>
       </c>
       <c r="N41" t="n">
         <v>143</v>
@@ -2429,10 +2429,10 @@
         <v>0.9</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.111</v>
+        <v>-0.0949</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.109</v>
+        <v>-1.8031</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.79</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2326</v>
+        <v>-0.2178</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.4194</v>
+        <v>-4.1382</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.72</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2999</v>
+        <v>-0.2861</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.6981</v>
+        <v>-5.4359</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.61</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3969</v>
+        <v>-0.3859</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.5411</v>
+        <v>-7.3321</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.48</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5115</v>
+        <v>-0.5112</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.718500000000001</v>
+        <v>-9.7128</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.66</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3714</v>
+        <v>1.4068</v>
       </c>
       <c r="J7" t="n">
-        <v>26.0566</v>
+        <v>26.7292</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.51</v>
       </c>
       <c r="I8" t="n">
-        <v>1.112</v>
+        <v>1.1213</v>
       </c>
       <c r="J8" t="n">
-        <v>21.128</v>
+        <v>21.3047</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.37</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8615</v>
+        <v>0.8509</v>
       </c>
       <c r="J9" t="n">
-        <v>16.3685</v>
+        <v>16.1671</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.34</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8047</v>
+        <v>0.7905</v>
       </c>
       <c r="J10" t="n">
-        <v>15.2893</v>
+        <v>15.0195</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.15</v>
       </c>
       <c r="I11" t="n">
-        <v>0.402</v>
+        <v>0.3703</v>
       </c>
       <c r="J11" t="n">
-        <v>7.638</v>
+        <v>7.0357</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.35</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6848</v>
+        <v>0.6293</v>
       </c>
       <c r="J12" t="n">
-        <v>19.1744</v>
+        <v>17.6204</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0238</v>
+        <v>-0.0175</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6664</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.88</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1667</v>
+        <v>-0.1467</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.6676</v>
+        <v>-4.1076</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.82</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2296</v>
+        <v>-0.2093</v>
       </c>
       <c r="J15" t="n">
-        <v>-6.4288</v>
+        <v>-5.8604</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2397</v>
+        <v>-0.2195</v>
       </c>
       <c r="J16" t="n">
-        <v>-6.7116</v>
+        <v>-6.146</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5713</v>
+        <v>0.5317</v>
       </c>
       <c r="J17" t="n">
-        <v>15.9964</v>
+        <v>14.8876</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.13</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4061</v>
+        <v>0.3647</v>
       </c>
       <c r="J18" t="n">
-        <v>11.3708</v>
+        <v>10.2116</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3302</v>
+        <v>0.2906</v>
       </c>
       <c r="J19" t="n">
-        <v>9.2456</v>
+        <v>8.136799999999999</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.93</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2703</v>
+        <v>-0.2303</v>
       </c>
       <c r="J20" t="n">
-        <v>-7.5684</v>
+        <v>-6.4484</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.92</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2986</v>
+        <v>-0.2575</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.360799999999999</v>
+        <v>-7.21</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.16</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2718</v>
+        <v>0.2187</v>
       </c>
       <c r="J22" t="n">
-        <v>11.4156</v>
+        <v>9.1854</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.05</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1108</v>
+        <v>0.0806</v>
       </c>
       <c r="J23" t="n">
-        <v>4.6536</v>
+        <v>3.3852</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.05</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1108</v>
+        <v>0.0806</v>
       </c>
       <c r="J24" t="n">
-        <v>4.6536</v>
+        <v>3.3852</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.01</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0328</v>
+        <v>0.0209</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3776</v>
+        <v>0.8778</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3561</v>
+        <v>-0.3419</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.9562</v>
+        <v>-14.3598</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.23</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3671</v>
+        <v>0.3608</v>
       </c>
       <c r="J27" t="n">
-        <v>15.4182</v>
+        <v>15.1536</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.14</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2473</v>
+        <v>0.2333</v>
       </c>
       <c r="J28" t="n">
-        <v>10.3866</v>
+        <v>9.7986</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.11</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2044</v>
+        <v>0.1893</v>
       </c>
       <c r="J29" t="n">
-        <v>8.5848</v>
+        <v>7.9506</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.03</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0731</v>
+        <v>0.0619</v>
       </c>
       <c r="J30" t="n">
-        <v>3.0702</v>
+        <v>2.5998</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.84</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2181</v>
+        <v>-0.1976</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.1602</v>
+        <v>-8.299200000000001</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>0.96</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0437</v>
+        <v>-0.0321</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.0488</v>
+        <v>-0.7704</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.93</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.0712</v>
       </c>
       <c r="J33" t="n">
-        <v>-2.04</v>
+        <v>-1.7088</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2205</v>
+        <v>-0.2045</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.292</v>
+        <v>-4.908</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.65</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.368</v>
+        <v>-0.3545</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.832000000000001</v>
+        <v>-8.507999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.43</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5613</v>
+        <v>-0.5686</v>
       </c>
       <c r="J36" t="n">
-        <v>-13.4712</v>
+        <v>-13.6464</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.55</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1924</v>
+        <v>1.2083</v>
       </c>
       <c r="J37" t="n">
-        <v>28.6176</v>
+        <v>28.9992</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.54</v>
       </c>
       <c r="I38" t="n">
-        <v>1.1747</v>
+        <v>1.1886</v>
       </c>
       <c r="J38" t="n">
-        <v>28.1928</v>
+        <v>28.5264</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.33</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7743</v>
       </c>
       <c r="J39" t="n">
-        <v>19.0032</v>
+        <v>18.5832</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.31</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7532</v>
+        <v>0.7337</v>
       </c>
       <c r="J40" t="n">
-        <v>18.0768</v>
+        <v>17.6088</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.03</v>
       </c>
       <c r="I41" t="n">
-        <v>0.079</v>
+        <v>0.0573</v>
       </c>
       <c r="J41" t="n">
-        <v>1.896</v>
+        <v>1.3752</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.71</v>
       </c>
       <c r="I42" t="n">
-        <v>1.2293</v>
+        <v>1.2287</v>
       </c>
       <c r="J42" t="n">
-        <v>29.5032</v>
+        <v>29.4888</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.25</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5924</v>
+        <v>0.5839</v>
       </c>
       <c r="J43" t="n">
-        <v>14.2176</v>
+        <v>14.0136</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.14</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4054</v>
+        <v>0.3722</v>
       </c>
       <c r="J44" t="n">
-        <v>9.7296</v>
+        <v>8.9328</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.07</v>
       </c>
       <c r="I45" t="n">
-        <v>0.224</v>
+        <v>0.1946</v>
       </c>
       <c r="J45" t="n">
-        <v>5.376</v>
+        <v>4.6704</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.97</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1764</v>
+        <v>-0.1454</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.2336</v>
+        <v>-3.4896</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.11</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3286</v>
+        <v>0.2828</v>
       </c>
       <c r="J47" t="n">
-        <v>7.8864</v>
+        <v>6.7872</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>0.75</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.2812</v>
+        <v>-0.2637</v>
       </c>
       <c r="J48" t="n">
-        <v>-6.7488</v>
+        <v>-6.3288</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.75</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2812</v>
+        <v>-0.2637</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.7488</v>
+        <v>-6.3288</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.71</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3183</v>
+        <v>-0.3019</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.6392</v>
+        <v>-7.2456</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.68</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3459</v>
+        <v>-0.3307</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.301600000000001</v>
+        <v>-7.9368</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.55</v>
       </c>
       <c r="I52" t="n">
-        <v>0.994</v>
+        <v>0.9828</v>
       </c>
       <c r="J52" t="n">
-        <v>22.862</v>
+        <v>22.6044</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.44</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8485</v>
+        <v>0.8367</v>
       </c>
       <c r="J53" t="n">
-        <v>19.5155</v>
+        <v>19.2441</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.41</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.7968</v>
       </c>
       <c r="J54" t="n">
-        <v>18.584</v>
+        <v>18.3264</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.22</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5331</v>
+        <v>0.5303</v>
       </c>
       <c r="J55" t="n">
-        <v>12.2613</v>
+        <v>12.1969</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>1.21</v>
       </c>
       <c r="I56" t="n">
-        <v>0.517</v>
+        <v>0.5123</v>
       </c>
       <c r="J56" t="n">
-        <v>11.891</v>
+        <v>11.7829</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5274</v>
+        <v>0.5097</v>
       </c>
       <c r="J57" t="n">
-        <v>12.1302</v>
+        <v>11.7231</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.84</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1942</v>
+        <v>-0.1776</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.4666</v>
+        <v>-4.0848</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.75</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2804</v>
+        <v>-0.2631</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.4492</v>
+        <v>-6.0513</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.65</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3722</v>
+        <v>-0.3586</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.560600000000001</v>
+        <v>-8.2478</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.49</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5134</v>
+        <v>-0.5142</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.8082</v>
+        <v>-11.8266</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.3</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5913</v>
+        <v>0.5697</v>
       </c>
       <c r="J62" t="n">
-        <v>14.7825</v>
+        <v>14.2425</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>0.95</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0631</v>
       </c>
       <c r="J63" t="n">
-        <v>-1.8825</v>
+        <v>-1.5775</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.87</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1694</v>
+        <v>-0.1515</v>
       </c>
       <c r="J64" t="n">
-        <v>-4.235</v>
+        <v>-3.7875</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.72</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3159</v>
+        <v>-0.2987</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.8975</v>
+        <v>-7.4675</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.48</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.529</v>
+        <v>-0.5329</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.225</v>
+        <v>-13.3225</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.78</v>
       </c>
       <c r="I67" t="n">
-        <v>1.3076</v>
+        <v>1.3118</v>
       </c>
       <c r="J67" t="n">
-        <v>32.69</v>
+        <v>32.795</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.49</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9296</v>
+        <v>0.9157</v>
       </c>
       <c r="J68" t="n">
-        <v>23.24</v>
+        <v>22.8925</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.22</v>
       </c>
       <c r="I69" t="n">
-        <v>0.5432</v>
+        <v>0.5386</v>
       </c>
       <c r="J69" t="n">
-        <v>13.58</v>
+        <v>13.465</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.97</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1835</v>
+        <v>-0.1531</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.5875</v>
+        <v>-3.8275</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.89</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4183</v>
+        <v>-0.3791</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.4575</v>
+        <v>-9.477499999999999</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.44</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5346</v>
+        <v>0.4962</v>
       </c>
       <c r="J72" t="n">
-        <v>13.365</v>
+        <v>12.405</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.42</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5191</v>
+        <v>0.477</v>
       </c>
       <c r="J73" t="n">
-        <v>12.9775</v>
+        <v>11.925</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.17</v>
       </c>
       <c r="I74" t="n">
-        <v>0.265</v>
+        <v>0.2155</v>
       </c>
       <c r="J74" t="n">
-        <v>6.625</v>
+        <v>5.3875</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1439</v>
+        <v>0.1112</v>
       </c>
       <c r="J75" t="n">
-        <v>3.5975</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.72</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3424</v>
+        <v>-0.3289</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.56</v>
+        <v>-8.2225</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.15</v>
       </c>
       <c r="I77" t="n">
-        <v>0.279</v>
+        <v>0.2656</v>
       </c>
       <c r="J77" t="n">
-        <v>6.975</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.13</v>
       </c>
       <c r="I78" t="n">
-        <v>0.25</v>
+        <v>0.2349</v>
       </c>
       <c r="J78" t="n">
-        <v>6.25</v>
+        <v>5.8725</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.88</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1654</v>
+        <v>-0.1457</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.135</v>
+        <v>-3.6425</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.88</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1654</v>
+        <v>-0.1457</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.135</v>
+        <v>-3.6425</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.74</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3063</v>
+        <v>-0.2886</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.6575</v>
+        <v>-7.215</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.4</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6651</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>19.2879</v>
+        <v>18.3744</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.18</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3949</v>
+        <v>0.3389</v>
       </c>
       <c r="J83" t="n">
-        <v>11.4521</v>
+        <v>9.828099999999999</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.06</v>
       </c>
       <c r="I84" t="n">
-        <v>0.1673</v>
+        <v>0.131</v>
       </c>
       <c r="J84" t="n">
-        <v>4.8517</v>
+        <v>3.799</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.79</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2641</v>
+        <v>-0.2447</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.6589</v>
+        <v>-7.0963</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.67</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3767</v>
+        <v>-0.3645</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.9243</v>
+        <v>-10.5705</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.38</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8137</v>
+        <v>0.798</v>
       </c>
       <c r="J87" t="n">
-        <v>23.5973</v>
+        <v>23.142</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.26</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6299</v>
+        <v>0.616</v>
       </c>
       <c r="J88" t="n">
-        <v>18.2671</v>
+        <v>17.864</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.09</v>
       </c>
       <c r="I89" t="n">
-        <v>0.3006</v>
+        <v>0.2635</v>
       </c>
       <c r="J89" t="n">
-        <v>8.7174</v>
+        <v>7.6415</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0121</v>
+        <v>-0.0081</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.3509</v>
+        <v>-0.2349</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.67</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.888</v>
+        <v>-0.8731</v>
       </c>
       <c r="J91" t="n">
-        <v>-25.752</v>
+        <v>-25.3199</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.12</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3637</v>
+        <v>0.3202</v>
       </c>
       <c r="J92" t="n">
-        <v>8.0014</v>
+        <v>7.0444</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.301</v>
+        <v>0.2599</v>
       </c>
       <c r="J93" t="n">
-        <v>6.622</v>
+        <v>5.7178</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.3329</v>
+        <v>-0.3176</v>
       </c>
       <c r="J94" t="n">
-        <v>-7.3238</v>
+        <v>-6.9872</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.61</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.4051</v>
+        <v>-0.394</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.9122</v>
+        <v>-8.667999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.32</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.6797</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.4254</v>
+        <v>-14.9534</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.42</v>
       </c>
       <c r="I97" t="n">
-        <v>0.9560999999999999</v>
+        <v>0.9513</v>
       </c>
       <c r="J97" t="n">
-        <v>21.0342</v>
+        <v>20.9286</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.4</v>
       </c>
       <c r="I98" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9121</v>
       </c>
       <c r="J98" t="n">
-        <v>20.2598</v>
+        <v>20.0662</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.4</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9121</v>
       </c>
       <c r="J99" t="n">
-        <v>20.2598</v>
+        <v>20.0662</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.31</v>
       </c>
       <c r="I100" t="n">
-        <v>0.753</v>
+        <v>0.7335</v>
       </c>
       <c r="J100" t="n">
-        <v>16.566</v>
+        <v>16.137</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>1.24</v>
       </c>
       <c r="I101" t="n">
-        <v>0.6108</v>
+        <v>0.5849</v>
       </c>
       <c r="J101" t="n">
-        <v>13.4376</v>
+        <v>12.8678</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.1</v>
       </c>
       <c r="I102" t="n">
-        <v>0.357</v>
+        <v>0.324</v>
       </c>
       <c r="J102" t="n">
-        <v>8.211</v>
+        <v>7.452</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.2117</v>
+        <v>-0.1966</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.8691</v>
+        <v>-4.5218</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.62</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3878</v>
+        <v>-0.3763</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.9194</v>
+        <v>-8.6549</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.59</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4144</v>
+        <v>-0.4045</v>
       </c>
       <c r="J105" t="n">
-        <v>-9.5312</v>
+        <v>-9.3035</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.37</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6067</v>
+        <v>-0.6206</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.9541</v>
+        <v>-14.2738</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.66</v>
       </c>
       <c r="I107" t="n">
-        <v>1.2727</v>
+        <v>1.2918</v>
       </c>
       <c r="J107" t="n">
-        <v>29.2721</v>
+        <v>29.7114</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.52</v>
       </c>
       <c r="I108" t="n">
-        <v>1.0946</v>
+        <v>1.1095</v>
       </c>
       <c r="J108" t="n">
-        <v>25.1758</v>
+        <v>25.5185</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.47</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0269</v>
+        <v>1.0352</v>
       </c>
       <c r="J109" t="n">
-        <v>23.6187</v>
+        <v>23.8096</v>
       </c>
     </row>
     <row r="110">
@@ -6789,10 +6789,10 @@
         <v>1.05</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1332</v>
+        <v>0.1051</v>
       </c>
       <c r="J111" t="n">
-        <v>3.0636</v>
+        <v>2.4173</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.31</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6014</v>
+        <v>0.5417</v>
       </c>
       <c r="J112" t="n">
-        <v>21.6504</v>
+        <v>19.5012</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.09</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2259</v>
+        <v>0.1831</v>
       </c>
       <c r="J113" t="n">
-        <v>8.132400000000001</v>
+        <v>6.5916</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.01</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0394</v>
+        <v>0.0275</v>
       </c>
       <c r="J114" t="n">
-        <v>1.4184</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.97</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.0614</v>
+        <v>-0.048</v>
       </c>
       <c r="J115" t="n">
-        <v>-2.2104</v>
+        <v>-1.728</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.84</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2158</v>
+        <v>-0.1953</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.7688</v>
+        <v>-7.0308</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.23</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6347</v>
+        <v>0.5978</v>
       </c>
       <c r="J117" t="n">
-        <v>22.8492</v>
+        <v>21.5208</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.2</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5678</v>
+        <v>0.5284</v>
       </c>
       <c r="J118" t="n">
-        <v>20.4408</v>
+        <v>19.0224</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5678</v>
+        <v>0.5284</v>
       </c>
       <c r="J119" t="n">
-        <v>20.4408</v>
+        <v>19.0224</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.88</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4081</v>
+        <v>-0.3651</v>
       </c>
       <c r="J120" t="n">
-        <v>-14.6916</v>
+        <v>-13.1436</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.84</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5074</v>
+        <v>-0.4658</v>
       </c>
       <c r="J121" t="n">
-        <v>-18.2664</v>
+        <v>-16.7688</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.58</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7029</v>
+        <v>0.6308</v>
       </c>
       <c r="J122" t="n">
-        <v>18.9783</v>
+        <v>17.0316</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.35</v>
       </c>
       <c r="I123" t="n">
-        <v>0.466</v>
+        <v>0.4</v>
       </c>
       <c r="J123" t="n">
-        <v>12.582</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.27</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3781</v>
+        <v>0.3184</v>
       </c>
       <c r="J124" t="n">
-        <v>10.2087</v>
+        <v>8.5968</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>1</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0156</v>
+        <v>-0.0131</v>
       </c>
       <c r="J125" t="n">
-        <v>-0.4212</v>
+        <v>-0.3537</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.88</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.187</v>
+        <v>-0.1675</v>
       </c>
       <c r="J126" t="n">
-        <v>-5.049</v>
+        <v>-4.5225</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.56</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8005</v>
+        <v>0.8772</v>
       </c>
       <c r="J127" t="n">
-        <v>21.6135</v>
+        <v>23.6844</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.21</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3713</v>
+        <v>0.367</v>
       </c>
       <c r="J128" t="n">
-        <v>10.0251</v>
+        <v>9.909000000000001</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.79</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2544</v>
+        <v>-0.2347</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.8688</v>
+        <v>-6.3369</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.55</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4735</v>
+        <v>-0.4706</v>
       </c>
       <c r="J130" t="n">
-        <v>-12.7845</v>
+        <v>-12.7062</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.47</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.5484</v>
       </c>
       <c r="J131" t="n">
-        <v>-14.6286</v>
+        <v>-14.8068</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.05</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1824</v>
+        <v>0.1451</v>
       </c>
       <c r="J132" t="n">
-        <v>4.9248</v>
+        <v>3.9177</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.01</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0731</v>
+        <v>0.0538</v>
       </c>
       <c r="J133" t="n">
-        <v>1.9737</v>
+        <v>1.4526</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.93</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0989</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.6703</v>
+        <v>-2.295</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.73</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3045</v>
+        <v>-0.287</v>
       </c>
       <c r="J135" t="n">
-        <v>-8.221500000000001</v>
+        <v>-7.749</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.5</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.51</v>
+        <v>-0.5109</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.77</v>
+        <v>-13.7943</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.46</v>
       </c>
       <c r="I137" t="n">
-        <v>1.0301</v>
+        <v>1.034</v>
       </c>
       <c r="J137" t="n">
-        <v>27.8127</v>
+        <v>27.918</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.36</v>
       </c>
       <c r="I138" t="n">
-        <v>0.855</v>
+        <v>0.8381</v>
       </c>
       <c r="J138" t="n">
-        <v>23.085</v>
+        <v>22.6287</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.25</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6402</v>
+        <v>0.613</v>
       </c>
       <c r="J139" t="n">
-        <v>17.2854</v>
+        <v>16.551</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.24</v>
       </c>
       <c r="I140" t="n">
-        <v>0.6194</v>
+        <v>0.5916</v>
       </c>
       <c r="J140" t="n">
-        <v>16.7238</v>
+        <v>15.9732</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.15</v>
       </c>
       <c r="I141" t="n">
-        <v>0.4196</v>
+        <v>0.3875</v>
       </c>
       <c r="J141" t="n">
-        <v>11.3292</v>
+        <v>10.4625</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.15</v>
       </c>
       <c r="I142" t="n">
-        <v>0.3587</v>
+        <v>0.3046</v>
       </c>
       <c r="J142" t="n">
-        <v>10.761</v>
+        <v>9.138</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.04</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1334</v>
+        <v>0.1008</v>
       </c>
       <c r="J143" t="n">
-        <v>4.002</v>
+        <v>3.024</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.98</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0396</v>
+        <v>-0.0308</v>
       </c>
       <c r="J144" t="n">
-        <v>-1.188</v>
+        <v>-0.924</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.96</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.0694</v>
+        <v>-0.0566</v>
       </c>
       <c r="J145" t="n">
-        <v>-2.082</v>
+        <v>-1.698</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.6</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4326</v>
+        <v>-0.4252</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.978</v>
+        <v>-12.756</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.46</v>
       </c>
       <c r="I147" t="n">
-        <v>1.0726</v>
+        <v>1.0822</v>
       </c>
       <c r="J147" t="n">
-        <v>32.178</v>
+        <v>32.466</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.2</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5613</v>
+        <v>0.5226</v>
       </c>
       <c r="J148" t="n">
-        <v>16.839</v>
+        <v>15.678</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.09</v>
       </c>
       <c r="I149" t="n">
-        <v>0.299</v>
+        <v>0.2629</v>
       </c>
       <c r="J149" t="n">
-        <v>8.970000000000001</v>
+        <v>7.887</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.88</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4136</v>
+        <v>-0.3708</v>
       </c>
       <c r="J150" t="n">
-        <v>-12.408</v>
+        <v>-11.124</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.86</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.464</v>
+        <v>-0.4217</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.92</v>
+        <v>-12.651</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.29</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5746</v>
+        <v>0.515</v>
       </c>
       <c r="J152" t="n">
-        <v>16.0888</v>
+        <v>14.42</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1878</v>
+        <v>0.149</v>
       </c>
       <c r="J153" t="n">
-        <v>5.2584</v>
+        <v>4.172</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.06</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1665</v>
+        <v>0.1305</v>
       </c>
       <c r="J154" t="n">
-        <v>4.662</v>
+        <v>3.654</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0014</v>
+        <v>-0.0007</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.0392</v>
+        <v>-0.0196</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.71</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3407</v>
+        <v>-0.3256</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.5396</v>
+        <v>-9.1168</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.2</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5588</v>
+        <v>0.5205</v>
       </c>
       <c r="J157" t="n">
-        <v>15.6464</v>
+        <v>14.574</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.19</v>
       </c>
       <c r="I158" t="n">
-        <v>0.5364</v>
+        <v>0.4976</v>
       </c>
       <c r="J158" t="n">
-        <v>15.0192</v>
+        <v>13.9328</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.16</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4677</v>
+        <v>0.4284</v>
       </c>
       <c r="J159" t="n">
-        <v>13.0956</v>
+        <v>11.9952</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.14</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4207</v>
+        <v>0.3817</v>
       </c>
       <c r="J160" t="n">
-        <v>11.7796</v>
+        <v>10.6876</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.86</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4663</v>
+        <v>-0.4242</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.0564</v>
+        <v>-11.8776</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.28</v>
       </c>
       <c r="I162" t="n">
-        <v>0.7313</v>
+        <v>0.7002</v>
       </c>
       <c r="J162" t="n">
-        <v>19.7451</v>
+        <v>18.9054</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.13</v>
       </c>
       <c r="I163" t="n">
-        <v>0.3966</v>
+        <v>0.358</v>
       </c>
       <c r="J163" t="n">
-        <v>10.7082</v>
+        <v>9.666</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.11</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3482</v>
+        <v>0.3109</v>
       </c>
       <c r="J164" t="n">
-        <v>9.401400000000001</v>
+        <v>8.394299999999999</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.08</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2706</v>
+        <v>0.2366</v>
       </c>
       <c r="J165" t="n">
-        <v>7.3062</v>
+        <v>6.3882</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.96</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.1893</v>
+        <v>-0.1548</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.1111</v>
+        <v>-4.1796</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.32</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.5816</v>
       </c>
       <c r="J167" t="n">
-        <v>17.2422</v>
+        <v>15.7032</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.04</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1295</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="J168" t="n">
-        <v>3.4965</v>
+        <v>2.6352</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.02</v>
       </c>
       <c r="I169" t="n">
-        <v>0.0776</v>
+        <v>0.0551</v>
       </c>
       <c r="J169" t="n">
-        <v>2.0952</v>
+        <v>1.4877</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.83</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2193</v>
+        <v>-0.1988</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.9211</v>
+        <v>-5.3676</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.63</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4081</v>
+        <v>-0.3983</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.0187</v>
+        <v>-10.7541</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.66</v>
       </c>
       <c r="I172" t="n">
-        <v>1.3064</v>
+        <v>1.3264</v>
       </c>
       <c r="J172" t="n">
-        <v>31.3536</v>
+        <v>31.8336</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.53</v>
       </c>
       <c r="I173" t="n">
-        <v>1.1347</v>
+        <v>1.1473</v>
       </c>
       <c r="J173" t="n">
-        <v>27.2328</v>
+        <v>27.5352</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.37</v>
       </c>
       <c r="I174" t="n">
-        <v>0.8815</v>
+        <v>0.8646</v>
       </c>
       <c r="J174" t="n">
-        <v>21.156</v>
+        <v>20.7504</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.19</v>
       </c>
       <c r="I175" t="n">
-        <v>0.5175999999999999</v>
+        <v>0.4856</v>
       </c>
       <c r="J175" t="n">
-        <v>12.4224</v>
+        <v>11.6544</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.5</v>
       </c>
       <c r="I176" t="n">
-        <v>-1.2512</v>
+        <v>-1.2918</v>
       </c>
       <c r="J176" t="n">
-        <v>-30.0288</v>
+        <v>-31.0032</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.35</v>
       </c>
       <c r="I177" t="n">
-        <v>0.702</v>
+        <v>0.6501</v>
       </c>
       <c r="J177" t="n">
-        <v>16.848</v>
+        <v>15.6024</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.17</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4016</v>
+        <v>0.3463</v>
       </c>
       <c r="J178" t="n">
-        <v>9.638400000000001</v>
+        <v>8.311199999999999</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.92</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1179</v>
+        <v>-0.1012</v>
       </c>
       <c r="J179" t="n">
-        <v>-2.8296</v>
+        <v>-2.4288</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.67</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3679</v>
+        <v>-0.3541</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.829599999999999</v>
+        <v>-8.4984</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.5</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5169</v>
+        <v>-0.5199</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.4056</v>
+        <v>-12.4776</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.97</v>
       </c>
       <c r="I182" t="n">
-        <v>1.639</v>
+        <v>1.6813</v>
       </c>
       <c r="J182" t="n">
-        <v>31.141</v>
+        <v>31.9447</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.6</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1913</v>
+        <v>1.2092</v>
       </c>
       <c r="J183" t="n">
-        <v>22.6347</v>
+        <v>22.9748</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.6</v>
       </c>
       <c r="I184" t="n">
-        <v>1.1913</v>
+        <v>1.2092</v>
       </c>
       <c r="J184" t="n">
-        <v>22.6347</v>
+        <v>22.9748</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.2</v>
       </c>
       <c r="I185" t="n">
-        <v>0.507</v>
+        <v>0.4784</v>
       </c>
       <c r="J185" t="n">
-        <v>9.632999999999999</v>
+        <v>9.089600000000001</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.99</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1361</v>
+        <v>-0.1206</v>
       </c>
       <c r="J186" t="n">
-        <v>-2.5859</v>
+        <v>-2.2914</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>0.8</v>
       </c>
       <c r="I187" t="n">
-        <v>-0.1938</v>
+        <v>-0.1753</v>
       </c>
       <c r="J187" t="n">
-        <v>-3.6822</v>
+        <v>-3.3307</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.75</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.2477</v>
+        <v>-0.233</v>
       </c>
       <c r="J188" t="n">
-        <v>-4.7063</v>
+        <v>-4.427</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.62</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3743</v>
+        <v>-0.3667</v>
       </c>
       <c r="J189" t="n">
-        <v>-7.1117</v>
+        <v>-6.9673</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.48</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4946</v>
+        <v>-0.4925</v>
       </c>
       <c r="J190" t="n">
-        <v>-9.397399999999999</v>
+        <v>-9.3575</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.25</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.6984</v>
+        <v>-0.7279</v>
       </c>
       <c r="J191" t="n">
-        <v>-13.2696</v>
+        <v>-13.8301</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.23</v>
       </c>
       <c r="I192" t="n">
-        <v>0.3747</v>
+        <v>0.3689</v>
       </c>
       <c r="J192" t="n">
-        <v>13.4892</v>
+        <v>13.2804</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.14</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2533</v>
+        <v>0.2386</v>
       </c>
       <c r="J193" t="n">
-        <v>9.1188</v>
+        <v>8.589600000000001</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1009</v>
+        <v>-0.0837</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.6324</v>
+        <v>-3.0132</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.91</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1375</v>
+        <v>-0.1181</v>
       </c>
       <c r="J195" t="n">
-        <v>-4.95</v>
+        <v>-4.2516</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.9</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.149</v>
+        <v>-0.1292</v>
       </c>
       <c r="J196" t="n">
-        <v>-5.364</v>
+        <v>-4.6512</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.37</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5013</v>
+        <v>0.4328</v>
       </c>
       <c r="J197" t="n">
-        <v>18.0468</v>
+        <v>15.5808</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.36</v>
       </c>
       <c r="I198" t="n">
-        <v>0.4903</v>
+        <v>0.4223</v>
       </c>
       <c r="J198" t="n">
-        <v>17.6508</v>
+        <v>15.2028</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.13</v>
       </c>
       <c r="I199" t="n">
-        <v>0.2172</v>
+        <v>0.1726</v>
       </c>
       <c r="J199" t="n">
-        <v>7.8192</v>
+        <v>6.2136</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.05</v>
       </c>
       <c r="I200" t="n">
-        <v>0.1006</v>
+        <v>0.075</v>
       </c>
       <c r="J200" t="n">
-        <v>3.6216</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.68</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3754</v>
+        <v>-0.3642</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.5144</v>
+        <v>-13.1112</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.71</v>
       </c>
       <c r="I202" t="n">
-        <v>1.3574</v>
+        <v>1.3798</v>
       </c>
       <c r="J202" t="n">
-        <v>32.5776</v>
+        <v>33.1152</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.3</v>
       </c>
       <c r="I203" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.7159</v>
       </c>
       <c r="J203" t="n">
-        <v>17.7216</v>
+        <v>17.1816</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.28</v>
       </c>
       <c r="I204" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="J204" t="n">
-        <v>16.7784</v>
+        <v>16.1976</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.25</v>
       </c>
       <c r="I205" t="n">
-        <v>0.6381</v>
+        <v>0.6116</v>
       </c>
       <c r="J205" t="n">
-        <v>15.3144</v>
+        <v>14.6784</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.0518</v>
+        <v>-0.0474</v>
       </c>
       <c r="J206" t="n">
-        <v>-1.2432</v>
+        <v>-1.1376</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.1</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2658</v>
+        <v>0.2179</v>
       </c>
       <c r="J207" t="n">
-        <v>6.3792</v>
+        <v>5.2296</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1</v>
       </c>
       <c r="I208" t="n">
-        <v>0.0081</v>
+        <v>0.0049</v>
       </c>
       <c r="J208" t="n">
-        <v>0.1944</v>
+        <v>0.1176</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.96</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.0687</v>
+        <v>-0.0562</v>
       </c>
       <c r="J209" t="n">
-        <v>-1.6488</v>
+        <v>-1.3488</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.82</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2264</v>
+        <v>-0.2062</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.4336</v>
+        <v>-4.9488</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.8</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2464</v>
+        <v>-0.2265</v>
       </c>
       <c r="J211" t="n">
-        <v>-5.9136</v>
+        <v>-5.436</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.32</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6259</v>
+        <v>0.5673</v>
       </c>
       <c r="J212" t="n">
-        <v>17.5252</v>
+        <v>15.8844</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.14</v>
       </c>
       <c r="I213" t="n">
-        <v>0.326</v>
+        <v>0.2737</v>
       </c>
       <c r="J213" t="n">
-        <v>9.128</v>
+        <v>7.6636</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.96</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0733</v>
+        <v>-0.0587</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.0524</v>
+        <v>-1.6436</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.85</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2024</v>
+        <v>-0.1817</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.6672</v>
+        <v>-5.0876</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.78</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.273</v>
+        <v>-0.2538</v>
       </c>
       <c r="J216" t="n">
-        <v>-7.644</v>
+        <v>-7.1064</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.38</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9402</v>
+        <v>0.9271</v>
       </c>
       <c r="J217" t="n">
-        <v>26.3256</v>
+        <v>25.9588</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.27</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7149</v>
+        <v>0.6825</v>
       </c>
       <c r="J218" t="n">
-        <v>20.0172</v>
+        <v>19.11</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0146</v>
+        <v>-0.0102</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.4088</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.97</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1522</v>
+        <v>-0.1211</v>
       </c>
       <c r="J220" t="n">
-        <v>-4.2616</v>
+        <v>-3.3908</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.85</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4879</v>
+        <v>-0.446</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.6612</v>
+        <v>-12.488</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.14</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3393</v>
+        <v>0.2861</v>
       </c>
       <c r="J222" t="n">
-        <v>8.8218</v>
+        <v>7.4386</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.03</v>
       </c>
       <c r="I223" t="n">
-        <v>0.1076</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="J223" t="n">
-        <v>2.7976</v>
+        <v>2.0592</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.89</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1539</v>
+        <v>-0.1346</v>
       </c>
       <c r="J224" t="n">
-        <v>-4.0014</v>
+        <v>-3.4996</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.85</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1969</v>
+        <v>-0.1766</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.1194</v>
+        <v>-4.5916</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.84</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2073</v>
+        <v>-0.187</v>
       </c>
       <c r="J226" t="n">
-        <v>-5.3898</v>
+        <v>-4.862</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.57</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2058</v>
+        <v>1.2216</v>
       </c>
       <c r="J227" t="n">
-        <v>31.3508</v>
+        <v>31.7616</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.17</v>
       </c>
       <c r="I228" t="n">
-        <v>0.4824</v>
+        <v>0.4464</v>
       </c>
       <c r="J228" t="n">
-        <v>12.5424</v>
+        <v>11.6064</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.13</v>
       </c>
       <c r="I229" t="n">
-        <v>0.3896</v>
+        <v>0.3543</v>
       </c>
       <c r="J229" t="n">
-        <v>10.1296</v>
+        <v>9.2118</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.02</v>
       </c>
       <c r="I230" t="n">
-        <v>0.0722</v>
+        <v>0.0559</v>
       </c>
       <c r="J230" t="n">
-        <v>1.8772</v>
+        <v>1.4534</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.98</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1302</v>
+        <v>-0.103</v>
       </c>
       <c r="J231" t="n">
-        <v>-3.3852</v>
+        <v>-2.678</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.2</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4386</v>
+        <v>0.381</v>
       </c>
       <c r="J232" t="n">
-        <v>12.2808</v>
+        <v>10.668</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.06</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1734</v>
+        <v>0.1354</v>
       </c>
       <c r="J233" t="n">
-        <v>4.8552</v>
+        <v>3.7912</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.93</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.1099</v>
+        <v>-0.0925</v>
       </c>
       <c r="J234" t="n">
-        <v>-3.0772</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.91</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1337</v>
+        <v>-0.1149</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.7436</v>
+        <v>-3.2172</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.8</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.2506</v>
+        <v>-0.2306</v>
       </c>
       <c r="J236" t="n">
-        <v>-7.0168</v>
+        <v>-6.4568</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.35</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8905999999999999</v>
+        <v>0.8719</v>
       </c>
       <c r="J237" t="n">
-        <v>24.9368</v>
+        <v>24.4132</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.29</v>
       </c>
       <c r="I238" t="n">
-        <v>0.7659</v>
+        <v>0.7366</v>
       </c>
       <c r="J238" t="n">
-        <v>21.4452</v>
+        <v>20.6248</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.18</v>
       </c>
       <c r="I239" t="n">
-        <v>0.5235</v>
+        <v>0.4829</v>
       </c>
       <c r="J239" t="n">
-        <v>14.658</v>
+        <v>13.5212</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.95</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2121</v>
+        <v>-0.1757</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.9388</v>
+        <v>-4.9196</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.55</v>
       </c>
       <c r="I241" t="n">
-        <v>-1.129</v>
+        <v>-1.1447</v>
       </c>
       <c r="J241" t="n">
-        <v>-31.612</v>
+        <v>-32.0516</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1</v>
       </c>
       <c r="I242" t="n">
-        <v>0.1022</v>
+        <v>0.1071</v>
       </c>
       <c r="J242" t="n">
-        <v>2.2484</v>
+        <v>2.3562</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.74</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.2755</v>
+        <v>-0.2624</v>
       </c>
       <c r="J243" t="n">
-        <v>-6.061</v>
+        <v>-5.7728</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.68</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.3316</v>
+        <v>-0.3197</v>
       </c>
       <c r="J244" t="n">
-        <v>-7.2952</v>
+        <v>-7.0334</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.62</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3831</v>
+        <v>-0.3724</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.4282</v>
+        <v>-8.1928</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.26</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6977</v>
+        <v>-0.7285</v>
       </c>
       <c r="J246" t="n">
-        <v>-15.3494</v>
+        <v>-16.027</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.78</v>
       </c>
       <c r="I247" t="n">
-        <v>1.4213</v>
+        <v>1.4476</v>
       </c>
       <c r="J247" t="n">
-        <v>31.2686</v>
+        <v>31.8472</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.66</v>
       </c>
       <c r="I248" t="n">
-        <v>1.273</v>
+        <v>1.2921</v>
       </c>
       <c r="J248" t="n">
-        <v>28.006</v>
+        <v>28.4262</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.63</v>
       </c>
       <c r="I249" t="n">
-        <v>1.2353</v>
+        <v>1.2531</v>
       </c>
       <c r="J249" t="n">
-        <v>27.1766</v>
+        <v>27.5682</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>1.05</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1335</v>
+        <v>0.1054</v>
       </c>
       <c r="J250" t="n">
-        <v>2.937</v>
+        <v>2.3188</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>1</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0677</v>
       </c>
       <c r="J251" t="n">
-        <v>-1.529</v>
+        <v>-1.4894</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.43</v>
       </c>
       <c r="I252" t="n">
-        <v>1.0203</v>
+        <v>1.0209</v>
       </c>
       <c r="J252" t="n">
-        <v>30.609</v>
+        <v>30.627</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.17</v>
       </c>
       <c r="I253" t="n">
-        <v>0.4888</v>
+        <v>0.45</v>
       </c>
       <c r="J253" t="n">
-        <v>14.664</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.08</v>
       </c>
       <c r="I254" t="n">
-        <v>0.2692</v>
+        <v>0.2357</v>
       </c>
       <c r="J254" t="n">
-        <v>8.076000000000001</v>
+        <v>7.071</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.97</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.1574</v>
+        <v>-0.126</v>
       </c>
       <c r="J255" t="n">
-        <v>-4.722</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.96</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.1912</v>
+        <v>-0.1566</v>
       </c>
       <c r="J256" t="n">
-        <v>-5.736</v>
+        <v>-4.698</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.25</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5171</v>
+        <v>0.458</v>
       </c>
       <c r="J257" t="n">
-        <v>15.513</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.14</v>
       </c>
       <c r="I258" t="n">
-        <v>0.328</v>
+        <v>0.2755</v>
       </c>
       <c r="J258" t="n">
-        <v>9.84</v>
+        <v>8.265000000000001</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.07</v>
       </c>
       <c r="I259" t="n">
-        <v>0.1916</v>
+        <v>0.1517</v>
       </c>
       <c r="J259" t="n">
-        <v>5.748</v>
+        <v>4.551</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.83</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2222</v>
+        <v>-0.2017</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.666</v>
+        <v>-6.051</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.71</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3385</v>
+        <v>-0.323</v>
       </c>
       <c r="J261" t="n">
-        <v>-10.155</v>
+        <v>-9.69</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>2</v>
       </c>
       <c r="I262" t="n">
-        <v>1.6578</v>
+        <v>1.7016</v>
       </c>
       <c r="J262" t="n">
-        <v>28.1826</v>
+        <v>28.9272</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.79</v>
       </c>
       <c r="I263" t="n">
-        <v>1.4126</v>
+        <v>1.4401</v>
       </c>
       <c r="J263" t="n">
-        <v>24.0142</v>
+        <v>24.4817</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.49</v>
       </c>
       <c r="I264" t="n">
-        <v>1.0452</v>
+        <v>1.0609</v>
       </c>
       <c r="J264" t="n">
-        <v>17.7684</v>
+        <v>18.0353</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.28</v>
       </c>
       <c r="I265" t="n">
-        <v>0.6654</v>
+        <v>0.6454</v>
       </c>
       <c r="J265" t="n">
-        <v>11.3118</v>
+        <v>10.9718</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>1.22</v>
       </c>
       <c r="I266" t="n">
-        <v>0.5392</v>
+        <v>0.5117</v>
       </c>
       <c r="J266" t="n">
-        <v>9.166399999999999</v>
+        <v>8.6989</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.18</v>
       </c>
       <c r="I267" t="n">
-        <v>0.611</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="J267" t="n">
-        <v>10.387</v>
+        <v>10.5655</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.64</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.3572</v>
+        <v>-0.3487</v>
       </c>
       <c r="J268" t="n">
-        <v>-6.0724</v>
+        <v>-5.9279</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.42</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.5485</v>
+        <v>-0.5523</v>
       </c>
       <c r="J269" t="n">
-        <v>-9.3245</v>
+        <v>-9.389099999999999</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.35</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.6105</v>
+        <v>-0.6234</v>
       </c>
       <c r="J270" t="n">
-        <v>-10.3785</v>
+        <v>-10.5978</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.34</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6194</v>
+        <v>-0.6337</v>
       </c>
       <c r="J271" t="n">
-        <v>-10.5298</v>
+        <v>-10.7729</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.4</v>
       </c>
       <c r="I272" t="n">
-        <v>0.969</v>
+        <v>0.9603</v>
       </c>
       <c r="J272" t="n">
-        <v>34.884</v>
+        <v>34.5708</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.36</v>
       </c>
       <c r="I273" t="n">
-        <v>0.8925</v>
+        <v>0.8737</v>
       </c>
       <c r="J273" t="n">
-        <v>32.13</v>
+        <v>31.4532</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.08</v>
       </c>
       <c r="I274" t="n">
-        <v>0.2692</v>
+        <v>0.2357</v>
       </c>
       <c r="J274" t="n">
-        <v>9.6912</v>
+        <v>8.485200000000001</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.03</v>
       </c>
       <c r="I275" t="n">
-        <v>0.1177</v>
+        <v>0.096</v>
       </c>
       <c r="J275" t="n">
-        <v>4.2372</v>
+        <v>3.456</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.74</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.746</v>
+        <v>-0.7188</v>
       </c>
       <c r="J276" t="n">
-        <v>-26.856</v>
+        <v>-25.8768</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.21</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4621</v>
+        <v>0.4044</v>
       </c>
       <c r="J277" t="n">
-        <v>16.6356</v>
+        <v>14.5584</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.16</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3744</v>
+        <v>0.3194</v>
       </c>
       <c r="J278" t="n">
-        <v>13.4784</v>
+        <v>11.4984</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.96</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.0568</v>
       </c>
       <c r="J279" t="n">
-        <v>-2.52</v>
+        <v>-2.0448</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.84</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2079</v>
+        <v>-0.1875</v>
       </c>
       <c r="J280" t="n">
-        <v>-7.4844</v>
+        <v>-6.75</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.61</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4247</v>
+        <v>-0.4166</v>
       </c>
       <c r="J281" t="n">
-        <v>-15.2892</v>
+        <v>-14.9976</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.17</v>
       </c>
       <c r="I282" t="n">
-        <v>0.5252</v>
+        <v>0.4838</v>
       </c>
       <c r="J282" t="n">
-        <v>15.756</v>
+        <v>14.514</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.14</v>
       </c>
       <c r="I283" t="n">
-        <v>0.4518</v>
+        <v>0.4089</v>
       </c>
       <c r="J283" t="n">
-        <v>13.554</v>
+        <v>12.267</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.9</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3368</v>
+        <v>-0.2957</v>
       </c>
       <c r="J284" t="n">
-        <v>-10.104</v>
+        <v>-8.871</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.86</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4389</v>
+        <v>-0.3963</v>
       </c>
       <c r="J285" t="n">
-        <v>-13.167</v>
+        <v>-11.889</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.8</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5819</v>
+        <v>-0.5422</v>
       </c>
       <c r="J286" t="n">
-        <v>-17.457</v>
+        <v>-16.266</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.63</v>
       </c>
       <c r="I287" t="n">
-        <v>1.0183</v>
+        <v>0.985</v>
       </c>
       <c r="J287" t="n">
-        <v>30.549</v>
+        <v>29.55</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.21</v>
       </c>
       <c r="I288" t="n">
-        <v>0.4226</v>
+        <v>0.3681</v>
       </c>
       <c r="J288" t="n">
-        <v>12.678</v>
+        <v>11.043</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.18</v>
       </c>
       <c r="I289" t="n">
-        <v>0.3738</v>
+        <v>0.3222</v>
       </c>
       <c r="J289" t="n">
-        <v>11.214</v>
+        <v>9.666</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.93</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.1243</v>
+        <v>-0.1057</v>
       </c>
       <c r="J290" t="n">
-        <v>-3.729</v>
+        <v>-3.171</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.83</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.2353</v>
+        <v>-0.2159</v>
       </c>
       <c r="J291" t="n">
-        <v>-7.059</v>
+        <v>-6.477</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.48</v>
       </c>
       <c r="I292" t="n">
-        <v>1.0791</v>
+        <v>1.0884</v>
       </c>
       <c r="J292" t="n">
-        <v>30.2148</v>
+        <v>30.4752</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.23</v>
       </c>
       <c r="I293" t="n">
-        <v>0.6103</v>
+        <v>0.5767</v>
       </c>
       <c r="J293" t="n">
-        <v>17.0884</v>
+        <v>16.1476</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.14</v>
       </c>
       <c r="I294" t="n">
-        <v>0.4117</v>
+        <v>0.3767</v>
       </c>
       <c r="J294" t="n">
-        <v>11.5276</v>
+        <v>10.5476</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.13</v>
       </c>
       <c r="I295" t="n">
-        <v>0.3876</v>
+        <v>0.3529</v>
       </c>
       <c r="J295" t="n">
-        <v>10.8528</v>
+        <v>9.8812</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.96</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2032</v>
+        <v>-0.1688</v>
       </c>
       <c r="J296" t="n">
-        <v>-5.6896</v>
+        <v>-4.7264</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.05</v>
       </c>
       <c r="I297" t="n">
-        <v>0.1667</v>
+        <v>0.1295</v>
       </c>
       <c r="J297" t="n">
-        <v>4.6676</v>
+        <v>3.626</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.02</v>
       </c>
       <c r="I298" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="J298" t="n">
-        <v>2.5172</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>0.9</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.1394</v>
+        <v>-0.1219</v>
       </c>
       <c r="J299" t="n">
-        <v>-3.9032</v>
+        <v>-3.4132</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.82</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.2232</v>
+        <v>-0.2034</v>
       </c>
       <c r="J300" t="n">
-        <v>-6.2496</v>
+        <v>-5.6952</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.72</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3198</v>
+        <v>-0.3028</v>
       </c>
       <c r="J301" t="n">
-        <v>-8.9544</v>
+        <v>-8.478400000000001</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>2.27</v>
       </c>
       <c r="I302" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J302" t="n">
-        <v>36.8068</v>
+        <v>37.6542</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.68</v>
       </c>
       <c r="I303" t="n">
-        <v>1.2876</v>
+        <v>1.3087</v>
       </c>
       <c r="J303" t="n">
-        <v>24.4644</v>
+        <v>24.8653</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.29</v>
       </c>
       <c r="I304" t="n">
-        <v>0.694</v>
+        <v>0.6752</v>
       </c>
       <c r="J304" t="n">
-        <v>13.186</v>
+        <v>12.8288</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.18</v>
       </c>
       <c r="I305" t="n">
-        <v>0.4586</v>
+        <v>0.4281</v>
       </c>
       <c r="J305" t="n">
-        <v>8.7134</v>
+        <v>8.133900000000001</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>1.06</v>
       </c>
       <c r="I306" t="n">
-        <v>0.1534</v>
+        <v>0.1223</v>
       </c>
       <c r="J306" t="n">
-        <v>2.9146</v>
+        <v>2.3237</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>0.89</v>
       </c>
       <c r="I307" t="n">
-        <v>-0.0897</v>
+        <v>-0.065</v>
       </c>
       <c r="J307" t="n">
-        <v>-1.7043</v>
+        <v>-1.235</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>0.62</v>
       </c>
       <c r="I308" t="n">
-        <v>-0.3752</v>
+        <v>-0.3674</v>
       </c>
       <c r="J308" t="n">
-        <v>-7.1288</v>
+        <v>-6.9806</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.53</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.4517</v>
+        <v>-0.4464</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.5823</v>
+        <v>-8.4816</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.52</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.4604</v>
+        <v>-0.4556</v>
       </c>
       <c r="J310" t="n">
-        <v>-8.7476</v>
+        <v>-8.6564</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.37</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.5928</v>
+        <v>-0.6028</v>
       </c>
       <c r="J311" t="n">
-        <v>-11.2632</v>
+        <v>-11.4532</v>
       </c>
     </row>
   </sheetData>
